--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-675.25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.14588e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-76.476</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4043484521157514</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.215962186150545</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.268641205323905</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.459481751572342</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.40224004186938</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.59262550879092</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 16.795x + -42442.008</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.446174346851953e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2957.310878308546</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000863e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8157917288676616</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-612.7600000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.15266e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.35899999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1031259032910742</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5158474768805559</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.708667559043178</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.769346542631169</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26.87303368000161</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.73964791022215</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.555x + -41747.851</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.926645648633865e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2818.136109904397</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000002828e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8160709004996413</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-586.7299999999996</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.15732e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-77.54600000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4003635143987926</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.035660664594701</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.24303048267201</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.877751060886731</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.2135071072412</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.95959426068042</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 18.827x + -44233.502</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.611273692567308e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2770.499883988268</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001066e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8161112397314851</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-582.1000000000004</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.16052e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.679</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2790848463037553</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9720057910622409</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.086357294667117</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.56070852187476</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.69027406821463</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.94337178722895</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.727x + -43419.102</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.799116131230236e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2738.470783795171</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8161415299526497</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-580.0700000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.16273e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.785</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1320005761776266</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5898788448772524</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.722435633099827</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.886422766226668</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.25570876041729</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.91349190472587</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.545x + -42499.256</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.607870339666786e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2709.938762978423</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000667272e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8162417044935256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-572.6900000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.16474e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.896</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1011488539538705</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9759825648127232</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.600592509802231</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.592813711548603</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.75840149040733</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.94667929210912</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.747x + -42562.097</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.368947295474501e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2682.490353294699</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8163743724006977</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-564.77</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.16627e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.997</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01113256244457741</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6932445030505685</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.565342913733387</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.05307304989934</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.12355275679124</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.99139012516692</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.026x + -42825.367</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.365977579057178e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2656.665108107153</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.0000000000008e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8165368433119899</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-562.7999999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.16757e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.092</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.08001167371406193</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8978201401428407</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.801134971614064</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.498852406745278</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.26161573876769</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.01787587563746</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.196x + -42825.617</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.427297575336334e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2631.534078467009</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8167168904194366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-552.8499999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.16893e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.182</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5091193001696683</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9883547374671894</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.080962937004636</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.641231383331418</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.35913274757482</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.10495485611359</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.774x + -43856.380</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.690208246476083e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2608.156234797522</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8169165456261026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-544.4200000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.16993e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.27500000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6287450907855094</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.555440802087011</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.182005324648082</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.696524026390361</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.67751904678535</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.13236369503805</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.963x + -43927.055</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.183236991163669e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2585.520217216732</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8171273304527732</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-556.0999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.171e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-78.357</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.03797378536093708</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7404786995810581</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.504904605511882</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.689527057539915</v>
+      </c>
+      <c r="J12" t="n">
+        <v>28.60051469682928</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.00815885216461</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 19.133x + -41567.382</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.321865884620514e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2563.558732946935</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.00000000000115e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8173456463765618</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-544.9200000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.17173e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-78.444</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.372339589765871</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.056167599638492</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.664232576800258</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.186092132764961</v>
+      </c>
+      <c r="J13" t="n">
+        <v>30.39833560627109</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.11014508342402</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.810x + -42825.600</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.492375011082116e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2542.278840355799</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000045e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8175839800948166</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-546.4900000000002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.17268e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-78.527</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2241826537055487</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6995981196637117</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.613274581092191</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.60581834824017</v>
+      </c>
+      <c r="J14" t="n">
+        <v>28.97699599713805</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.06609018252058</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 19.512x + -41759.591</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.961145902892358e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2521.254784654522</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8178274353645306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-544.3899999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.17331e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.608</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.152903171872562</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5410564601294139</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.468643521979724</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.897861082371155</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29.18412697496073</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.08117010795162</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 19.613x + -41655.717</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.374557051954847e-07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2500.248698783896</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8180875736245282</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-540.7399999999998</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.17404e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.69</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.07929164518249984</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7496777894488938</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.47934804324184</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.695175027802178</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29.366564473248</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.10851731474619</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 19.799x + -41731.687</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.00188860235249e-07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2479.724872045197</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.818339884569883</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-532.3899999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.17489e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.777</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2834877170914586</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6880792967926237</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.677578895432414</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.570421953081238</v>
+      </c>
+      <c r="J17" t="n">
+        <v>29.7000588817853</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.1432633073413</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 20.040x + -41939.708</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.547185666435741e-07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2459.630766855817</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000038e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8185987080568147</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-518.46</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.17559e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.857</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6951035669063017</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.369238074906568</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.153683317268301</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.495228206445029</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.48863692569178</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.29865939470274</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 21.194x + -44235.075</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.065801067077589e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2439.037013680881</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000028196e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8188696057591242</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-520.2399999999998</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.17626e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.937</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6085294471584232</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9320251544391329</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.763740913529393</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.11548786633966</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.66075856745751</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.24781104439947</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 20.802x + -42958.585</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.697536725218422e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2418.007745563672</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8191409326258356</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-513.5500000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.17692e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.024</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5506468406664737</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.006631604603938</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.968783456763452</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.219914874500947</v>
+      </c>
+      <c r="J20" t="n">
+        <v>32.12124618548355</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.27759628297817</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.030x + -43110.927</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.498804900438821e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2397.833093734187</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000001034516e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8194210955129446</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-519.6800000000003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.17784e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.09699999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3863404955666404</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8908644633863094</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.597349487633154</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.466298700158758</v>
+      </c>
+      <c r="J21" t="n">
+        <v>30.59816874889495</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.23330587556472</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 20.693x + -41981.280</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.108808720553675e-11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2376.986127538287</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8197060794426098</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-517.3500000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.17848e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.18000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0255792381051713</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8619366017402794</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.712016492473449</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.872758600193317</v>
+      </c>
+      <c r="J22" t="n">
+        <v>30.71820629786453</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.25079846954695</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 20.825x + -41898.688</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>4.663823310436081e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2355.811891586343</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8200016120837688</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-932.3299999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.24795e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-71.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.351712089447939</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5346525096525196</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.358868894601456</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.891891045710701</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.92521170774455</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.77518067147459</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.936x + -31695.466</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.633407731575203e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3348.858405847063</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000001433e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8176324688964132</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-705.8099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.27591e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74.598</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2604726081155406</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8682925588597629</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.843003209222122</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.283966450167652</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.72230928969712</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.8311535793419</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.720x + -34693.279</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.130932399777183e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2971.210459584276</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8186304488560482</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-645.4900000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.27491e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-75.431</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3405891629510262</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7570740741950369</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.624819355432402</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.937162563780081</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.22588634253819</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.09618173693333</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.654x + -35722.081</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.34596987664797e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2874.888625268681</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000494e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8188392396729105</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-610.71</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.27115e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-75.86799999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09281359806952362</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6248765585282292</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.673313312434118</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.943416987370702</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.55264525426246</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.27872389887898</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.375x + -36866.371</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.068528083846652e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2825.492354650542</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.818931678424702</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-593.79</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.26829e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.175</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3252507702836441</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6702863792720708</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.334154849460684</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.498736115110913</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.39637737286728</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.29693210589024</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.451x + -36471.813</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.063072804677998e-13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2786.392827857368</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8190300039319343</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-561.54</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.26654e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.435</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6031141791312884</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.361318890316561</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.142103666731459</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.676917197283583</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35.25966877663292</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.60718310888254</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.868x + -39602.555</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>71.32371058738921</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2951.124386511959</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.94122543945176e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7739560161413798</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-557.48</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.26435e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-76.666</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2782517778857684</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8560230663468272</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.730144211991121</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.025694554913239</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32.56882469018585</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.58337727919802</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.750x + -38731.297</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.671664069029631e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2713.963161309691</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8193195411474939</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-560.77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.26406e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-76.863</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.209247147859762</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4898523840610475</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.350900677888602</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.341463337810215</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.90564934737897</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.42852888923302</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.022x + -36386.844</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15906027969333e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2679.141089504836</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000231054e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8195179577502167</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-533.48</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.26383e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3554047557858076</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.065682989103138</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.115374416730028</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.19396444985413</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.40010693709632</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.71544148268364</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 17.425x + -39367.710</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.961402321364459e-07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2644.967983086389</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000215072e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.819741044798654</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-533.5999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.2639e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.214</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2396836215717126</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8212276295098015</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.65852005091707</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.728566689720725</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.84643536872823</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.6650937504582</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 17.161x + -38233.571</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.830874305526209e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2612.878688775992</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8199776686689161</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-2692.62</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.30997e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-62.577</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09828268689513774</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7616029056828015</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.078156139971908</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.887470264740475</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.540827423535551</v>
+      </c>
+      <c r="K2" t="n">
+        <v>73.45804965490171</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 3.367x + -7394.455</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.250176133771185e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2800.436648582273</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000040855e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8193011799911082</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-2541.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.26476e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-65.34699999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07077816799164052</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5862023396974281</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.462658255783064</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.416665106777531</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.229822125904165</v>
+      </c>
+      <c r="K3" t="n">
+        <v>75.57068894449941</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 3.886x + -8459.622</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.49134392677757e-07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2748.639652876695</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001799e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8196078125782346</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-2374.98</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.22903e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.461</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2051452341700901</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8918816129602155</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.531562759830749</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.377326985851015</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.726290479791841</v>
+      </c>
+      <c r="K4" t="n">
+        <v>77.30774954570983</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 4.440x + -9623.181</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.616761597915119e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2695.722714724801</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000094228e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8199153253866724</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-2268.27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.20005e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-69.122</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02790397103786388</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6694233187989301</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.300299990918514</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.437635894679349</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.324860777640135</v>
+      </c>
+      <c r="K5" t="n">
+        <v>78.40122813074431</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 4.872x + -10357.193</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.957277251521179e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2644.119877974922</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001134e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8202081499390663</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-2145.64</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.17614e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-70.48099999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1703525666696599</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6356889912352495</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.448334753129535</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.581733133281594</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.87607783700206</v>
+      </c>
+      <c r="K6" t="n">
+        <v>79.41318029601423</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 5.350x + -11237.118</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.365394999646195e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2595.641709450079</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000003405e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8205028790290346</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-2026.19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.15564e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.61499999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3468692571341039</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7992433087307012</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.466827841876408</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.381558727541909</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.297198166494563</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.33088549594437</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 5.869x + -12235.653</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.907519249614416e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2550.046520342485</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000082604e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8208088214209822</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-1930.18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.1381e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.572</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3559432753220502</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9029088367543165</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.842867295771248</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.460246614094649</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.809432899368176</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.02085763252262</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 6.329x + -13039.193</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.712281434731494e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2508.296240714393</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.00000000003338e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.821104107191778</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-1853.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.12286e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-73.383</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4061000737413815</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9607490568131309</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.890969493454323</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.31893544742964</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.544806418161984</v>
+      </c>
+      <c r="K9" t="n">
+        <v>81.5544416450562</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.735x + -13681.613</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.77150846792743e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2470.123988374298</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000182e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8214009304057527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-1774.15</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.10946e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-74.098</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3574589822946755</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.174132230665793</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.042499321019899</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.345018449643465</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.072520674758248</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82.06296280385537</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 7.173x + -14416.936</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.267559160568494e-07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2435.292632029961</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000040989e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8216952007464622</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-1716.54</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.09743e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-74.703</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.159299162903933</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9348794798731803</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.88919938055293</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.177263910844529</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.455125735459037</v>
+      </c>
+      <c r="K11" t="n">
+        <v>82.44174116019333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 7.537x + -14959.172</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.970629965494482e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2403.989581371949</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8219854515502615</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-1652.17</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.08665e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-75.248</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2818989704902979</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9796848400953101</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.024466056910844</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.302292843004511</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8.940381589777905</v>
+      </c>
+      <c r="K12" t="n">
+        <v>82.82501076003599</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 7.944x + -15620.647</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.503251757311421e-13</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2375.224608979984</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000459538e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8222867300141146</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-1601.62</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.07698e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-75.712</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1445195712622094</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9964225549353219</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.90034700930518</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.341532147649316</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9.392634698903572</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.14070009546953</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 8.313x + -16202.691</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.880385663385272e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2349.059633724833</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000332e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8225974640222026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-1543.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.0681e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-76.13800000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5109715658727142</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.280810961529238</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.338564743009697</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.898628342599343</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9.971522821040548</v>
+      </c>
+      <c r="K14" t="n">
+        <v>83.47313745807372</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 8.740x + -16933.632</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.33776394399385e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2325.134590092293</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000271805e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8228930558337284</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-1500.92</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.06005e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-76.535</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3079482834051703</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.02901282246354</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.080629440570107</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.429391222295253</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10.30814208468092</v>
+      </c>
+      <c r="K15" t="n">
+        <v>83.70982217498826</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 9.072x + -17399.934</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.691897970421873e-07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2302.386213503685</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000001017256e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8232082846873828</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-1464.27</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.05279e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-76.875</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2232806569564605</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8083771709602533</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.965184303090051</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.085782893982667</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10.60354919654724</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.90195612293191</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.360x + -17780.218</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.596420863316985e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2281.482957277099</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000254311e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8235093953344125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-1423.18</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.04601e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-77.181</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3291835035346856</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.239683973528461</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.186628463024579</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.524495949682303</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11.13585691283479</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.14449794891284</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 9.751x + -18432.760</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>4.04914153174012e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2262.267413097</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000057361e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.823833526716292</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-1397.94</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.03995e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-77.462</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1400064075823448</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6469150326797338</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.801147583736497</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.855228063291323</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11.26177529320516</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.25873709399208</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 9.946x + -18590.350</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.332678423767153e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2243.561325798672</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000059156e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8241433372471451</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-1361.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.03445e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-77.717</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3362170438938402</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.083205160999825</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.069666852391792</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.270577796676044</v>
+      </c>
+      <c r="J19" t="n">
+        <v>11.77426459771022</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.46349994238881</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.317x + -19198.012</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.791828506452589e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2225.670396846531</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000004698e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.824472087062335</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-1344.47</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.0294e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-77.94799999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0727942817379712</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6197745946682452</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.782346509260883</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.350902416540029</v>
+      </c>
+      <c r="J20" t="n">
+        <v>11.84755259556691</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.54481336644989</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.471x + -19274.714</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.54871228109796e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2208.721313615383</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000241999e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8247862378301662</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-1314.67</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.02476e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-78.15300000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1371498733023936</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7819557533516355</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.735665174115177</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.929247007000049</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12.27745721386311</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.70810079069841</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 10.796x + -19784.154</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.308285351258949e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2191.54226953775</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000523e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8251300850646156</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-1277.58</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.02064e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-78.36199999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6118407143698689</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.283535086177792</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.242561983970486</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.730252570759999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12.93574989817571</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.90798416109189</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.222x + -20508.204</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.981113434266894e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2173.953277816343</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000004667e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8254646451709602</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-2184.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.06066e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-68.13500000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03323529411764239</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5329512893983199</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.040393667094533</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.646461735510718</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.115095997461773</v>
+      </c>
+      <c r="K2" t="n">
+        <v>80.04099918911723</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 5.695x + -17003.780</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.299017170095969e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3561.534783168827</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000003729e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8153311125924353</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1375.22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.06208e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74.447</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09072677934034948</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7766287201793104</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.539887881209698</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.036479106934163</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.2068029139813</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.10238482167318</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.681x + -24412.228</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.56791028328439e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3027.806120731897</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8164793472096545</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-1096.69</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.04516e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.376</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.006214192682343294</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7199004900552514</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.574285941957029</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.677150142644777</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.73929516339864</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.36411992149205</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.332x + -29857.004</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.58890149087939e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2904.169312889709</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001367e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.816662360779307</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-962.8199999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.03513e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04535874625506804</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9479411596577552</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.442507000543924</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.760958915287476</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17.45263507456779</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.96138567476852</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.163x + -33763.966</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.047744283612714e-07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2850.779693181451</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001214e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8166529721515329</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-885.1399999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.03004e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.761</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2312135216452247</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.029093103977876</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.704303430190909</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.007237105857376</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.46884776122788</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.29606168709921</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.447x + -36400.095</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.766171171012999e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2811.130742374824</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8166752976051159</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-822.1300000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.02787e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6491779029721033</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.112004246251603</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.254264922955687</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.585852162641555</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.66769371779804</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.58269874209907</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.746x + -39140.930</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.709643256509537e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2774.385414273814</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000001774e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8167686746850028</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-781.3099999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.02807e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.396</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4446433033262315</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.03047810737575</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.159218905806052</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.720878315563495</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.07699888230249</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.74667569071333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.593x + -40636.058</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.260716213093649e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2737.063204049498</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000055239e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8169304140449013</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-764.1599999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.02836e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.63200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0768541015609565</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7127548916280178</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.902331487485214</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.616194317281392</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.83192782000825</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.76097448571575</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.670x + -40135.137</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.91574825998866e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2700.104305961372</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000045479e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8171093812715161</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-732.7199999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.02979e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.822</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2981907175878466</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9032201191637206</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.89304867273694</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.496090710654481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.43064060720236</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.91784436976786</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.572x + -41779.691</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.430121711400597e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2664.010242578872</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8173120931724253</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-706.23</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.03194e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.998</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5386269788962353</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.093624007962492</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.299923682823214</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.380605833319633</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25.37458953308474</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.01672316109487</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.188x + -42674.754</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.211919562091871e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2629.397398106514</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8175394345116048</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1637.08</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.57842e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.52500000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2752556759131756</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8738438933436339</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.258277039167286</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.978384527812829</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.38699743355181</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.45804501702681</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.720x + -21153.516</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.151231363974261e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2940.378757410544</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000429e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8170800878527218</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1580.03</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.448459999999999e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.194</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.34125152597249</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.006189172385059</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.835071799875098</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.955126100229385</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.07052166666573</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.7692368297954</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.159x + -21692.061</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.435099714356694e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2877.569849263805</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000109e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8171699025327676</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-1564.46</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.401880000000001e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.426</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2897065712944905</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.952688158111617</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.769378983903508</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.982383950829181</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12.2283898656731</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.88109535025947</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.328x + -21827.756</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.8788766745626e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2839.102511532107</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.817286867446649</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-1549.19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.375e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.62</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2784728491911144</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9484133574272525</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.865205005101297</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.121437656206457</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12.37299735721171</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.97626890675576</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.477x + -21923.512</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.121789508584776e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2803.344846551031</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000238e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8174671550524111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-1538.46</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.35872e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.804</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2887792939535761</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8608184478155398</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.769491461449418</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.792931833817793</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12.15265269469043</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.0100665319235</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.530x + -21745.042</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.113421678113385e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2768.84520082553</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000001092429e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8176950499965467</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-1524.24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.35006e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.967</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1976087673160707</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9967828845401603</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.653806226773447</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.77575285691956</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12.27558872343377</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.09830283809207</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.674x + -21832.580</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.437600200508825e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2735.163410080701</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000113e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8179413635802457</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-1516.51</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.34184e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.126</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1463057955242794</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.856438485434916</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.719302940828131</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.638636263935107</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12.11917066239051</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.11414152123977</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.700x + -21596.551</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.110718102358396e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2703.336167217894</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000038399e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8182121173767615</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-1499.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.3349e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.28100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1682067765033459</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6027132807923332</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.567620268735897</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.478623539342166</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.27617286274879</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.20301444750847</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.850x + -21717.162</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.506544322010399e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2673.1586047477</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000263e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8184951795438188</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-1482.93</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.32978e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.426</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2638759593495467</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8460017919454449</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.659374231115234</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.804038992718056</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12.42129076838562</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.28788042574816</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.997x + -21832.005</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.623944926286973e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2644.167051989636</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000204752e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8187806748227648</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-1461.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.32597e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.56100000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2703651978947011</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9339526706017143</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.843266510795637</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.99821834362161</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12.89544509940919</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.41238414287929</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.222x + -22181.036</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.444662089361109e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2617.839018677864</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000681719e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8190555621016918</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-1458.27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.31941e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-77.68000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.272702464986374</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8516656219295848</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.700321886216652</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.823896425598233</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12.68976922571673</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.41609917966559</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.228x + -21937.962</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.132752311169298e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2592.809537806709</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000252437e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8193113550764618</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-1433.41</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.315040000000001e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-77.804</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2432533855233023</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9811496632182641</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.885274537030452</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.185695933084879</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.161686605499</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.53410750147854</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 10.451x + -22299.467</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.176235806691076e-11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2569.205079885846</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000231679e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.819588945908863</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-1431.19</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9.3097e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-77.917</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2088343137697278</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9405279858098018</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.631914700329005</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.718176772366594</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12.95295012753672</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.54168297740989</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 10.465x + -22091.474</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.919843425299996e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2547.103345394961</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000007411e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8198538157558599</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-1424.93</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9.30356e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.027</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1539535727695503</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7461654873667664</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.57912517488274</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.428835808229914</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12.8050435640045</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.55528078569466</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.491x + -21924.615</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.732945103672952e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2525.510442954363</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000012506e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.820117022014795</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-1409.17</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.29782e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.13200000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2858722662231373</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8422743896107837</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.804580163022474</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.798510379591264</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13.18660702381656</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.65271676541001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.684x + -22212.937</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.004175479941784e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2504.72971191496</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000008694e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8203806527482911</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-1397.98</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.29285e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.22799999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1952876557735781</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9575754935998457</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.806523278271809</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.893537039049648</v>
+      </c>
+      <c r="J17" t="n">
+        <v>13.29637268490651</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.70259433701786</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.785x + -22258.458</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.867388137333673e-07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2482.542656206414</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000010991e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8207189152318026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-1401.26</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.29393e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.321</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1674167759634101</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5515399556758261</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.476307558152973</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.254327644549057</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12.86616697538675</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.64603379665971</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.670x + -21725.981</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.382385891958653e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2461.482341022391</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.00000000003205e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8209876267237027</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-1391.67</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.289809999999999e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.41800000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05240661942094939</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6821530609324619</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.384632971425122</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.17139615298087</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12.97531977791049</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.69457329624034</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.769x + -21762.479</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.797996536432553e-07</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2441.084636013304</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000366e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8212695826713596</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-1376.68</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9.28614e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-78.514</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1443545867623132</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.01683993127507</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.654138553702395</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.616527856109052</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13.34168565550203</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.79348366567947</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.974x + -22071.437</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.81385976352895e-12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2420.631508356611</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000751e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8215462268639109</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-1368.71</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9.2822e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-78.59999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1900543335885306</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8466804075772832</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.57034902983026</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.646454359194162</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.41818418369149</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.82866510632823</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 11.049x + -22052.732</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>9.728538909672386e-12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2400.477899831852</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000052846e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8218357846702239</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-1363.06</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9.27903e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-78.684</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2886238425663464</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9033020761400803</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.673273219257798</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.596829312972383</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.48579011402794</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.86466674483461</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.127x + -22035.205</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.784561525906281e-14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2380.003056550901</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000034616e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8221202952507087</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-2016.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.08446e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-69.045</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3282519128899155</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4745549738219638</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.406175059952042</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.327945555082893</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.570073520712516</v>
+      </c>
+      <c r="K2" t="n">
+        <v>80.73721974616664</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 6.132x + -17632.540</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.634118355191929e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3426.277144175976</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000008346e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8146441018578838</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1103.42</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.06218e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.702</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2747326961679309</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.053371435186905</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.203422194001293</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.878288145950755</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.82212803326438</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.28228895460036</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.117x + -30470.533</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.545621766313861e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2993.890538410906</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000003499e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8159917055448808</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-826.1200000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.04858e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-77.483</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06691848804571922</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9825703387453746</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.050678709553928</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.443859330279585</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.10825284867704</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.43391916616659</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.046x + -38878.028</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.717342870050876e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2881.523445665949</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8162090927494554</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-699.6199999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.04557e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.26000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1585903117301093</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.920541679164488</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.71063238095848</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.117307654668878</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.50599786847739</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.88917099067753</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.400x + -43691.149</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.82560378692336e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2822.684840454448</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000004966e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8162584938880966</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-620.5699999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.04766e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.70399999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2557441835726451</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8920178745492362</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.678978948650969</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.186563895992851</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.49326071477693</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.17527610992676</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 20.267x + -47442.447</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.319020738600766e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2776.070691800724</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.0000000001712e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8163215401654593</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-563.77</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.05223e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.97199999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7751065582185139</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.296322420044849</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.293963779076286</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.784245072124547</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.07934373742279</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.40124002427947</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 22.032x + -50997.177</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.532729892221022e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2732.703664316689</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000002247e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8164255107216594</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-532.4699999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.05818e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-79.18000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8220000234391124</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.266504796533109</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.31384566685294</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.035243654466353</v>
+      </c>
+      <c r="J8" t="n">
+        <v>36.86370558174956</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.51565192774606</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 23.048x + -52612.937</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.451648262922935e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2690.013723299287</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8165961113650829</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-516.5599999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0646e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-79.351</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.000533340677953229</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7218626016830588</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.551734041007746</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.755654836899503</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.97973420230609</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.45931338250887</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 22.537x + -50504.572</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.144191463462293e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2649.58340716017</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000024128e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8167803308257643</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-491.98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.07121e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.485</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2315240271075035</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.046114567747623</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.611517431102326</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.268281906905949</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38.76723528088041</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.60017302396662</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 23.861x + -52924.021</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.522646389400353e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2612.572034898169</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000010473e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.816979169562252</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-468.5299999999997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.07777e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.614</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4176678509650156</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.032178646042464</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.959736747386208</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.672823096138819</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40.60450106713367</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.66655849222002</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 24.541x + -53765.870</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>7.739910425933144e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2577.284475807136</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.817183405243335</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-950.79</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.12216e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.479</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01459818192057035</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7843182501984999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.473100244793213</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.864628262350316</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.72544786090992</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.55801376568304</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.873x + -32628.333</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.158407408728681e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3000.966359437378</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000016e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8164130298239989</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-620.2600000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.08974e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.91</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2852022569977062</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.976256923290896</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.69723827600437</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.386750131070586</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.41541545467047</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.01869226000765</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 19.201x + -46331.837</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.267505402280966e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2858.286452220459</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000006568e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8167065647458969</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-566.3900000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.08961e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.289</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5956303474934135</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.131043270143834</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.13368993283181</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.284043524765971</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.72600850162941</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.29918540887293</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 21.199x + -50460.777</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.278638785548944e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2810.125957375854</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000103e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8167515396757253</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-558.3699999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.09131e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.46299999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2186491142607339</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5557849035218243</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.647142043977808</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.989378216992125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32.21264936371034</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.22868639762271</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.658x + -48376.396</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.212920454889216e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2775.718603901964</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8168150122545582</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-528.4299999999998</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.09354e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.617</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7004861922642784</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.282758413169379</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.683304026240483</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.417028269304212</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.82580566467998</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.4464775306823</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 22.423x + -52222.310</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.772125858531818e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2743.087221394611</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000412e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8169349031679062</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-528.8499999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.09563e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.754</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.178904364539893</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9668409934956337</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.897286768666898</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.181105565122921</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.36444895627479</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.34289911308397</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 21.548x + -49409.958</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.662437145494402e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2712.132656919507</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8170880359488286</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-517.3899999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.09764e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.871</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1875788963649715</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7727692712609656</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.705178506442147</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.057269809859197</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.01134848913876</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.39173444736568</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 21.952x + -49827.070</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.815134372643754e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2681.705135094257</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.00000000021995e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.81727606034416</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-507.4299999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.09962e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.995</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1984586395792218</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6108531505405014</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.617097081587966</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.141242047260463</v>
+      </c>
+      <c r="J9" t="n">
+        <v>36.06041067582967</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.4350536058772</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 22.323x + -50164.765</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.189743503652721e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2652.352521733277</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000058091e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8174811092270026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-495.8699999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.10124e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.107</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1627757475292828</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8158418787450992</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.990506142132369</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.053935758469916</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36.77464044963155</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.47838622652074</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 22.707x + -50547.523</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.874349845264225e-07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2624.277451985394</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000053324e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8176967688679421</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-489.21</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.10288e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.20999999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3795029295029077</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8920816479133088</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.765145370883507</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.53370399283537</v>
+      </c>
+      <c r="J11" t="n">
+        <v>37.41929287696064</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.5136861120926</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 23.030x + -50785.136</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.09508720581169e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2597.402466653782</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8179342730306878</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-489.3200000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.10439e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-79.315</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1221528593256752</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.712269772537787</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.605058834299211</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.922214100421593</v>
+      </c>
+      <c r="J12" t="n">
+        <v>36.04157715384267</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.47477935649151</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 22.675x + -49418.887</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.292069902934848e-07</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2571.338485166099</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000458739e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8181862236986954</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-467.8599999999997</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.10574e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-79.42</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5121144597659713</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.26419587763395</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.270105709686632</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.833606801051158</v>
+      </c>
+      <c r="J13" t="n">
+        <v>41.45632676217607</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.65379973104764</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 24.407x + -52973.431</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.404457906466545e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2545.880687723539</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000001074221e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8184522424406639</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-468.1500000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.1071e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-79.51300000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1304831456412655</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9995802760611733</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.824102859274035</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.185914003007538</v>
+      </c>
+      <c r="J14" t="n">
+        <v>39.70790059689025</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.61231714323459</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 23.983x + -51462.067</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.332997920019119e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2521.208120926528</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8187267803925982</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-468.6100000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.10818e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.602</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2839603162915313</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9205451098103361</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.443719874368739</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.220654932892219</v>
+      </c>
+      <c r="J15" t="n">
+        <v>37.65759245200111</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.58201238566807</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 23.682x + -50257.670</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.657303427527979e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2496.692704455005</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000137e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8190160205410225</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-468.04</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.1093e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.70399999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1232232152711174</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9739127982943729</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.202335417744026</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.573768742174883</v>
+      </c>
+      <c r="J16" t="n">
+        <v>46.43259293589293</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.53579354827451</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 23.237x + -48760.849</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.783544532625746e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2472.811559824472</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000892e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8193016796615211</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-454.04</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.11052e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.797</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2242079725817378</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9187996126687451</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.663033531451613</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.027639813458334</v>
+      </c>
+      <c r="J17" t="n">
+        <v>39.11480892770913</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.6292814653274</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 24.154x + -50362.640</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.62555120752889e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2449.452069762684</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000346234e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8196020131215307</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-454.0500000000002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.11142e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.88500000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.09628163967238541</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9741841030878656</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.120354554949283</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.414226438917147</v>
+      </c>
+      <c r="J18" t="n">
+        <v>47.88016550422084</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.58538057022264</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 23.715x + -48898.049</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.497575016897093e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2426.012853127347</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000047255e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.819906549407887</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-436.71</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.11242e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.97799999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3534869785112671</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.175115882483673</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.006792044378245</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.63146428611903</v>
+      </c>
+      <c r="J19" t="n">
+        <v>42.80082741720497</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.7471153452157</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 25.419x + -52205.138</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.316421128727929e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2402.776169862276</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000004265e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8202219260390889</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-437.52</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.11353e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-80.068</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.520487214004851</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.029235087183098</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.758815055088038</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.760017712314506</v>
+      </c>
+      <c r="J20" t="n">
+        <v>40.80039090402697</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.71733754839852</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 25.087x + -50954.371</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.157482282360261e-07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2379.335549036302</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000001512e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8205438244321003</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-436.5900000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.11442e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-80.167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1204059498060851</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.157991760388923</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.389271685238115</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.692478720796502</v>
+      </c>
+      <c r="J21" t="n">
+        <v>50.14117466759721</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.67545158645949</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 24.635x + -49449.557</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.907853953670926e-07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2355.776928591757</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000093169e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8208714781043512</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-427.9099999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.11541e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-80.247</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4074102287826862</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9613513484258321</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.631324314147351</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.089787321185214</v>
+      </c>
+      <c r="J22" t="n">
+        <v>41.76096035670199</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.77433507579211</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 25.730x + -51302.461</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.648069116068909e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2331.960599037601</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000613e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8212019332917957</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1292.42</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.16473e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-73.529</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1705113486479065</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.669380866269891</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.495849710787956</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.680957906794052</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.98386916406004</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.81504757162242</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.228x + -22663.296</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.543391031898314e-07</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2835.730603540367</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000011267e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8167432614181571</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-681.1700000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.14144e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-78.32599999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3443449724295845</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8887198939682264</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.038171851145195</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.022664429652752</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.84978111335135</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.73163801047664</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.511x + -37185.606</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.120566299024315e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2475.638686923035</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000058823e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.817839548612131</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-550.4900000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.13888e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.29600000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3080628928242944</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8883974021555604</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.681490067924781</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.842035550518899</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.72756344206774</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.22155861351979</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 20.605x + -42030.693</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.681365641592461e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2384.73543797787</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8180575496901341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-508.9000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.14279e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.645</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1521575297163524</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9787137605648326</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.90350576530762</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.80551532983539</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37.0201779492005</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.28285371747484</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 21.071x + -41999.979</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.271332618036654e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2337.765754142115</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8181737072291551</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-482.0499999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.14852e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-79.82299999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3909932948450671</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.31732583051466</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.577516924395491</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.608130294759603</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41.92343973626763</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.42452716147827</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 22.232x + -43750.633</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.542384284277862e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2299.674847311927</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8183282288016709</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-469.2599999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.15459e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-79.93899999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5376425147784402</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.11915567034871</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.478954541474962</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.63319318604163</v>
+      </c>
+      <c r="J7" t="n">
+        <v>43.02328505880315</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.46758262560354</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 22.610x + -43879.381</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.994722067746133e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2263.576090227162</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000014804e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8185535913428899</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-459.7599999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.16084e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.044</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.421688878271318</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.143131684485049</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.251422612861625</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.720374269805484</v>
+      </c>
+      <c r="J8" t="n">
+        <v>43.74850398809537</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.4984682620041</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 22.890x + -43782.556</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.241463530229632e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2227.982508099498</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000019271e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8188106316763375</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-450.6699999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.16684e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.127</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6365592676736873</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.231003351028856</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.057367278282964</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.228800864550201</v>
+      </c>
+      <c r="J9" t="n">
+        <v>36.49159985701773</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.57902636059939</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 23.652x + -44716.215</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.648657909093709e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2193.76059181959</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000576e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8191120987680168</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-451.1799999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.17275e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-80.19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4924842691373197</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.134240198789247</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.07631910575286</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.48830110929413</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36.50822922866388</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.58993977220025</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 23.760x + -44328.177</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.862618998077169e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2161.87893388501</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000451769e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8194207176122302</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-457.0500000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.17853e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-80.256</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2264305433850435</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.117392401829239</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.322577930274851</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.935797991719898</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40.78955656474856</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.47833890099541</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 22.707x + -41631.849</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.43643614570388e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2132.278289166683</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8197143521420047</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-635.3400000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.28197e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-74.108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1064554128584123</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.723646542944746</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.676437364998014</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.164699549237364</v>
+      </c>
+      <c r="J2" t="n">
+        <v>29.87842624708597</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.9830618655326</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 14.240x + -38132.834</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-38132.8339456133</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.953906100490987e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>635.3400000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000023038e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.814679482164695</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-590.1399999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.28059e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74.872</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07754210820838091</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5794318978754281</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.46129865511279</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.573167636479671</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.17717386508153</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.12328136640721</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 14.757x + -38156.196</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-38156.19630627904</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.877106411401045e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>590.1399999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8150082898075091</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-556.4400000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.28295e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-75.40900000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.127993002124909</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.601992350057154</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.590583914195647</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.788867417764002</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.67782644253197</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.3031339344174</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 15.477x + -38871.998</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-38871.99816183687</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.386027534591969e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>556.4400000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000028e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8152581892365701</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-526.54</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.28391e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-75.785</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2746975209751816</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.151410124808615</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.017523787125124</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.688083327609251</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.04151004180406</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.56350830036413</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 16.653x + -41102.281</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-41102.28092246929</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.439713344369826e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>526.54</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000372e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8154826676393956</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-515.9899999999998</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.28426e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.105</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1747247486835757</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8481655765330968</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.667613251273402</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.877180311973918</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36.37031325931914</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.54510966945305</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 16.564x + -40036.462</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-40036.46154239417</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>78.53704790793282</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>515.9899999999998</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.738751977367518e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7789491904179999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-502.6099999999997</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.28414e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.355</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2801884206066353</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9587330388134956</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.692183183613805</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.952344700347482</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.79967431912971</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.62832489143814</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 16.974x + -40428.375</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-40428.37521305256</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.690695553711296e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>502.6099999999997</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000041e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8158937760381044</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-488.9300000000003</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.28377e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-76.58499999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2568233066973304</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9999132273237242</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.901894083248264</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.116360948905601</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39.21264438855209</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.70581550039525</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 17.374x + -40838.121</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-40838.12123561982</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.931127353574814e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>488.9300000000003</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8160969064026584</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-489.4699999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.28335e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-76.777</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.063483997821269</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6874721448384377</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.54972212901152</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.556446352945444</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.03130433638032</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.63775485952988</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 17.021x + -39410.075</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-39410.07518989902</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.473006236715822e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>489.4699999999998</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8162903173407705</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-474.46</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.28267e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-76.94199999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2130723998028579</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.179269023899987</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.899433613260027</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.223206782438076</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.58253376510598</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.8165993740856</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 17.980x + -41322.738</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41322.73790030564</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.026810933974505e-07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>474.46</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000084e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8164823137323599</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-469.2999999999997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.28177e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.098</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.542966985438997</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8374179095309104</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.862952161601065</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.138637684016357</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.43146965288656</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.85672590772522</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 18.210x + -41430.598</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-41430.59824245364</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.990645963012199e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>469.2999999999997</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000008241e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8166769811266618</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>86.59262550879092</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 16.795x + -42442.008</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-42442.00844638641</v>
       </c>
       <c r="Y2" t="n">
         <v>4.446174346851953e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2957.310878308546</v>
+        <v>675.25</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000863e-08</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>86.73964791022215</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.555x + -41747.851</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-41747.8505701392</v>
       </c>
       <c r="Y3" t="n">
         <v>3.926645648633865e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2818.136109904397</v>
+        <v>612.7600000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000002828e-08</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>86.95959426068042</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.827x + -44233.502</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-44233.50237363524</v>
       </c>
       <c r="Y4" t="n">
         <v>4.611273692567308e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2770.499883988268</v>
+        <v>586.7299999999996</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001066e-08</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>86.94337178722895</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.727x + -43419.102</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-43419.10243874054</v>
       </c>
       <c r="Y5" t="n">
         <v>6.799116131230236e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2738.470783795171</v>
+        <v>582.1000000000004</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000125e-08</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>86.91349190472587</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.545x + -42499.256</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-42499.25624233932</v>
       </c>
       <c r="Y6" t="n">
         <v>4.607870339666786e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2709.938762978423</v>
+        <v>580.0700000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000667272e-08</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>86.94667929210912</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.747x + -42562.097</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-42562.09660949936</v>
       </c>
       <c r="Y7" t="n">
         <v>3.368947295474501e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>2682.490353294699</v>
+        <v>572.6900000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>86.99139012516692</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.026x + -42825.367</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-42825.36712938253</v>
       </c>
       <c r="Y8" t="n">
         <v>1.365977579057178e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>2656.665108107153</v>
+        <v>564.77</v>
       </c>
       <c r="AA8" t="n">
         <v>1.0000000000008e-08</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.01787587563746</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.196x + -42825.617</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-42825.61654719553</v>
       </c>
       <c r="Y9" t="n">
         <v>2.427297575336334e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2631.534078467009</v>
+        <v>562.7999999999997</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000002e-08</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.10495485611359</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.774x + -43856.380</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-43856.38023846823</v>
       </c>
       <c r="Y10" t="n">
         <v>7.690208246476083e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2608.156234797522</v>
+        <v>552.8499999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000007e-08</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.13236369503805</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.963x + -43927.055</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-43927.05484160499</v>
       </c>
       <c r="Y11" t="n">
         <v>9.183236991163669e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2585.520217216732</v>
+        <v>544.4200000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.00815885216461</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 19.133x + -41567.382</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-41567.38222781925</v>
       </c>
       <c r="Y12" t="n">
         <v>1.321865884620514e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2563.558732946935</v>
+        <v>556.0999999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000115e-08</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.11014508342402</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.810x + -42825.600</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-42825.60024840761</v>
       </c>
       <c r="Y13" t="n">
         <v>1.492375011082116e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2542.278840355799</v>
+        <v>544.9200000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000045e-08</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.06609018252058</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 19.512x + -41759.591</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-41759.59065945874</v>
       </c>
       <c r="Y14" t="n">
         <v>1.961145902892358e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2521.254784654522</v>
+        <v>546.4900000000002</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>87.08117010795162</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 19.613x + -41655.717</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-41655.71686141488</v>
       </c>
       <c r="Y15" t="n">
         <v>1.374557051954847e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>2500.248698783896</v>
+        <v>544.3899999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000013e-08</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>87.10851731474619</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 19.799x + -41731.687</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-41731.68655746619</v>
       </c>
       <c r="Y16" t="n">
         <v>2.00188860235249e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2479.724872045197</v>
+        <v>540.7399999999998</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000011e-08</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>87.1432633073413</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 20.040x + -41939.708</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-41939.70817145566</v>
       </c>
       <c r="Y17" t="n">
         <v>1.547185666435741e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2459.630766855817</v>
+        <v>532.3899999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000038e-08</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>87.29865939470274</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 21.194x + -44235.075</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-44235.07464291344</v>
       </c>
       <c r="Y18" t="n">
         <v>3.065801067077589e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2439.037013680881</v>
+        <v>518.46</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000028196e-08</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>87.24781104439947</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 20.802x + -42958.585</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-42958.58507308229</v>
       </c>
       <c r="Y19" t="n">
         <v>6.697536725218422e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>2418.007745563672</v>
+        <v>520.2399999999998</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>87.27759628297817</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.030x + -43110.927</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-43110.92731383773</v>
       </c>
       <c r="Y20" t="n">
         <v>4.498804900438821e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2397.833093734187</v>
+        <v>513.5500000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000001034516e-08</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>87.23330587556472</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 20.693x + -41981.280</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-41981.28002095004</v>
       </c>
       <c r="Y21" t="n">
         <v>1.108808720553675e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>2376.986127538287</v>
+        <v>519.6800000000003</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>87.25079846954695</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 20.825x + -41898.688</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-41898.68804860903</v>
       </c>
       <c r="Y22" t="n">
         <v>4.663823310436081e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2355.811891586343</v>
+        <v>517.3500000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000002e-08</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-541.25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.28058e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.84099999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.194163433587738</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6670985057724697</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.709193311379262</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.819686127346812</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33.80561875811108</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.42018966566322</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 15.984x + -39134.886</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-39134.88641109465</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.346201584347315e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>541.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8154757819674585</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-503.8700000000003</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.27829e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.136</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4747294728314576</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.102091159869512</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.901047706145416</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.679641803997807</v>
+      </c>
+      <c r="J3" t="n">
+        <v>43.05627570807684</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.67330523273606</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 17.204x + -41876.946</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-41876.94588019341</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>83.75473117886415</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>503.8700000000003</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.691142992723424e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.780967023409491</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-496.8199999999997</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.27668e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.336</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1392105860737702</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8768134498366723</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.661150343777948</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.863944713813107</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.79208983319131</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.60482114697501</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 16.856x + -40550.862</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-40550.86197859904</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.778305349677007e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>496.8199999999997</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000075494e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8155189922185858</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-490.6399999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.27571e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.52200000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2143551654566022</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.766405458812792</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.488153616138504</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.580953681497222</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.15027569081094</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.54534473807956</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 16.565x + -39380.509</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-39380.50890870148</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.042367087715085e-13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>490.6399999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000039e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8156234761308356</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-471.3600000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.27539e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.68300000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4885509323865456</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.020740679921186</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.294267129666909</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.910855980219346</v>
+      </c>
+      <c r="J6" t="n">
+        <v>48.97494706455098</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.84878892542856</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 18.164x + -43042.070</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-43042.06978230023</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.226765655563096e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>471.3600000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8157785700358812</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-479.6099999999997</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.27534e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.839</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08132073954127679</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6970211513684268</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.574008974242742</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.635225204086892</v>
+      </c>
+      <c r="J7" t="n">
+        <v>36.58997116610398</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.64711581006519</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 17.069x + -39778.551</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-39778.55145872511</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.370555213838477e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>479.6099999999997</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000028039e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.815958463414011</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-471.6199999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.27533e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-76.98399999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5503181036311141</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7586991216008276</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.505824045544018</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.714998155504976</v>
+      </c>
+      <c r="J8" t="n">
+        <v>37.04345048996161</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.68626034326493</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 17.271x + -39845.885</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-39845.88477792585</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.639426865264397e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>471.6199999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000346e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8161565733378053</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-467.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.27576e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.122</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.248076773120728</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8228164088986888</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.530265305268447</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.704399840750741</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37.57168347329423</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.73805912349943</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 17.546x + -40088.364</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-40088.36449265295</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.89106698798573e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>467.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.816367191251169</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-461.27</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.27601e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.26000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.283092877129246</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6324421221654721</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.558016361027063</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.579758735041262</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38.33538168701444</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.78336861665026</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 17.794x + -40265.934</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-40265.93407313389</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.487039066630172e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>461.27</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8165838324755447</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-453.6100000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.27635e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.39400000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1232250051749076</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9452559549712601</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.892889993227141</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.681253005050837</v>
+      </c>
+      <c r="J11" t="n">
+        <v>38.86940340644297</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.84233742792398</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 18.127x + -40641.367</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-40641.36749474185</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.251661115633033e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>453.6100000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000097e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8168057218030972</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-452.4000000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.27662e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-77.511</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3395658066756795</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8852471682783654</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.53324140218562</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.599496307331837</v>
+      </c>
+      <c r="J12" t="n">
+        <v>38.90562008065035</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.86972303195957</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 18.286x + -40608.098</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-40608.09838101802</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.15906019768179e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>452.4000000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000002822e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8170357128606585</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-454.5100000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.27724e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-77.63</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.143103732856886</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.033791853624912</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.553374370983815</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.197847100359748</v>
+      </c>
+      <c r="J13" t="n">
+        <v>35.46209488087393</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.79657569852306</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 17.867x + -39215.835</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-39215.834981334</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.011035109359172e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>454.5100000000002</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000004689e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.817267568166834</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-437.3099999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.27747e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-77.74299999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6867834704656951</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.142718263417642</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.112321836629423</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.222110741927112</v>
+      </c>
+      <c r="J14" t="n">
+        <v>46.26837202526865</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.04622717891026</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 19.380x + -42415.607</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-42415.60652058148</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.568197931079739e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>437.3099999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000004463e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.817498530694392</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-440.4499999999998</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.27769e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-77.85599999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3070810280766944</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.945461239627484</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.864621360776083</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.882192974311684</v>
+      </c>
+      <c r="J15" t="n">
+        <v>40.84405486143866</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.96987243117405</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 18.891x + -40865.635</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-40865.63523803785</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.668882385665964e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>440.4499999999998</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000034587e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8177484728990478</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-436.3000000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.27797e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-77.95399999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2764510935659455</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8584474492437424</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.732304512806591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.703316406116046</v>
+      </c>
+      <c r="J16" t="n">
+        <v>41.29586192612239</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.00801075613096</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 19.132x + -41060.154</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-41060.15352908917</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.975493885944445e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>436.3000000000002</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000083e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8179983119206899</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-433.0100000000002</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.27819e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.054</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4129723848099105</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9930463655975794</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.868847711609742</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.669374340653552</v>
+      </c>
+      <c r="J17" t="n">
+        <v>41.7331518553174</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.04735833237801</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 19.388x + -41297.608</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-41297.60757870334</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.180398849691809e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>433.0100000000002</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000036812e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8182425081455851</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-433.6800000000003</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.27815e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.15300000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2799956614230413</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9266123712229771</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.492119513334114</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.626126002821499</v>
+      </c>
+      <c r="J18" t="n">
+        <v>37.38913629774545</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.97995825622959</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 18.954x + -39955.254</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-39955.25431451828</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.411626433414081e-07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>433.6800000000003</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000518e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8185019954625765</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-435.9000000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.27844e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.249</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1329113333557849</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6156678325618595</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.086166729616057</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.973528992268247</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.42789423791547</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.90422215506818</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 18.490x + -38582.233</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-38582.23345171555</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.623225235348359e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>435.9000000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000129e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8187606006791117</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-427.2300000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.27864e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-78.337</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.03525333069189232</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9453581139107263</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.464975822075341</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.397735650134339</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.46258477845766</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.03502287608852</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 19.307x + -40108.849</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-40108.84850815025</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.286020065073641e-07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>427.2300000000002</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8190213597313608</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-419.6499999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.27859e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-78.43600000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5548289363493469</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.781478476044307</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.590893656929183</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.43492517675447</v>
+      </c>
+      <c r="J21" t="n">
+        <v>39.03253939354724</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.06902628940732</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 19.531x + -40293.176</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-40293.17597285898</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.2205882081286e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>419.6499999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000289402e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8192920096820018</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-413.7200000000003</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.27857e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-78.52200000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6468039654194114</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.197533273761979</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.89195225538363</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.208686475502759</v>
+      </c>
+      <c r="J22" t="n">
+        <v>44.23170969233752</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.18324832877551</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 20.325x + -41759.076</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-41759.07643624504</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.315705945364943e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>413.7200000000003</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000049884e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8195598352457896</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.77518067147459</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.936x + -31695.466</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-31695.46634223383</v>
       </c>
       <c r="Y2" t="n">
         <v>7.633407731575203e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>3348.858405847063</v>
+        <v>932.3299999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000001433e-08</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.8311535793419</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.720x + -34693.279</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-34693.27933809021</v>
       </c>
       <c r="Y3" t="n">
         <v>2.130932399777183e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2971.210459584276</v>
+        <v>705.8099999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.09618173693333</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.654x + -35722.081</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-35722.08121465044</v>
       </c>
       <c r="Y4" t="n">
         <v>4.34596987664797e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2874.888625268681</v>
+        <v>645.4900000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000494e-08</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.27872389887898</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.375x + -36866.371</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-36866.3705112435</v>
       </c>
       <c r="Y5" t="n">
         <v>2.068528083846652e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2825.492354650542</v>
+        <v>610.71</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.29693210589024</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.451x + -36471.813</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-36471.81292042318</v>
       </c>
       <c r="Y6" t="n">
         <v>2.063072804677998e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>2786.392827857368</v>
+        <v>593.79</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.60718310888254</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.868x + -39602.555</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-39602.55460301263</v>
       </c>
       <c r="Y7" t="n">
         <v>71.32371058738921</v>
       </c>
       <c r="Z7" t="n">
-        <v>2951.124386511959</v>
+        <v>561.54</v>
       </c>
       <c r="AA7" t="n">
         <v>1.94122543945176e-08</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.58337727919802</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.750x + -38731.297</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-38731.29715043544</v>
       </c>
       <c r="Y8" t="n">
         <v>5.671664069029631e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2713.963161309691</v>
+        <v>557.48</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000012e-08</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.42852888923302</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.022x + -36386.844</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-36386.84426795913</v>
       </c>
       <c r="Y9" t="n">
         <v>1.15906027969333e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2679.141089504836</v>
+        <v>560.77</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000231054e-08</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.71544148268364</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 17.425x + -39367.710</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-39367.70994830685</v>
       </c>
       <c r="Y10" t="n">
         <v>1.961402321364459e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>2644.967983086389</v>
+        <v>533.48</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000215072e-08</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>86.6650937504582</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 17.161x + -38233.571</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-38233.57053699046</v>
       </c>
       <c r="Y11" t="n">
         <v>3.830874305526209e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2612.878688775992</v>
+        <v>533.5999999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000004e-08</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>73.45804965490171</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 3.367x + -7394.455</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7394.454779681775</v>
       </c>
       <c r="Y2" t="n">
         <v>1.250176133771185e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2800.436648582273</v>
+        <v>2692.62</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000040855e-08</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>75.57068894449941</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 3.886x + -8459.622</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8459.62206740124</v>
       </c>
       <c r="Y3" t="n">
         <v>1.49134392677757e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2748.639652876695</v>
+        <v>2541.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001799e-08</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>77.30774954570983</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 4.440x + -9623.181</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9623.180604717325</v>
       </c>
       <c r="Y4" t="n">
         <v>7.616761597915119e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2695.722714724801</v>
+        <v>2374.98</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000094228e-08</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>78.40122813074431</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 4.872x + -10357.193</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10357.19282243696</v>
       </c>
       <c r="Y5" t="n">
         <v>9.957277251521179e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2644.119877974922</v>
+        <v>2268.27</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001134e-08</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>79.41318029601423</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 5.350x + -11237.118</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11237.11769570434</v>
       </c>
       <c r="Y6" t="n">
         <v>1.365394999646195e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2595.641709450079</v>
+        <v>2145.64</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003405e-08</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>80.33088549594437</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 5.869x + -12235.653</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12235.65279251055</v>
       </c>
       <c r="Y7" t="n">
         <v>6.907519249614416e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2550.046520342485</v>
+        <v>2026.19</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000082604e-08</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>81.02085763252262</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 6.329x + -13039.193</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13039.19299753835</v>
       </c>
       <c r="Y8" t="n">
         <v>2.712281434731494e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2508.296240714393</v>
+        <v>1930.18</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000003338e-08</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>81.5544416450562</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.735x + -13681.613</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-13681.61296526258</v>
       </c>
       <c r="Y9" t="n">
         <v>1.77150846792743e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2470.123988374298</v>
+        <v>1853.1</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000182e-08</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>82.06296280385537</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 7.173x + -14416.936</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14416.93606936701</v>
       </c>
       <c r="Y10" t="n">
         <v>1.267559160568494e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>2435.292632029961</v>
+        <v>1774.15</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000040989e-08</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>82.44174116019333</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 7.537x + -14959.172</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14959.17237644951</v>
       </c>
       <c r="Y11" t="n">
         <v>3.970629965494482e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2403.989581371949</v>
+        <v>1716.54</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000009e-08</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>82.82501076003599</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 7.944x + -15620.647</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-15620.6470556805</v>
       </c>
       <c r="Y12" t="n">
         <v>9.503251757311421e-13</v>
       </c>
       <c r="Z12" t="n">
-        <v>2375.224608979984</v>
+        <v>1652.17</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000459538e-08</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>83.14070009546953</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 8.313x + -16202.691</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-16202.69067657345</v>
       </c>
       <c r="Y13" t="n">
         <v>3.880385663385272e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2349.059633724833</v>
+        <v>1601.62</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000332e-08</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>83.47313745807372</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 8.740x + -16933.632</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-16933.63222417414</v>
       </c>
       <c r="Y14" t="n">
         <v>4.33776394399385e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2325.134590092293</v>
+        <v>1543.9</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000271805e-08</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>83.70982217498826</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 9.072x + -17399.934</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-17399.93435001546</v>
       </c>
       <c r="Y15" t="n">
         <v>3.691897970421873e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>2302.386213503685</v>
+        <v>1500.92</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000001017256e-08</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>83.90195612293191</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 9.360x + -17780.218</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-17780.21772305097</v>
       </c>
       <c r="Y16" t="n">
         <v>2.596420863316985e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2281.482957277099</v>
+        <v>1464.27</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000254311e-08</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>84.14449794891284</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 9.751x + -18432.760</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-18432.76049437571</v>
       </c>
       <c r="Y17" t="n">
         <v>4.04914153174012e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2262.267413097</v>
+        <v>1423.18</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000057361e-08</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>84.25873709399208</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 9.946x + -18590.350</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-18590.34975627036</v>
       </c>
       <c r="Y18" t="n">
         <v>2.332678423767153e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2243.561325798672</v>
+        <v>1397.94</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000059156e-08</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>84.46349994238881</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.317x + -19198.012</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-19198.0121281137</v>
       </c>
       <c r="Y19" t="n">
         <v>8.791828506452589e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2225.670396846531</v>
+        <v>1361.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000004698e-08</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>84.54481336644989</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 10.471x + -19274.714</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-19274.71448398443</v>
       </c>
       <c r="Y20" t="n">
         <v>1.54871228109796e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2208.721313615383</v>
+        <v>1344.47</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000241999e-08</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>84.70810079069841</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 10.796x + -19784.154</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-19784.15357346259</v>
       </c>
       <c r="Y21" t="n">
         <v>1.308285351258949e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2191.54226953775</v>
+        <v>1314.67</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000523e-08</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>84.90798416109189</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 11.222x + -20508.204</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-20508.20360593375</v>
       </c>
       <c r="Y22" t="n">
         <v>2.981113434266894e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2173.953277816343</v>
+        <v>1277.58</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000004667e-08</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>80.04099918911723</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 5.695x + -17003.780</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-17003.7804559832</v>
       </c>
       <c r="Y2" t="n">
         <v>7.299017170095969e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>3561.534783168827</v>
+        <v>2184.7</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003729e-08</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>84.10238482167318</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.681x + -24412.228</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-24412.2281274665</v>
       </c>
       <c r="Y3" t="n">
         <v>2.56791028328439e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3027.806120731897</v>
+        <v>1375.22</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000006e-08</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.36411992149205</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.332x + -29857.004</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-29857.0041688394</v>
       </c>
       <c r="Y4" t="n">
         <v>4.58890149087939e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2904.169312889709</v>
+        <v>1096.69</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001367e-08</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>85.96138567476852</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.163x + -33763.966</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-33763.96624746999</v>
       </c>
       <c r="Y5" t="n">
         <v>3.047744283612714e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>2850.779693181451</v>
+        <v>962.8199999999997</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001214e-08</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.29606168709921</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.447x + -36400.095</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-36400.09492190822</v>
       </c>
       <c r="Y6" t="n">
         <v>5.766171171012999e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2811.130742374824</v>
+        <v>885.1399999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000024e-08</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.58269874209907</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.746x + -39140.930</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-39140.92978270056</v>
       </c>
       <c r="Y7" t="n">
         <v>1.709643256509537e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2774.385414273814</v>
+        <v>822.1300000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001774e-08</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.74667569071333</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.593x + -40636.058</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-40636.05799411037</v>
       </c>
       <c r="Y8" t="n">
         <v>2.260716213093649e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2737.063204049498</v>
+        <v>781.3099999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000055239e-08</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.76097448571575</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.670x + -40135.137</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-40135.13670245658</v>
       </c>
       <c r="Y9" t="n">
         <v>2.91574825998866e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2700.104305961372</v>
+        <v>764.1599999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000045479e-08</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>86.91784436976786</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.572x + -41779.691</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41779.69062934875</v>
       </c>
       <c r="Y10" t="n">
         <v>2.430121711400597e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2664.010242578872</v>
+        <v>732.7199999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000043e-08</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>87.01672316109487</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.188x + -42674.754</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-42674.75409014634</v>
       </c>
       <c r="Y11" t="n">
         <v>3.211919562091871e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2629.397398106514</v>
+        <v>706.23</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>83.45804501702681</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.720x + -21153.516</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-21153.51643436788</v>
       </c>
       <c r="Y2" t="n">
         <v>2.151231363974261e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2940.378757410544</v>
+        <v>1637.08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000429e-08</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>83.7692368297954</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.159x + -21692.061</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-21692.06069299027</v>
       </c>
       <c r="Y3" t="n">
         <v>2.435099714356694e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2877.569849263805</v>
+        <v>1580.03</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000109e-08</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>83.88109535025947</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.328x + -21827.756</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-21827.75625252727</v>
       </c>
       <c r="Y4" t="n">
         <v>1.8788766745626e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2839.102511532107</v>
+        <v>1564.46</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>83.97626890675576</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.477x + -21923.512</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21923.51170903886</v>
       </c>
       <c r="Y5" t="n">
         <v>2.121789508584776e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2803.344846551031</v>
+        <v>1549.19</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000238e-08</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>84.0100665319235</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.530x + -21745.042</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-21745.04189984535</v>
       </c>
       <c r="Y6" t="n">
         <v>1.113421678113385e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2768.84520082553</v>
+        <v>1538.46</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000001092429e-08</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>84.09830283809207</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 9.674x + -21832.580</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21832.57958975694</v>
       </c>
       <c r="Y7" t="n">
         <v>2.437600200508825e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2735.163410080701</v>
+        <v>1524.24</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000113e-08</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>84.11414152123977</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.700x + -21596.551</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21596.55056860856</v>
       </c>
       <c r="Y8" t="n">
         <v>4.110718102358396e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2703.336167217894</v>
+        <v>1516.51</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000038399e-08</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>84.20301444750847</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.850x + -21717.162</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21717.16180044214</v>
       </c>
       <c r="Y9" t="n">
         <v>8.506544322010399e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2673.1586047477</v>
+        <v>1499.8</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000263e-08</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>84.28788042574816</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.997x + -21832.005</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21832.00522023965</v>
       </c>
       <c r="Y10" t="n">
         <v>5.623944926286973e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2644.167051989636</v>
+        <v>1482.93</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000204752e-08</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>84.41238414287929</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.222x + -22181.036</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-22181.03649170305</v>
       </c>
       <c r="Y11" t="n">
         <v>3.444662089361109e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2617.839018677864</v>
+        <v>1461.2</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000681719e-08</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>84.41609917966559</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.228x + -21937.962</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-21937.96182038993</v>
       </c>
       <c r="Y12" t="n">
         <v>5.132752311169298e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2592.809537806709</v>
+        <v>1458.27</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000252437e-08</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>84.53410750147854</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 10.451x + -22299.467</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-22299.46689124181</v>
       </c>
       <c r="Y13" t="n">
         <v>5.176235806691076e-11</v>
       </c>
       <c r="Z13" t="n">
-        <v>2569.205079885846</v>
+        <v>1433.41</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000231679e-08</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>84.54168297740989</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 10.465x + -22091.474</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-22091.47418929515</v>
       </c>
       <c r="Y14" t="n">
         <v>2.919843425299996e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2547.103345394961</v>
+        <v>1431.19</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000007411e-08</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>84.55528078569466</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 10.491x + -21924.615</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-21924.61462688688</v>
       </c>
       <c r="Y15" t="n">
         <v>3.732945103672952e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2525.510442954363</v>
+        <v>1424.93</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000012506e-08</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>84.65271676541001</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 10.684x + -22212.937</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-22212.93677855975</v>
       </c>
       <c r="Y16" t="n">
         <v>5.004175479941784e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2504.72971191496</v>
+        <v>1409.17</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000008694e-08</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>84.70259433701786</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 10.785x + -22258.458</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-22258.458195896</v>
       </c>
       <c r="Y17" t="n">
         <v>2.867388137333673e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2482.542656206414</v>
+        <v>1397.98</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000010991e-08</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>84.64603379665971</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 10.670x + -21725.981</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-21725.98098129785</v>
       </c>
       <c r="Y18" t="n">
         <v>1.382385891958653e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2461.482341022391</v>
+        <v>1401.26</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000003205e-08</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>84.69457329624034</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.769x + -21762.479</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-21762.47927966942</v>
       </c>
       <c r="Y19" t="n">
         <v>1.797996536432553e-07</v>
       </c>
       <c r="Z19" t="n">
-        <v>2441.084636013304</v>
+        <v>1391.67</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000366e-08</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>84.79348366567947</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 10.974x + -22071.437</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-22071.43666722395</v>
       </c>
       <c r="Y20" t="n">
         <v>5.81385976352895e-12</v>
       </c>
       <c r="Z20" t="n">
-        <v>2420.631508356611</v>
+        <v>1376.68</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000751e-08</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>84.82866510632823</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 11.049x + -22052.732</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-22052.73214628453</v>
       </c>
       <c r="Y21" t="n">
         <v>9.728538909672386e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>2400.477899831852</v>
+        <v>1368.71</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000052846e-08</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>84.86466674483461</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 11.127x + -22035.205</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-22035.20524721704</v>
       </c>
       <c r="Y22" t="n">
         <v>1.784561525906281e-14</v>
       </c>
       <c r="Z22" t="n">
-        <v>2380.003056550901</v>
+        <v>1363.06</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000034616e-08</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>80.73721974616664</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 6.132x + -17632.540</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-17632.54020588438</v>
       </c>
       <c r="Y2" t="n">
         <v>4.634118355191929e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>3426.277144175976</v>
+        <v>2016.05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000008346e-08</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.28228895460036</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.117x + -30470.533</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-30470.53300919475</v>
       </c>
       <c r="Y3" t="n">
         <v>2.545621766313861e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2993.890538410906</v>
+        <v>1103.42</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000003499e-08</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.43391916616659</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.046x + -38878.028</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-38878.02805081943</v>
       </c>
       <c r="Y4" t="n">
         <v>5.717342870050876e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2881.523445665949</v>
+        <v>826.1200000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.88917099067753</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.400x + -43691.149</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-43691.14923864724</v>
       </c>
       <c r="Y5" t="n">
         <v>6.82560378692336e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2822.684840454448</v>
+        <v>699.6199999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000004966e-08</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>87.17527610992676</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 20.267x + -47442.447</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-47442.44694915169</v>
       </c>
       <c r="Y6" t="n">
         <v>5.319020738600766e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2776.070691800724</v>
+        <v>620.5699999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.0000000001712e-08</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>87.40124002427947</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.032x + -50997.177</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-50997.17662337609</v>
       </c>
       <c r="Y7" t="n">
         <v>1.532729892221022e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>2732.703664316689</v>
+        <v>563.77</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000002247e-08</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>87.51565192774606</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.048x + -52612.937</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-52612.93724515766</v>
       </c>
       <c r="Y8" t="n">
         <v>3.451648262922935e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2690.013723299287</v>
+        <v>532.4699999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000011e-08</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>87.45931338250887</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 22.537x + -50504.572</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-50504.57157258208</v>
       </c>
       <c r="Y9" t="n">
         <v>1.144191463462293e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2649.58340716017</v>
+        <v>516.5599999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000024128e-08</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>87.60017302396662</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 23.861x + -52924.021</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-52924.02082403241</v>
       </c>
       <c r="Y10" t="n">
         <v>3.522646389400353e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2612.572034898169</v>
+        <v>491.98</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000010473e-08</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>87.66655849222002</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 24.541x + -53765.870</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-53765.86962565793</v>
       </c>
       <c r="Y11" t="n">
         <v>7.739910425933144e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2577.284475807136</v>
+        <v>468.5299999999997</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.55801376568304</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.873x + -32628.333</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-32628.33277405092</v>
       </c>
       <c r="Y2" t="n">
         <v>1.158407408728681e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>3000.966359437378</v>
+        <v>950.79</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000016e-08</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>87.01869226000765</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 19.201x + -46331.837</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-46331.83728125821</v>
       </c>
       <c r="Y3" t="n">
         <v>9.267505402280966e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2858.286452220459</v>
+        <v>620.2600000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000006568e-08</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>87.29918540887293</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 21.199x + -50460.777</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-50460.77652652798</v>
       </c>
       <c r="Y4" t="n">
         <v>8.278638785548944e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2810.125957375854</v>
+        <v>566.3900000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000103e-08</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>87.22868639762271</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.658x + -48376.396</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-48376.39602861545</v>
       </c>
       <c r="Y5" t="n">
         <v>9.212920454889216e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2775.718603901964</v>
+        <v>558.3699999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000006e-08</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>87.4464775306823</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 22.423x + -52222.310</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-52222.31034223757</v>
       </c>
       <c r="Y6" t="n">
         <v>1.772125858531818e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2743.087221394611</v>
+        <v>528.4299999999998</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000412e-08</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>87.34289911308397</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 21.548x + -49409.958</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-49409.95767648036</v>
       </c>
       <c r="Y7" t="n">
         <v>1.662437145494402e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2712.132656919507</v>
+        <v>528.8499999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000012e-08</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>87.39173444736568</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 21.952x + -49827.070</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-49827.06997530271</v>
       </c>
       <c r="Y8" t="n">
         <v>8.815134372643754e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2681.705135094257</v>
+        <v>517.3899999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000021995e-08</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>87.4350536058772</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 22.323x + -50164.765</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-50164.76515232034</v>
       </c>
       <c r="Y9" t="n">
         <v>3.189743503652721e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2652.352521733277</v>
+        <v>507.4299999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000058091e-08</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>87.47838622652074</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 22.707x + -50547.523</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-50547.52303501256</v>
       </c>
       <c r="Y10" t="n">
         <v>1.874349845264225e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>2624.277451985394</v>
+        <v>495.8699999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000053324e-08</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>87.5136861120926</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 23.030x + -50785.136</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-50785.13580091142</v>
       </c>
       <c r="Y11" t="n">
         <v>1.09508720581169e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2597.402466653782</v>
+        <v>489.21</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000002e-08</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>87.47477935649151</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 22.675x + -49418.887</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-49418.88726750809</v>
       </c>
       <c r="Y12" t="n">
         <v>1.292069902934848e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>2571.338485166099</v>
+        <v>489.3200000000002</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000458739e-08</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>87.65379973104764</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 24.407x + -52973.431</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-52973.43115342722</v>
       </c>
       <c r="Y13" t="n">
         <v>8.404457906466545e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2545.880687723539</v>
+        <v>467.8599999999997</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000001074221e-08</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>87.61231714323459</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 23.983x + -51462.067</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-51462.0670299963</v>
       </c>
       <c r="Y14" t="n">
         <v>9.332997920019119e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2521.208120926528</v>
+        <v>468.1500000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000004e-08</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>87.58201238566807</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 23.682x + -50257.670</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-50257.67016735821</v>
       </c>
       <c r="Y15" t="n">
         <v>3.657303427527979e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2496.692704455005</v>
+        <v>468.6100000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000137e-08</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>87.53579354827451</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 23.237x + -48760.849</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-48760.84925814068</v>
       </c>
       <c r="Y16" t="n">
         <v>2.783544532625746e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2472.811559824472</v>
+        <v>468.04</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000892e-08</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>87.6292814653274</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 24.154x + -50362.640</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-50362.63980650193</v>
       </c>
       <c r="Y17" t="n">
         <v>3.62555120752889e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2449.452069762684</v>
+        <v>454.04</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000346234e-08</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>87.58538057022264</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 23.715x + -48898.049</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-48898.0485121388</v>
       </c>
       <c r="Y18" t="n">
         <v>6.497575016897093e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>2426.012853127347</v>
+        <v>454.0500000000002</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000047255e-08</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>87.7471153452157</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 25.419x + -52205.138</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-52205.13770878645</v>
       </c>
       <c r="Y19" t="n">
         <v>1.316421128727929e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2402.776169862276</v>
+        <v>436.71</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000004265e-08</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>87.71733754839852</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 25.087x + -50954.371</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-50954.37139681785</v>
       </c>
       <c r="Y20" t="n">
         <v>2.157482282360261e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>2379.335549036302</v>
+        <v>437.52</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001512e-08</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>87.67545158645949</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 24.635x + -49449.557</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-49449.55677672399</v>
       </c>
       <c r="Y21" t="n">
         <v>1.907853953670926e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>2355.776928591757</v>
+        <v>436.5900000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000093169e-08</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>87.77433507579211</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 25.730x + -51302.461</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-51302.46071411396</v>
       </c>
       <c r="Y22" t="n">
         <v>5.648069116068909e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2331.960599037601</v>
+        <v>427.9099999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000613e-08</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>83.81504757162242</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.228x + -22663.296</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-22663.29617342908</v>
       </c>
       <c r="Y2" t="n">
         <v>2.543391031898314e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>2835.730603540367</v>
+        <v>1292.42</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000011267e-08</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.73163801047664</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.511x + -37185.606</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-37185.60590686703</v>
       </c>
       <c r="Y3" t="n">
         <v>3.120566299024315e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2475.638686923035</v>
+        <v>681.1700000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000058823e-08</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>87.22155861351979</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 20.605x + -42030.693</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-42030.69338665235</v>
       </c>
       <c r="Y4" t="n">
         <v>2.681365641592461e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2384.73543797787</v>
+        <v>550.4900000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>87.28285371747484</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 21.071x + -41999.979</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-41999.97855136172</v>
       </c>
       <c r="Y5" t="n">
         <v>3.271332618036654e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2337.765754142115</v>
+        <v>508.9000000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>87.42452716147827</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 22.232x + -43750.633</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-43750.63328642953</v>
       </c>
       <c r="Y6" t="n">
         <v>4.542384284277862e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2299.674847311927</v>
+        <v>482.0499999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>87.46758262560354</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.610x + -43879.381</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-43879.38074988562</v>
       </c>
       <c r="Y7" t="n">
         <v>6.994722067746133e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2263.576090227162</v>
+        <v>469.2599999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000014804e-08</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>87.4984682620041</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 22.890x + -43782.556</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-43782.55575465207</v>
       </c>
       <c r="Y8" t="n">
         <v>1.241463530229632e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>2227.982508099498</v>
+        <v>459.7599999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000019271e-08</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>87.57902636059939</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 23.652x + -44716.215</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-44716.21498348555</v>
       </c>
       <c r="Y9" t="n">
         <v>8.648657909093709e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2193.76059181959</v>
+        <v>450.6699999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000576e-08</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>87.58993977220025</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 23.760x + -44328.177</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-44328.17691225108</v>
       </c>
       <c r="Y10" t="n">
         <v>4.862618998077169e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2161.87893388501</v>
+        <v>451.1799999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000451769e-08</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>87.47833890099541</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 22.707x + -41631.849</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-41631.84936293787</v>
       </c>
       <c r="Y11" t="n">
         <v>3.43643614570388e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2132.278289166683</v>
+        <v>457.0500000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000017e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>85.9830618655326</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.240x + -38132.834</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.24016815554302</v>
       </c>
       <c r="X2" t="n">
         <v>-38132.8339456133</v>
@@ -600,7 +598,7 @@
         <v>2.953906100490987e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>635.3400000000001</v>
+        <v>3175.008692786096</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000023038e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.12328136640721</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.757x + -38156.196</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.75689193654533</v>
       </c>
       <c r="X3" t="n">
         <v>-38156.19630627904</v>
@@ -652,7 +648,7 @@
         <v>5.877106411401045e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>590.1399999999999</v>
+        <v>3055.107758096767</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000002e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>86.3031339344174</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.477x + -38871.998</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.47695969870335</v>
       </c>
       <c r="X4" t="n">
         <v>-38871.99816183687</v>
@@ -704,7 +698,7 @@
         <v>4.386027534591969e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>556.4400000000001</v>
+        <v>2963.698906734357</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000028e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.56350830036413</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.653x + -41102.281</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.65275615089208</v>
       </c>
       <c r="X5" t="n">
         <v>-41102.28092246929</v>
@@ -756,7 +748,7 @@
         <v>2.439713344369826e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>526.54</v>
+        <v>2897.704904144261</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000372e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>86.54510966945305</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.564x + -40036.462</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.56386015521477</v>
       </c>
       <c r="X6" t="n">
         <v>-40036.46154239417</v>
@@ -808,7 +798,7 @@
         <v>78.53704790793282</v>
       </c>
       <c r="Z6" t="n">
-        <v>515.9899999999998</v>
+        <v>2969.482668111022</v>
       </c>
       <c r="AA6" t="n">
         <v>1.738751977367518e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>86.62832489143814</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.974x + -40428.375</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.97364809196308</v>
       </c>
       <c r="X7" t="n">
         <v>-40428.37521305256</v>
@@ -860,7 +848,7 @@
         <v>4.690695553711296e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>502.6099999999997</v>
+        <v>2798.066878200266</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000041e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>86.70581550039525</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.374x + -40838.121</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.3738396417849</v>
       </c>
       <c r="X8" t="n">
         <v>-40838.12123561982</v>
@@ -912,7 +898,7 @@
         <v>3.931127353574814e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>488.9300000000003</v>
+        <v>2757.72998409456</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000006e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>86.63775485952988</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.021x + -39410.075</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.02136339980462</v>
       </c>
       <c r="X9" t="n">
         <v>-39410.07518989902</v>
@@ -964,7 +948,7 @@
         <v>1.473006236715822e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>489.4699999999998</v>
+        <v>2722.957052516254</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000003e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>86.8165993740856</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.980x + -41322.738</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.97976963939739</v>
       </c>
       <c r="X10" t="n">
         <v>-41322.73790030564</v>
@@ -1016,7 +998,7 @@
         <v>1.026810933974505e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>474.46</v>
+        <v>2691.072347880301</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000084e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>86.85672590772522</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.210x + -41430.598</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.20976656362333</v>
       </c>
       <c r="X11" t="n">
         <v>-41430.59824245364</v>
@@ -1068,7 +1048,7 @@
         <v>6.990645963012199e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>469.2999999999997</v>
+        <v>2662.185686610608</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000008241e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>86.59262550879092</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.795x + -42442.008</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.79540018822912</v>
       </c>
       <c r="X2" t="n">
         <v>-42442.00844638641</v>
@@ -1266,7 +1244,7 @@
         <v>4.446174346851953e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>675.25</v>
+        <v>2957.310878308546</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000863e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>86.73964791022215</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.555x + -41747.851</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.55452244310214</v>
       </c>
       <c r="X3" t="n">
         <v>-41747.8505701392</v>
@@ -1318,7 +1294,7 @@
         <v>3.926645648633865e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>612.7600000000002</v>
+        <v>2818.136109904397</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000002828e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.95959426068042</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.827x + -44233.502</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.8270890532893</v>
       </c>
       <c r="X4" t="n">
         <v>-44233.50237363524</v>
@@ -1370,7 +1344,7 @@
         <v>4.611273692567308e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>586.7299999999996</v>
+        <v>2770.499883988268</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001066e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>86.94337178722895</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.727x + -43419.102</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.72697952821918</v>
       </c>
       <c r="X5" t="n">
         <v>-43419.10243874054</v>
@@ -1422,7 +1394,7 @@
         <v>6.799116131230236e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>582.1000000000004</v>
+        <v>2738.470783795171</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000125e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>86.91349190472587</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.545x + -42499.256</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.54534117618882</v>
       </c>
       <c r="X6" t="n">
         <v>-42499.25624233932</v>
@@ -1474,7 +1444,7 @@
         <v>4.607870339666786e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>580.0700000000002</v>
+        <v>2709.938762978423</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000667272e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>86.94667929210912</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.747x + -42562.097</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.74730401950919</v>
       </c>
       <c r="X7" t="n">
         <v>-42562.09660949936</v>
@@ -1526,7 +1494,7 @@
         <v>3.368947295474501e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>572.6900000000001</v>
+        <v>2682.490353294699</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>86.99139012516692</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.026x + -42825.367</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.02643126283851</v>
       </c>
       <c r="X8" t="n">
         <v>-42825.36712938253</v>
@@ -1578,7 +1544,7 @@
         <v>1.365977579057178e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>564.77</v>
+        <v>2656.665108107153</v>
       </c>
       <c r="AA8" t="n">
         <v>1.0000000000008e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.01787587563746</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.196x + -42825.617</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.19572426526515</v>
       </c>
       <c r="X9" t="n">
         <v>-42825.61654719553</v>
@@ -1630,7 +1594,7 @@
         <v>2.427297575336334e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>562.7999999999997</v>
+        <v>2631.534078467009</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000002e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.10495485611359</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.774x + -43856.380</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.77413408734121</v>
       </c>
       <c r="X10" t="n">
         <v>-43856.38023846823</v>
@@ -1682,7 +1644,7 @@
         <v>7.690208246476083e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>552.8499999999999</v>
+        <v>2608.156234797522</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000007e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.13236369503805</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.963x + -43927.055</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.96345561032832</v>
       </c>
       <c r="X11" t="n">
         <v>-43927.05484160499</v>
@@ -1734,7 +1694,7 @@
         <v>9.183236991163669e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>544.4200000000001</v>
+        <v>2585.520217216732</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.00815885216461</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 19.133x + -41567.382</t>
-        </is>
+      <c r="W12" t="n">
+        <v>19.13326669055241</v>
       </c>
       <c r="X12" t="n">
         <v>-41567.38222781925</v>
@@ -1786,7 +1744,7 @@
         <v>1.321865884620514e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>556.0999999999999</v>
+        <v>2563.558732946935</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000115e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.11014508342402</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.810x + -42825.600</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.80970922560326</v>
       </c>
       <c r="X13" t="n">
         <v>-42825.60024840761</v>
@@ -1838,7 +1794,7 @@
         <v>1.492375011082116e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>544.9200000000001</v>
+        <v>2542.278840355799</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000045e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.06609018252058</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.512x + -41759.591</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.51174235464678</v>
       </c>
       <c r="X14" t="n">
         <v>-41759.59065945874</v>
@@ -1890,7 +1844,7 @@
         <v>1.961145902892358e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>546.4900000000002</v>
+        <v>2521.254784654522</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>87.08117010795162</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 19.613x + -41655.717</t>
-        </is>
+      <c r="W15" t="n">
+        <v>19.61272435039211</v>
       </c>
       <c r="X15" t="n">
         <v>-41655.71686141488</v>
@@ -1942,7 +1894,7 @@
         <v>1.374557051954847e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>544.3899999999999</v>
+        <v>2500.248698783896</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000013e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>87.10851731474619</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.799x + -41731.687</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.79853835051375</v>
       </c>
       <c r="X16" t="n">
         <v>-41731.68655746619</v>
@@ -1994,7 +1944,7 @@
         <v>2.00188860235249e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>540.7399999999998</v>
+        <v>2479.724872045197</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000011e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>87.1432633073413</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 20.040x + -41939.708</t>
-        </is>
+      <c r="W17" t="n">
+        <v>20.03975141950219</v>
       </c>
       <c r="X17" t="n">
         <v>-41939.70817145566</v>
@@ -2046,7 +1994,7 @@
         <v>1.547185666435741e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>532.3899999999999</v>
+        <v>2459.630766855817</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000038e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>87.29865939470274</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 21.194x + -44235.075</t>
-        </is>
+      <c r="W18" t="n">
+        <v>21.19440972404233</v>
       </c>
       <c r="X18" t="n">
         <v>-44235.07464291344</v>
@@ -2098,7 +2044,7 @@
         <v>3.065801067077589e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>518.46</v>
+        <v>2439.037013680881</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000028196e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>87.24781104439947</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.802x + -42958.585</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.80224386687447</v>
       </c>
       <c r="X19" t="n">
         <v>-42958.58507308229</v>
@@ -2150,7 +2094,7 @@
         <v>6.697536725218422e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>520.2399999999998</v>
+        <v>2418.007745563672</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>87.27759628297817</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.030x + -43110.927</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.03018535035652</v>
       </c>
       <c r="X20" t="n">
         <v>-43110.92731383773</v>
@@ -2202,7 +2144,7 @@
         <v>4.498804900438821e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>513.5500000000002</v>
+        <v>2397.833093734187</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000001034516e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>87.23330587556472</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 20.693x + -41981.280</t>
-        </is>
+      <c r="W21" t="n">
+        <v>20.69301389221734</v>
       </c>
       <c r="X21" t="n">
         <v>-41981.28002095004</v>
@@ -2254,7 +2194,7 @@
         <v>1.108808720553675e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>519.6800000000003</v>
+        <v>2376.986127538287</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>87.25079846954695</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.825x + -41898.688</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.82488345515663</v>
       </c>
       <c r="X22" t="n">
         <v>-41898.68804860903</v>
@@ -2306,7 +2244,7 @@
         <v>4.663823310436081e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>517.3500000000001</v>
+        <v>2355.811891586343</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000002e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>86.42018966566322</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.984x + -39134.886</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.98442371709577</v>
       </c>
       <c r="X2" t="n">
         <v>-39134.88641109465</v>
@@ -2504,7 +2440,7 @@
         <v>6.346201584347315e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>541.25</v>
+        <v>2888.025421322149</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000033e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>86.67330523273606</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.204x + -41876.946</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.20367645339503</v>
       </c>
       <c r="X3" t="n">
         <v>-41876.94588019341</v>
@@ -2556,7 +2490,7 @@
         <v>83.75473117886415</v>
       </c>
       <c r="Z3" t="n">
-        <v>503.8700000000003</v>
+        <v>3022.27719712357</v>
       </c>
       <c r="AA3" t="n">
         <v>1.691142992723424e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>86.60482114697501</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.856x + -40550.862</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.85587226052932</v>
       </c>
       <c r="X4" t="n">
         <v>-40550.86197859904</v>
@@ -2608,7 +2540,7 @@
         <v>8.778305349677007e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>496.8199999999997</v>
+        <v>2832.530158403174</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000075494e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>86.54534473807956</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.565x + -39380.509</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.5649899633888</v>
       </c>
       <c r="X5" t="n">
         <v>-39380.50890870148</v>
@@ -2660,7 +2590,7 @@
         <v>1.042367087715085e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>490.6399999999999</v>
+        <v>2803.854535460625</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000039e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>86.84878892542856</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.164x + -43042.070</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.16380919696649</v>
       </c>
       <c r="X6" t="n">
         <v>-43042.06978230023</v>
@@ -2712,7 +2640,7 @@
         <v>6.226765655563096e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>471.3600000000001</v>
+        <v>2773.885529941073</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000012e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>86.64711581006519</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.069x + -39778.551</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.06899463426671</v>
       </c>
       <c r="X7" t="n">
         <v>-39778.55145872511</v>
@@ -2764,7 +2690,7 @@
         <v>4.370555213838477e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>479.6099999999997</v>
+        <v>2743.312331257359</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000028039e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>86.68626034326493</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.271x + -39845.885</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.271085563754</v>
       </c>
       <c r="X8" t="n">
         <v>-39845.88477792585</v>
@@ -2816,7 +2740,7 @@
         <v>1.639426865264397e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>471.6199999999999</v>
+        <v>2713.193649824203</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000346e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>86.73805912349943</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.546x + -40088.364</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.54595370870052</v>
       </c>
       <c r="X9" t="n">
         <v>-40088.36449265295</v>
@@ -2868,7 +2790,7 @@
         <v>4.89106698798573e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>467.75</v>
+        <v>2683.841014606723</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000012e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>86.78336861665026</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.794x + -40265.934</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.79363728008729</v>
       </c>
       <c r="X10" t="n">
         <v>-40265.93407313389</v>
@@ -2920,7 +2840,7 @@
         <v>6.487039066630172e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>461.27</v>
+        <v>2655.668726110781</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>86.84233742792398</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.127x + -40641.367</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.12662325465679</v>
       </c>
       <c r="X11" t="n">
         <v>-40641.36749474185</v>
@@ -2972,7 +2890,7 @@
         <v>4.251661115633033e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>453.6100000000001</v>
+        <v>2627.814668587311</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000097e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>86.86972303195957</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 18.286x + -40608.098</t>
-        </is>
+      <c r="W12" t="n">
+        <v>18.28552636377845</v>
       </c>
       <c r="X12" t="n">
         <v>-40608.09838101802</v>
@@ -3024,7 +2940,7 @@
         <v>1.15906019768179e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>452.4000000000001</v>
+        <v>2601.024340728439</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000002822e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>86.79657569852306</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 17.867x + -39215.835</t>
-        </is>
+      <c r="W13" t="n">
+        <v>17.86715096361677</v>
       </c>
       <c r="X13" t="n">
         <v>-39215.834981334</v>
@@ -3076,7 +2990,7 @@
         <v>1.011035109359172e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>454.5100000000002</v>
+        <v>2576.156561204085</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000004689e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>87.04622717891026</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.380x + -42415.607</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.38030285596263</v>
       </c>
       <c r="X14" t="n">
         <v>-42415.60652058148</v>
@@ -3128,7 +3040,7 @@
         <v>8.568197931079739e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>437.3099999999999</v>
+        <v>2551.28120425517</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000004463e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>86.96987243117405</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 18.891x + -40865.635</t>
-        </is>
+      <c r="W15" t="n">
+        <v>18.89107024091491</v>
       </c>
       <c r="X15" t="n">
         <v>-40865.63523803785</v>
@@ -3180,7 +3090,7 @@
         <v>8.668882385665964e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>440.4499999999998</v>
+        <v>2527.73415986494</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000034587e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>87.00801075613096</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.132x + -41060.154</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.1323179176302</v>
       </c>
       <c r="X16" t="n">
         <v>-41060.15352908917</v>
@@ -3232,7 +3140,7 @@
         <v>2.975493885944445e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>436.3000000000002</v>
+        <v>2505.63080053129</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000083e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.04735833237801</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 19.388x + -41297.608</t>
-        </is>
+      <c r="W17" t="n">
+        <v>19.38774059540615</v>
       </c>
       <c r="X17" t="n">
         <v>-41297.60757870334</v>
@@ -3284,7 +3190,7 @@
         <v>8.180398849691809e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>433.0100000000002</v>
+        <v>2484.345251598205</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000036812e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>86.97995825622959</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 18.954x + -39955.254</t>
-        </is>
+      <c r="W18" t="n">
+        <v>18.95427703845301</v>
       </c>
       <c r="X18" t="n">
         <v>-39955.25431451828</v>
@@ -3336,7 +3240,7 @@
         <v>2.411626433414081e-07</v>
       </c>
       <c r="Z18" t="n">
-        <v>433.6800000000003</v>
+        <v>2463.688273415643</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000518e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>86.90422215506818</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 18.490x + -38582.233</t>
-        </is>
+      <c r="W19" t="n">
+        <v>18.48970275058602</v>
       </c>
       <c r="X19" t="n">
         <v>-38582.23345171555</v>
@@ -3388,7 +3290,7 @@
         <v>8.623225235348359e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>435.9000000000001</v>
+        <v>2444.242029882198</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000129e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>87.03502287608852</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 19.307x + -40108.849</t>
-        </is>
+      <c r="W20" t="n">
+        <v>19.30693678333607</v>
       </c>
       <c r="X20" t="n">
         <v>-40108.84850815025</v>
@@ -3440,7 +3340,7 @@
         <v>1.286020065073641e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>427.2300000000002</v>
+        <v>2425.190493971836</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000001e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>87.06902628940732</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 19.531x + -40293.176</t>
-        </is>
+      <c r="W21" t="n">
+        <v>19.53132246120225</v>
       </c>
       <c r="X21" t="n">
         <v>-40293.17597285898</v>
@@ -3492,7 +3390,7 @@
         <v>5.2205882081286e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>419.6499999999999</v>
+        <v>2406.66336318262</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000289402e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>87.18324832877551</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.325x + -41759.076</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.32469315436298</v>
       </c>
       <c r="X22" t="n">
         <v>-41759.07643624504</v>
@@ -3544,7 +3440,7 @@
         <v>7.315705945364943e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>413.7200000000003</v>
+        <v>2388.666390912387</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000049884e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.77518067147459</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.936x + -31695.466</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.93566498503863</v>
       </c>
       <c r="X2" t="n">
         <v>-31695.46634223383</v>
@@ -3742,7 +3636,7 @@
         <v>7.633407731575203e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>932.3299999999999</v>
+        <v>3348.858405847063</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000001433e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.8311535793419</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.720x + -34693.279</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.71953521039776</v>
       </c>
       <c r="X3" t="n">
         <v>-34693.27933809021</v>
@@ -3794,7 +3686,7 @@
         <v>2.130932399777183e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>705.8099999999999</v>
+        <v>2971.210459584276</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.09618173693333</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.654x + -35722.081</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.65413773417267</v>
       </c>
       <c r="X4" t="n">
         <v>-35722.08121465044</v>
@@ -3846,7 +3736,7 @@
         <v>4.34596987664797e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>645.4900000000002</v>
+        <v>2874.888625268681</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000494e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.27872389887898</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.375x + -36866.371</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.37515397966675</v>
       </c>
       <c r="X5" t="n">
         <v>-36866.3705112435</v>
@@ -3898,7 +3786,7 @@
         <v>2.068528083846652e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>610.71</v>
+        <v>2825.492354650542</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.29693210589024</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.451x + -36471.813</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.45096703617956</v>
       </c>
       <c r="X6" t="n">
         <v>-36471.81292042318</v>
@@ -3950,7 +3836,7 @@
         <v>2.063072804677998e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>593.79</v>
+        <v>2786.392827857368</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.60718310888254</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.868x + -39602.555</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.86763424158514</v>
       </c>
       <c r="X7" t="n">
         <v>-39602.55460301263</v>
@@ -4002,7 +3886,7 @@
         <v>71.32371058738921</v>
       </c>
       <c r="Z7" t="n">
-        <v>561.54</v>
+        <v>2951.124386511959</v>
       </c>
       <c r="AA7" t="n">
         <v>1.94122543945176e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.58337727919802</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.750x + -38731.297</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.7498303194033</v>
       </c>
       <c r="X8" t="n">
         <v>-38731.29715043544</v>
@@ -4054,7 +3936,7 @@
         <v>5.671664069029631e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>557.48</v>
+        <v>2713.963161309691</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000012e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.42852888923302</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.022x + -36386.844</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.02184381881267</v>
       </c>
       <c r="X9" t="n">
         <v>-36386.84426795913</v>
@@ -4106,7 +3986,7 @@
         <v>1.15906027969333e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>560.77</v>
+        <v>2679.141089504836</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000231054e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.71544148268364</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.425x + -39367.710</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.42486898241969</v>
       </c>
       <c r="X10" t="n">
         <v>-39367.70994830685</v>
@@ -4158,7 +4036,7 @@
         <v>1.961402321364459e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>533.48</v>
+        <v>2644.967983086389</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000215072e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.6650937504582</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.161x + -38233.571</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.16122066654443</v>
       </c>
       <c r="X11" t="n">
         <v>-38233.57053699046</v>
@@ -4210,7 +4086,7 @@
         <v>3.830874305526209e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>533.5999999999999</v>
+        <v>2612.878688775992</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000004e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>73.45804965490171</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 3.367x + -7394.455</t>
-        </is>
+      <c r="W2" t="n">
+        <v>3.366889073765473</v>
       </c>
       <c r="X2" t="n">
         <v>-7394.454779681775</v>
@@ -4408,7 +4282,7 @@
         <v>1.250176133771185e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2692.62</v>
+        <v>2800.436648582273</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000040855e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>75.57068894449941</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 3.886x + -8459.622</t>
-        </is>
+      <c r="W3" t="n">
+        <v>3.886487644215192</v>
       </c>
       <c r="X3" t="n">
         <v>-8459.62206740124</v>
@@ -4460,7 +4332,7 @@
         <v>1.49134392677757e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2541.5</v>
+        <v>2748.639652876695</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001799e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>77.30774954570983</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 4.440x + -9623.181</t>
-        </is>
+      <c r="W4" t="n">
+        <v>4.440150068679038</v>
       </c>
       <c r="X4" t="n">
         <v>-9623.180604717325</v>
@@ -4512,7 +4382,7 @@
         <v>7.616761597915119e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2374.98</v>
+        <v>2695.722714724801</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000094228e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>78.40122813074431</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 4.872x + -10357.193</t>
-        </is>
+      <c r="W5" t="n">
+        <v>4.872150334765174</v>
       </c>
       <c r="X5" t="n">
         <v>-10357.19282243696</v>
@@ -4564,7 +4432,7 @@
         <v>9.957277251521179e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2268.27</v>
+        <v>2644.119877974922</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001134e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>79.41318029601423</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 5.350x + -11237.118</t>
-        </is>
+      <c r="W6" t="n">
+        <v>5.35025935181079</v>
       </c>
       <c r="X6" t="n">
         <v>-11237.11769570434</v>
@@ -4616,7 +4482,7 @@
         <v>1.365394999646195e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2145.64</v>
+        <v>2595.641709450079</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003405e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>80.33088549594437</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 5.869x + -12235.653</t>
-        </is>
+      <c r="W7" t="n">
+        <v>5.869289364400495</v>
       </c>
       <c r="X7" t="n">
         <v>-12235.65279251055</v>
@@ -4668,7 +4532,7 @@
         <v>6.907519249614416e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2026.19</v>
+        <v>2550.046520342485</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000082604e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>81.02085763252262</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.329x + -13039.193</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.328661487669448</v>
       </c>
       <c r="X8" t="n">
         <v>-13039.19299753835</v>
@@ -4720,7 +4582,7 @@
         <v>2.712281434731494e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>1930.18</v>
+        <v>2508.296240714393</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000003338e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>81.5544416450562</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.735x + -13681.613</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.734926037722675</v>
       </c>
       <c r="X9" t="n">
         <v>-13681.61296526258</v>
@@ -4772,7 +4632,7 @@
         <v>1.77150846792743e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1853.1</v>
+        <v>2470.123988374298</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000182e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>82.06296280385537</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 7.173x + -14416.936</t>
-        </is>
+      <c r="W10" t="n">
+        <v>7.172551828871325</v>
       </c>
       <c r="X10" t="n">
         <v>-14416.93606936701</v>
@@ -4824,7 +4682,7 @@
         <v>1.267559160568494e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>1774.15</v>
+        <v>2435.292632029961</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000040989e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>82.44174116019333</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 7.537x + -14959.172</t>
-        </is>
+      <c r="W11" t="n">
+        <v>7.536529441977306</v>
       </c>
       <c r="X11" t="n">
         <v>-14959.17237644951</v>
@@ -4876,7 +4732,7 @@
         <v>3.970629965494482e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1716.54</v>
+        <v>2403.989581371949</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000009e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>82.82501076003599</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 7.944x + -15620.647</t>
-        </is>
+      <c r="W12" t="n">
+        <v>7.94370037160085</v>
       </c>
       <c r="X12" t="n">
         <v>-15620.6470556805</v>
@@ -4928,7 +4782,7 @@
         <v>9.503251757311421e-13</v>
       </c>
       <c r="Z12" t="n">
-        <v>1652.17</v>
+        <v>2375.224608979984</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000459538e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>83.14070009546953</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 8.313x + -16202.691</t>
-        </is>
+      <c r="W13" t="n">
+        <v>8.313062941192261</v>
       </c>
       <c r="X13" t="n">
         <v>-16202.69067657345</v>
@@ -4980,7 +4832,7 @@
         <v>3.880385663385272e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>1601.62</v>
+        <v>2349.059633724833</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000332e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>83.47313745807372</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 8.740x + -16933.632</t>
-        </is>
+      <c r="W14" t="n">
+        <v>8.740451955515589</v>
       </c>
       <c r="X14" t="n">
         <v>-16933.63222417414</v>
@@ -5032,7 +4882,7 @@
         <v>4.33776394399385e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1543.9</v>
+        <v>2325.134590092293</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000271805e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>83.70982217498826</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 9.072x + -17399.934</t>
-        </is>
+      <c r="W15" t="n">
+        <v>9.072145225865652</v>
       </c>
       <c r="X15" t="n">
         <v>-17399.93435001546</v>
@@ -5084,7 +4932,7 @@
         <v>3.691897970421873e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>1500.92</v>
+        <v>2302.386213503685</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000001017256e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>83.90195612293191</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 9.360x + -17780.218</t>
-        </is>
+      <c r="W16" t="n">
+        <v>9.36025993347933</v>
       </c>
       <c r="X16" t="n">
         <v>-17780.21772305097</v>
@@ -5136,7 +4982,7 @@
         <v>2.596420863316985e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1464.27</v>
+        <v>2281.482957277099</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000254311e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>84.14449794891284</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 9.751x + -18432.760</t>
-        </is>
+      <c r="W17" t="n">
+        <v>9.750857716675728</v>
       </c>
       <c r="X17" t="n">
         <v>-18432.76049437571</v>
@@ -5188,7 +5032,7 @@
         <v>4.04914153174012e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>1423.18</v>
+        <v>2262.267413097</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000057361e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>84.25873709399208</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 9.946x + -18590.350</t>
-        </is>
+      <c r="W18" t="n">
+        <v>9.946223720501369</v>
       </c>
       <c r="X18" t="n">
         <v>-18590.34975627036</v>
@@ -5240,7 +5082,7 @@
         <v>2.332678423767153e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1397.94</v>
+        <v>2243.561325798672</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000059156e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>84.46349994238881</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.317x + -19198.012</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.31650625074802</v>
       </c>
       <c r="X19" t="n">
         <v>-19198.0121281137</v>
@@ -5292,7 +5132,7 @@
         <v>8.791828506452589e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>1361.5</v>
+        <v>2225.670396846531</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000004698e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>84.54481336644989</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 10.471x + -19274.714</t>
-        </is>
+      <c r="W20" t="n">
+        <v>10.47123543689568</v>
       </c>
       <c r="X20" t="n">
         <v>-19274.71448398443</v>
@@ -5344,7 +5182,7 @@
         <v>1.54871228109796e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>1344.47</v>
+        <v>2208.721313615383</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000241999e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>84.70810079069841</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 10.796x + -19784.154</t>
-        </is>
+      <c r="W21" t="n">
+        <v>10.79626854335203</v>
       </c>
       <c r="X21" t="n">
         <v>-19784.15357346259</v>
@@ -5396,7 +5232,7 @@
         <v>1.308285351258949e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>1314.67</v>
+        <v>2191.54226953775</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000523e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>84.90798416109189</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.222x + -20508.204</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.22244219281164</v>
       </c>
       <c r="X22" t="n">
         <v>-20508.20360593375</v>
@@ -5448,7 +5282,7 @@
         <v>2.981113434266894e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1277.58</v>
+        <v>2173.953277816343</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000004667e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>80.04099918911723</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 5.695x + -17003.780</t>
-        </is>
+      <c r="W2" t="n">
+        <v>5.695109309334024</v>
       </c>
       <c r="X2" t="n">
         <v>-17003.7804559832</v>
@@ -5646,7 +5478,7 @@
         <v>7.299017170095969e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2184.7</v>
+        <v>3561.534783168827</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003729e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>84.10238482167318</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.681x + -24412.228</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.680740778241681</v>
       </c>
       <c r="X3" t="n">
         <v>-24412.2281274665</v>
@@ -5698,7 +5528,7 @@
         <v>2.56791028328439e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1375.22</v>
+        <v>3027.806120731897</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000006e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.36411992149205</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.332x + -29857.004</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.33222001801092</v>
       </c>
       <c r="X4" t="n">
         <v>-29857.0041688394</v>
@@ -5750,7 +5578,7 @@
         <v>4.58890149087939e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>1096.69</v>
+        <v>2904.169312889709</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001367e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>85.96138567476852</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.163x + -33763.966</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.16348612858299</v>
       </c>
       <c r="X5" t="n">
         <v>-33763.96624746999</v>
@@ -5802,7 +5628,7 @@
         <v>3.047744283612714e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>962.8199999999997</v>
+        <v>2850.779693181451</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001214e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.29606168709921</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.447x + -36400.095</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.44732595469001</v>
       </c>
       <c r="X6" t="n">
         <v>-36400.09492190822</v>
@@ -5854,7 +5678,7 @@
         <v>5.766171171012999e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>885.1399999999999</v>
+        <v>2811.130742374824</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000024e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.58269874209907</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.746x + -39140.930</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.74649658596935</v>
       </c>
       <c r="X7" t="n">
         <v>-39140.92978270056</v>
@@ -5906,7 +5728,7 @@
         <v>1.709643256509537e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>822.1300000000001</v>
+        <v>2774.385414273814</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001774e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.74667569071333</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.593x + -40636.058</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.59252534455447</v>
       </c>
       <c r="X8" t="n">
         <v>-40636.05799411037</v>
@@ -5958,7 +5778,7 @@
         <v>2.260716213093649e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>781.3099999999999</v>
+        <v>2737.063204049498</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000055239e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.76097448571575</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.670x + -40135.137</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.67035499512051</v>
       </c>
       <c r="X9" t="n">
         <v>-40135.13670245658</v>
@@ -6010,7 +5828,7 @@
         <v>2.91574825998866e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>764.1599999999999</v>
+        <v>2700.104305961372</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000045479e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.91784436976786</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.572x + -41779.691</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.57158067210354</v>
       </c>
       <c r="X10" t="n">
         <v>-41779.69062934875</v>
@@ -6062,7 +5878,7 @@
         <v>2.430121711400597e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>732.7199999999998</v>
+        <v>2664.010242578872</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000043e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>87.01672316109487</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.188x + -42674.754</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.18829377474301</v>
       </c>
       <c r="X11" t="n">
         <v>-42674.75409014634</v>
@@ -6114,7 +5928,7 @@
         <v>3.211919562091871e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>706.23</v>
+        <v>2629.397398106514</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>83.45804501702681</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.720x + -21153.516</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.720111820521359</v>
       </c>
       <c r="X2" t="n">
         <v>-21153.51643436788</v>
@@ -6312,7 +6124,7 @@
         <v>2.151231363974261e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1637.08</v>
+        <v>2940.378757410544</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000429e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>83.7692368297954</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.159x + -21692.061</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.159350156905285</v>
       </c>
       <c r="X3" t="n">
         <v>-21692.06069299027</v>
@@ -6364,7 +6174,7 @@
         <v>2.435099714356694e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1580.03</v>
+        <v>2877.569849263805</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000109e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>83.88109535025947</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.328x + -21827.756</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.328105944688248</v>
       </c>
       <c r="X4" t="n">
         <v>-21827.75625252727</v>
@@ -6416,7 +6224,7 @@
         <v>1.8788766745626e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>1564.46</v>
+        <v>2839.102511532107</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>83.97626890675576</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.477x + -21923.512</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.476605675421231</v>
       </c>
       <c r="X5" t="n">
         <v>-21923.51170903886</v>
@@ -6468,7 +6274,7 @@
         <v>2.121789508584776e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1549.19</v>
+        <v>2803.344846551031</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000238e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>84.0100665319235</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.530x + -21745.042</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.530471455674709</v>
       </c>
       <c r="X6" t="n">
         <v>-21745.04189984535</v>
@@ -6520,7 +6324,7 @@
         <v>1.113421678113385e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1538.46</v>
+        <v>2768.84520082553</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000001092429e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>84.09830283809207</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.674x + -21832.580</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.673997424453326</v>
       </c>
       <c r="X7" t="n">
         <v>-21832.57958975694</v>
@@ -6572,7 +6374,7 @@
         <v>2.437600200508825e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1524.24</v>
+        <v>2735.163410080701</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000113e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>84.11414152123977</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.700x + -21596.551</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.700214685389138</v>
       </c>
       <c r="X8" t="n">
         <v>-21596.55056860856</v>
@@ -6624,7 +6424,7 @@
         <v>4.110718102358396e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>1516.51</v>
+        <v>2703.336167217894</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000038399e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>84.20301444750847</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.850x + -21717.162</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.849971030126577</v>
       </c>
       <c r="X9" t="n">
         <v>-21717.16180044214</v>
@@ -6676,7 +6474,7 @@
         <v>8.506544322010399e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1499.8</v>
+        <v>2673.1586047477</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000263e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>84.28788042574816</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.997x + -21832.005</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.997309940605348</v>
       </c>
       <c r="X10" t="n">
         <v>-21832.00522023965</v>
@@ -6728,7 +6524,7 @@
         <v>5.623944926286973e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>1482.93</v>
+        <v>2644.167051989636</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000204752e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>84.41238414287929</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.222x + -22181.036</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.22153753297494</v>
       </c>
       <c r="X11" t="n">
         <v>-22181.03649170305</v>
@@ -6780,7 +6574,7 @@
         <v>3.444662089361109e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>1461.2</v>
+        <v>2617.839018677864</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000681719e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>84.41609917966559</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.228x + -21937.962</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.22838134125219</v>
       </c>
       <c r="X12" t="n">
         <v>-21937.96182038993</v>
@@ -6832,7 +6624,7 @@
         <v>5.132752311169298e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>1458.27</v>
+        <v>2592.809537806709</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000252437e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>84.53410750147854</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 10.451x + -22299.467</t>
-        </is>
+      <c r="W13" t="n">
+        <v>10.45060117301336</v>
       </c>
       <c r="X13" t="n">
         <v>-22299.46689124181</v>
@@ -6884,7 +6674,7 @@
         <v>5.176235806691076e-11</v>
       </c>
       <c r="Z13" t="n">
-        <v>1433.41</v>
+        <v>2569.205079885846</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000231679e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>84.54168297740989</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 10.465x + -22091.474</t>
-        </is>
+      <c r="W14" t="n">
+        <v>10.4651936411462</v>
       </c>
       <c r="X14" t="n">
         <v>-22091.47418929515</v>
@@ -6936,7 +6724,7 @@
         <v>2.919843425299996e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1431.19</v>
+        <v>2547.103345394961</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000007411e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>84.55528078569466</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 10.491x + -21924.615</t>
-        </is>
+      <c r="W15" t="n">
+        <v>10.49148834252562</v>
       </c>
       <c r="X15" t="n">
         <v>-21924.61462688688</v>
@@ -6988,7 +6774,7 @@
         <v>3.732945103672952e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>1424.93</v>
+        <v>2525.510442954363</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000012506e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>84.65271676541001</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 10.684x + -22212.937</t>
-        </is>
+      <c r="W16" t="n">
+        <v>10.68380529942918</v>
       </c>
       <c r="X16" t="n">
         <v>-22212.93677855975</v>
@@ -7040,7 +6824,7 @@
         <v>5.004175479941784e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1409.17</v>
+        <v>2504.72971191496</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000008694e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>84.70259433701786</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.785x + -22258.458</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.78498211860076</v>
       </c>
       <c r="X17" t="n">
         <v>-22258.458195896</v>
@@ -7092,7 +6874,7 @@
         <v>2.867388137333673e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>1397.98</v>
+        <v>2482.542656206414</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000010991e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>84.64603379665971</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 10.670x + -21725.981</t>
-        </is>
+      <c r="W18" t="n">
+        <v>10.67039167623514</v>
       </c>
       <c r="X18" t="n">
         <v>-21725.98098129785</v>
@@ -7144,7 +6924,7 @@
         <v>1.382385891958653e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1401.26</v>
+        <v>2461.482341022391</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000003205e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>84.69457329624034</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.769x + -21762.479</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.76858341444017</v>
       </c>
       <c r="X19" t="n">
         <v>-21762.47927966942</v>
@@ -7196,7 +6974,7 @@
         <v>1.797996536432553e-07</v>
       </c>
       <c r="Z19" t="n">
-        <v>1391.67</v>
+        <v>2441.084636013304</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000366e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>84.79348366567947</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 10.974x + -22071.437</t>
-        </is>
+      <c r="W20" t="n">
+        <v>10.97432181109442</v>
       </c>
       <c r="X20" t="n">
         <v>-22071.43666722395</v>
@@ -7248,7 +7024,7 @@
         <v>5.81385976352895e-12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1376.68</v>
+        <v>2420.631508356611</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000751e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>84.82866510632823</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 11.049x + -22052.732</t>
-        </is>
+      <c r="W21" t="n">
+        <v>11.04939312167336</v>
       </c>
       <c r="X21" t="n">
         <v>-22052.73214628453</v>
@@ -7300,7 +7074,7 @@
         <v>9.728538909672386e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1368.71</v>
+        <v>2400.477899831852</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000052846e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>84.86466674483461</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.127x + -22035.205</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.1272765403254</v>
       </c>
       <c r="X22" t="n">
         <v>-22035.20524721704</v>
@@ -7352,7 +7124,7 @@
         <v>1.784561525906281e-14</v>
       </c>
       <c r="Z22" t="n">
-        <v>1363.06</v>
+        <v>2380.003056550901</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000034616e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>80.73721974616664</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 6.132x + -17632.540</t>
-        </is>
+      <c r="W2" t="n">
+        <v>6.131609207638706</v>
       </c>
       <c r="X2" t="n">
         <v>-17632.54020588438</v>
@@ -7550,7 +7320,7 @@
         <v>4.634118355191929e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2016.05</v>
+        <v>3426.277144175976</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000008346e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.28228895460036</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.117x + -30470.533</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.1173670028781</v>
       </c>
       <c r="X3" t="n">
         <v>-30470.53300919475</v>
@@ -7602,7 +7370,7 @@
         <v>2.545621766313861e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1103.42</v>
+        <v>2993.890538410906</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000003499e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.43391916616659</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.046x + -38878.028</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.04612428919839</v>
       </c>
       <c r="X4" t="n">
         <v>-38878.02805081943</v>
@@ -7654,7 +7420,7 @@
         <v>5.717342870050876e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>826.1200000000003</v>
+        <v>2881.523445665949</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.88917099067753</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.400x + -43691.149</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.40006900872297</v>
       </c>
       <c r="X5" t="n">
         <v>-43691.14923864724</v>
@@ -7706,7 +7470,7 @@
         <v>6.82560378692336e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>699.6199999999999</v>
+        <v>2822.684840454448</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000004966e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>87.17527610992676</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 20.267x + -47442.447</t>
-        </is>
+      <c r="W6" t="n">
+        <v>20.26723810843348</v>
       </c>
       <c r="X6" t="n">
         <v>-47442.44694915169</v>
@@ -7758,7 +7520,7 @@
         <v>5.319020738600766e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>620.5699999999997</v>
+        <v>2776.070691800724</v>
       </c>
       <c r="AA6" t="n">
         <v>1.0000000001712e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>87.40124002427947</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.032x + -50997.177</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.03223232509919</v>
       </c>
       <c r="X7" t="n">
         <v>-50997.17662337609</v>
@@ -7810,7 +7570,7 @@
         <v>1.532729892221022e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>563.77</v>
+        <v>2732.703664316689</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000002247e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>87.51565192774606</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.048x + -52612.937</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.04824694090664</v>
       </c>
       <c r="X8" t="n">
         <v>-52612.93724515766</v>
@@ -7862,7 +7620,7 @@
         <v>3.451648262922935e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>532.4699999999998</v>
+        <v>2690.013723299287</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000011e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>87.45931338250887</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 22.537x + -50504.572</t>
-        </is>
+      <c r="W9" t="n">
+        <v>22.53651434714319</v>
       </c>
       <c r="X9" t="n">
         <v>-50504.57157258208</v>
@@ -7914,7 +7670,7 @@
         <v>1.144191463462293e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>516.5599999999999</v>
+        <v>2649.58340716017</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000024128e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>87.60017302396662</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 23.861x + -52924.021</t>
-        </is>
+      <c r="W10" t="n">
+        <v>23.86099942852023</v>
       </c>
       <c r="X10" t="n">
         <v>-52924.02082403241</v>
@@ -7966,7 +7720,7 @@
         <v>3.522646389400353e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>491.98</v>
+        <v>2612.572034898169</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000010473e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>87.66655849222002</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 24.541x + -53765.870</t>
-        </is>
+      <c r="W11" t="n">
+        <v>24.54061881906125</v>
       </c>
       <c r="X11" t="n">
         <v>-53765.86962565793</v>
@@ -8018,7 +7770,7 @@
         <v>7.739910425933144e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>468.5299999999997</v>
+        <v>2577.284475807136</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.55801376568304</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.873x + -32628.333</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.87283182847432</v>
       </c>
       <c r="X2" t="n">
         <v>-32628.33277405092</v>
@@ -8216,7 +7966,7 @@
         <v>1.158407408728681e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>950.79</v>
+        <v>3000.966359437378</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000016e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>87.01869226000765</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 19.201x + -46331.837</t>
-        </is>
+      <c r="W3" t="n">
+        <v>19.20099021711397</v>
       </c>
       <c r="X3" t="n">
         <v>-46331.83728125821</v>
@@ -8268,7 +8016,7 @@
         <v>9.267505402280966e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>620.2600000000002</v>
+        <v>2858.286452220459</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000006568e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>87.29918540887293</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 21.199x + -50460.777</t>
-        </is>
+      <c r="W4" t="n">
+        <v>21.19854369776972</v>
       </c>
       <c r="X4" t="n">
         <v>-50460.77652652798</v>
@@ -8320,7 +8066,7 @@
         <v>8.278638785548944e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>566.3900000000003</v>
+        <v>2810.125957375854</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000103e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>87.22868639762271</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.658x + -48376.396</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.65846716980608</v>
       </c>
       <c r="X5" t="n">
         <v>-48376.39602861545</v>
@@ -8372,7 +8116,7 @@
         <v>9.212920454889216e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>558.3699999999999</v>
+        <v>2775.718603901964</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000006e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>87.4464775306823</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 22.423x + -52222.310</t>
-        </is>
+      <c r="W6" t="n">
+        <v>22.42308050132992</v>
       </c>
       <c r="X6" t="n">
         <v>-52222.31034223757</v>
@@ -8424,7 +8166,7 @@
         <v>1.772125858531818e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>528.4299999999998</v>
+        <v>2743.087221394611</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000412e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>87.34289911308397</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 21.548x + -49409.958</t>
-        </is>
+      <c r="W7" t="n">
+        <v>21.54780776770696</v>
       </c>
       <c r="X7" t="n">
         <v>-49409.95767648036</v>
@@ -8476,7 +8216,7 @@
         <v>1.662437145494402e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>528.8499999999999</v>
+        <v>2712.132656919507</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000012e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>87.39173444736568</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 21.952x + -49827.070</t>
-        </is>
+      <c r="W8" t="n">
+        <v>21.95182750864125</v>
       </c>
       <c r="X8" t="n">
         <v>-49827.06997530271</v>
@@ -8528,7 +8266,7 @@
         <v>8.815134372643754e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>517.3899999999999</v>
+        <v>2681.705135094257</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000021995e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>87.4350536058772</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 22.323x + -50164.765</t>
-        </is>
+      <c r="W9" t="n">
+        <v>22.32307846666766</v>
       </c>
       <c r="X9" t="n">
         <v>-50164.76515232034</v>
@@ -8580,7 +8316,7 @@
         <v>3.189743503652721e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>507.4299999999998</v>
+        <v>2652.352521733277</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000058091e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>87.47838622652074</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 22.707x + -50547.523</t>
-        </is>
+      <c r="W10" t="n">
+        <v>22.70719761867609</v>
       </c>
       <c r="X10" t="n">
         <v>-50547.52303501256</v>
@@ -8632,7 +8366,7 @@
         <v>1.874349845264225e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>495.8699999999999</v>
+        <v>2624.277451985394</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000053324e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>87.5136861120926</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 23.030x + -50785.136</t>
-        </is>
+      <c r="W11" t="n">
+        <v>23.03000086713526</v>
       </c>
       <c r="X11" t="n">
         <v>-50785.13580091142</v>
@@ -8684,7 +8416,7 @@
         <v>1.09508720581169e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>489.21</v>
+        <v>2597.402466653782</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000002e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>87.47477935649151</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 22.675x + -49418.887</t>
-        </is>
+      <c r="W12" t="n">
+        <v>22.67472210390794</v>
       </c>
       <c r="X12" t="n">
         <v>-49418.88726750809</v>
@@ -8736,7 +8466,7 @@
         <v>1.292069902934848e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>489.3200000000002</v>
+        <v>2571.338485166099</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000458739e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>87.65379973104764</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 24.407x + -52973.431</t>
-        </is>
+      <c r="W13" t="n">
+        <v>24.40701755156487</v>
       </c>
       <c r="X13" t="n">
         <v>-52973.43115342722</v>
@@ -8788,7 +8516,7 @@
         <v>8.404457906466545e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>467.8599999999997</v>
+        <v>2545.880687723539</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000001074221e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>87.61231714323459</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 23.983x + -51462.067</t>
-        </is>
+      <c r="W14" t="n">
+        <v>23.98250180735008</v>
       </c>
       <c r="X14" t="n">
         <v>-51462.0670299963</v>
@@ -8840,7 +8566,7 @@
         <v>9.332997920019119e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>468.1500000000001</v>
+        <v>2521.208120926528</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000004e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>87.58201238566807</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 23.682x + -50257.670</t>
-        </is>
+      <c r="W15" t="n">
+        <v>23.68157744952672</v>
       </c>
       <c r="X15" t="n">
         <v>-50257.67016735821</v>
@@ -8892,7 +8616,7 @@
         <v>3.657303427527979e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>468.6100000000001</v>
+        <v>2496.692704455005</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000137e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>87.53579354827451</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 23.237x + -48760.849</t>
-        </is>
+      <c r="W16" t="n">
+        <v>23.23687117540677</v>
       </c>
       <c r="X16" t="n">
         <v>-48760.84925814068</v>
@@ -8944,7 +8666,7 @@
         <v>2.783544532625746e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>468.04</v>
+        <v>2472.811559824472</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000892e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>87.6292814653274</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 24.154x + -50362.640</t>
-        </is>
+      <c r="W17" t="n">
+        <v>24.15431327082992</v>
       </c>
       <c r="X17" t="n">
         <v>-50362.63980650193</v>
@@ -8996,7 +8716,7 @@
         <v>3.62555120752889e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>454.04</v>
+        <v>2449.452069762684</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000346234e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>87.58538057022264</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 23.715x + -48898.049</t>
-        </is>
+      <c r="W18" t="n">
+        <v>23.7146504221334</v>
       </c>
       <c r="X18" t="n">
         <v>-48898.0485121388</v>
@@ -9048,7 +8766,7 @@
         <v>6.497575016897093e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>454.0500000000002</v>
+        <v>2426.012853127347</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000047255e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>87.7471153452157</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 25.419x + -52205.138</t>
-        </is>
+      <c r="W19" t="n">
+        <v>25.41907698109745</v>
       </c>
       <c r="X19" t="n">
         <v>-52205.13770878645</v>
@@ -9100,7 +8816,7 @@
         <v>1.316421128727929e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>436.71</v>
+        <v>2402.776169862276</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000004265e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>87.71733754839852</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 25.087x + -50954.371</t>
-        </is>
+      <c r="W20" t="n">
+        <v>25.08713564989247</v>
       </c>
       <c r="X20" t="n">
         <v>-50954.37139681785</v>
@@ -9152,7 +8866,7 @@
         <v>2.157482282360261e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>437.52</v>
+        <v>2379.335549036302</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001512e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>87.67545158645949</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 24.635x + -49449.557</t>
-        </is>
+      <c r="W21" t="n">
+        <v>24.63460829349832</v>
       </c>
       <c r="X21" t="n">
         <v>-49449.55677672399</v>
@@ -9204,7 +8916,7 @@
         <v>1.907853953670926e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>436.5900000000001</v>
+        <v>2355.776928591757</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000093169e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>87.77433507579211</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 25.730x + -51302.461</t>
-        </is>
+      <c r="W22" t="n">
+        <v>25.73026928048823</v>
       </c>
       <c r="X22" t="n">
         <v>-51302.46071411396</v>
@@ -9256,7 +8966,7 @@
         <v>5.648069116068909e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>427.9099999999999</v>
+        <v>2331.960599037601</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000613e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>83.81504757162242</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.228x + -22663.296</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.227727530269064</v>
       </c>
       <c r="X2" t="n">
         <v>-22663.29617342908</v>
@@ -9454,7 +9162,7 @@
         <v>2.543391031898314e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1292.42</v>
+        <v>2835.730603540367</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000011267e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.73163801047664</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.511x + -37185.606</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.51140777795655</v>
       </c>
       <c r="X3" t="n">
         <v>-37185.60590686703</v>
@@ -9506,7 +9212,7 @@
         <v>3.120566299024315e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>681.1700000000001</v>
+        <v>2475.638686923035</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000058823e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>87.22155861351979</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 20.605x + -42030.693</t>
-        </is>
+      <c r="W4" t="n">
+        <v>20.60538730188275</v>
       </c>
       <c r="X4" t="n">
         <v>-42030.69338665235</v>
@@ -9558,7 +9262,7 @@
         <v>2.681365641592461e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>550.4900000000002</v>
+        <v>2384.73543797787</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>87.28285371747484</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 21.071x + -41999.979</t>
-        </is>
+      <c r="W5" t="n">
+        <v>21.07093812451513</v>
       </c>
       <c r="X5" t="n">
         <v>-41999.97855136172</v>
@@ -9610,7 +9312,7 @@
         <v>3.271332618036654e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>508.9000000000001</v>
+        <v>2337.765754142115</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>87.42452716147827</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 22.232x + -43750.633</t>
-        </is>
+      <c r="W6" t="n">
+        <v>22.23171756142272</v>
       </c>
       <c r="X6" t="n">
         <v>-43750.63328642953</v>
@@ -9662,7 +9362,7 @@
         <v>4.542384284277862e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>482.0499999999997</v>
+        <v>2299.674847311927</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>87.46758262560354</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.610x + -43879.381</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.61020047834003</v>
       </c>
       <c r="X7" t="n">
         <v>-43879.38074988562</v>
@@ -9714,7 +9412,7 @@
         <v>6.994722067746133e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>469.2599999999998</v>
+        <v>2263.576090227162</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000014804e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>87.4984682620041</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 22.890x + -43782.556</t>
-        </is>
+      <c r="W8" t="n">
+        <v>22.88972329230777</v>
       </c>
       <c r="X8" t="n">
         <v>-43782.55575465207</v>
@@ -9766,7 +9462,7 @@
         <v>1.241463530229632e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>459.7599999999998</v>
+        <v>2227.982508099498</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000019271e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>87.57902636059939</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 23.652x + -44716.215</t>
-        </is>
+      <c r="W9" t="n">
+        <v>23.65233389843858</v>
       </c>
       <c r="X9" t="n">
         <v>-44716.21498348555</v>
@@ -9818,7 +9512,7 @@
         <v>8.648657909093709e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>450.6699999999998</v>
+        <v>2193.76059181959</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000576e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>87.58993977220025</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 23.760x + -44328.177</t>
-        </is>
+      <c r="W10" t="n">
+        <v>23.75956543365822</v>
       </c>
       <c r="X10" t="n">
         <v>-44328.17691225108</v>
@@ -9870,7 +9562,7 @@
         <v>4.862618998077169e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>451.1799999999998</v>
+        <v>2161.87893388501</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000451769e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>87.47833890099541</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 22.707x + -41631.849</t>
-        </is>
+      <c r="W11" t="n">
+        <v>22.70677090829318</v>
       </c>
       <c r="X11" t="n">
         <v>-41631.84936293787</v>
@@ -9922,7 +9612,7 @@
         <v>3.43643614570388e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>457.0500000000002</v>
+        <v>2132.278289166683</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000017e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-635.3400000000001</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-590.1399999999999</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-556.4400000000001</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-526.54</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-515.9899999999998</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-502.6099999999997</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-488.9300000000003</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-489.4699999999998</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-474.46</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-469.2999999999997</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-932.3299999999999</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-705.8099999999999</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-645.4900000000002</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-610.71</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-593.79</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-561.54</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-557.48</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-560.77</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-533.48</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-533.5999999999999</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-2184.7</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-1375.22</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-1096.69</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-962.8199999999997</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-885.1399999999999</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-822.1300000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-781.3099999999999</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-764.1599999999999</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-732.7199999999998</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-706.23</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-2016.05</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-1103.42</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-826.1200000000003</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-699.6199999999999</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-620.5699999999997</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-563.77</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-532.4699999999998</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-516.5599999999999</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-491.98</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-468.5299999999997</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1292.42</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-681.1700000000001</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-550.4900000000002</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-508.9000000000001</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-482.0499999999997</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-469.2599999999998</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-459.7599999999998</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-450.6699999999998</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-451.1799999999998</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-457.0500000000002</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-635.3400000000001</v>
+        <v>2259.073</v>
       </c>
       <c r="D2" t="n">
         <v>1.28197e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-590.1399999999999</v>
+        <v>2158.171</v>
       </c>
       <c r="D3" t="n">
         <v>1.28059e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-556.4400000000001</v>
+        <v>2080.076</v>
       </c>
       <c r="D4" t="n">
         <v>1.28295e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-526.54</v>
+        <v>2034.017</v>
       </c>
       <c r="D5" t="n">
         <v>1.28391e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-515.9899999999998</v>
+        <v>1980.094</v>
       </c>
       <c r="D6" t="n">
         <v>1.28426e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-502.6099999999997</v>
+        <v>1944.416</v>
       </c>
       <c r="D7" t="n">
         <v>1.28414e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-488.9300000000003</v>
+        <v>1912.142</v>
       </c>
       <c r="D8" t="n">
         <v>1.28377e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-489.4699999999998</v>
+        <v>1873.944</v>
       </c>
       <c r="D9" t="n">
         <v>1.28335e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-474.46</v>
+        <v>1856.957</v>
       </c>
       <c r="D10" t="n">
         <v>1.28267e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-469.2999999999997</v>
+        <v>1832.666</v>
       </c>
       <c r="D11" t="n">
         <v>1.28177e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-675.25</v>
+        <v>2095.015</v>
       </c>
       <c r="D2" t="n">
         <v>1.14588e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-612.7600000000002</v>
+        <v>1942.56</v>
       </c>
       <c r="D3" t="n">
         <v>1.15266e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-586.7299999999996</v>
+        <v>1912.647</v>
       </c>
       <c r="D4" t="n">
         <v>1.15732e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-582.1000000000004</v>
+        <v>1878.785</v>
       </c>
       <c r="D5" t="n">
         <v>1.16052e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-580.0700000000002</v>
+        <v>1850.33</v>
       </c>
       <c r="D6" t="n">
         <v>1.16273e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-572.6900000000001</v>
+        <v>1827.594</v>
       </c>
       <c r="D7" t="n">
         <v>1.16474e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-564.77</v>
+        <v>1809.308</v>
       </c>
       <c r="D8" t="n">
         <v>1.16627e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-562.7999999999997</v>
+        <v>1786.477</v>
       </c>
       <c r="D9" t="n">
         <v>1.16757e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-552.8499999999999</v>
+        <v>1773.525</v>
       </c>
       <c r="D10" t="n">
         <v>1.16893e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-544.4200000000001</v>
+        <v>1759.778</v>
       </c>
       <c r="D11" t="n">
         <v>1.16993e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-556.0999999999999</v>
+        <v>1726.409</v>
       </c>
       <c r="D12" t="n">
         <v>1.171e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-544.9200000000001</v>
+        <v>1717.154</v>
       </c>
       <c r="D13" t="n">
         <v>1.17173e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-546.4900000000002</v>
+        <v>1695.56</v>
       </c>
       <c r="D14" t="n">
         <v>1.17268e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-544.3899999999999</v>
+        <v>1678.577</v>
       </c>
       <c r="D15" t="n">
         <v>1.17331e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-540.7399999999998</v>
+        <v>1662.797</v>
       </c>
       <c r="D16" t="n">
         <v>1.17404e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-532.3899999999999</v>
+        <v>1651.177</v>
       </c>
       <c r="D17" t="n">
         <v>1.17489e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-518.46</v>
+        <v>1645.527</v>
       </c>
       <c r="D18" t="n">
         <v>1.17559e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-520.2399999999998</v>
+        <v>1624.622</v>
       </c>
       <c r="D19" t="n">
         <v>1.17626e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-513.5500000000002</v>
+        <v>1611.732</v>
       </c>
       <c r="D20" t="n">
         <v>1.17692e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-519.6800000000003</v>
+        <v>1587.974</v>
       </c>
       <c r="D21" t="n">
         <v>1.17784e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-517.3500000000001</v>
+        <v>1571.216</v>
       </c>
       <c r="D22" t="n">
         <v>1.17848e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-541.25</v>
+        <v>2016.385</v>
       </c>
       <c r="D2" t="n">
         <v>1.28058e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-503.8700000000003</v>
+        <v>2000.103</v>
       </c>
       <c r="D3" t="n">
         <v>1.27829e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-496.8199999999997</v>
+        <v>1970.804</v>
       </c>
       <c r="D4" t="n">
         <v>1.27668e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-490.6399999999999</v>
+        <v>1940.552</v>
       </c>
       <c r="D5" t="n">
         <v>1.27571e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-471.3600000000001</v>
+        <v>1928.491</v>
       </c>
       <c r="D6" t="n">
         <v>1.27539e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-479.6099999999997</v>
+        <v>1888.034</v>
       </c>
       <c r="D7" t="n">
         <v>1.27534e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-471.6199999999999</v>
+        <v>1866.716</v>
       </c>
       <c r="D8" t="n">
         <v>1.27533e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-467.75</v>
+        <v>1841.636</v>
       </c>
       <c r="D9" t="n">
         <v>1.27576e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-461.27</v>
+        <v>1819.354</v>
       </c>
       <c r="D10" t="n">
         <v>1.27601e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-453.6100000000001</v>
+        <v>1799.848</v>
       </c>
       <c r="D11" t="n">
         <v>1.27635e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-452.4000000000001</v>
+        <v>1776.233</v>
       </c>
       <c r="D12" t="n">
         <v>1.27662e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-454.5100000000002</v>
+        <v>1750.01</v>
       </c>
       <c r="D13" t="n">
         <v>1.27724e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-437.3099999999999</v>
+        <v>1743.236</v>
       </c>
       <c r="D14" t="n">
         <v>1.27747e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-440.4499999999998</v>
+        <v>1717.85</v>
       </c>
       <c r="D15" t="n">
         <v>1.27769e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-436.3000000000002</v>
+        <v>1702.134</v>
       </c>
       <c r="D16" t="n">
         <v>1.27797e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-433.0100000000002</v>
+        <v>1685.086</v>
       </c>
       <c r="D17" t="n">
         <v>1.27819e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-433.6800000000003</v>
+        <v>1664.727</v>
       </c>
       <c r="D18" t="n">
         <v>1.27815e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-435.9000000000001</v>
+        <v>1643.39</v>
       </c>
       <c r="D19" t="n">
         <v>1.27844e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-427.2300000000002</v>
+        <v>1634.587</v>
       </c>
       <c r="D20" t="n">
         <v>1.27864e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-419.6499999999999</v>
+        <v>1622.423</v>
       </c>
       <c r="D21" t="n">
         <v>1.27859e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-413.7200000000003</v>
+        <v>1611.734</v>
       </c>
       <c r="D22" t="n">
         <v>1.27857e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-932.3299999999999</v>
+        <v>2497.835</v>
       </c>
       <c r="D2" t="n">
         <v>1.24795e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-705.8099999999999</v>
+        <v>2127.574</v>
       </c>
       <c r="D3" t="n">
         <v>1.27591e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-645.4900000000002</v>
+        <v>2029.177</v>
       </c>
       <c r="D4" t="n">
         <v>1.27491e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-610.71</v>
+        <v>1985.279</v>
       </c>
       <c r="D5" t="n">
         <v>1.27115e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-593.79</v>
+        <v>1948.283</v>
       </c>
       <c r="D6" t="n">
         <v>1.26829e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-561.54</v>
+        <v>1931.672</v>
       </c>
       <c r="D7" t="n">
         <v>1.26654e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-557.48</v>
+        <v>1893.567</v>
       </c>
       <c r="D8" t="n">
         <v>1.26435e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-560.77</v>
+        <v>1851.347</v>
       </c>
       <c r="D9" t="n">
         <v>1.26406e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-533.48</v>
+        <v>1839.816</v>
       </c>
       <c r="D10" t="n">
         <v>1.26383e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-533.5999999999999</v>
+        <v>1806.465</v>
       </c>
       <c r="D11" t="n">
         <v>1.2639e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-2692.62</v>
+        <v>1899.203</v>
       </c>
       <c r="D2" t="n">
         <v>1.30997e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-2541.5</v>
+        <v>1850.708</v>
       </c>
       <c r="D3" t="n">
         <v>1.26476e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-2374.98</v>
+        <v>1829.823</v>
       </c>
       <c r="D4" t="n">
         <v>1.22903e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-2268.27</v>
+        <v>1766.049</v>
       </c>
       <c r="D5" t="n">
         <v>1.20005e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-2145.64</v>
+        <v>1732.083</v>
       </c>
       <c r="D6" t="n">
         <v>1.17614e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-2026.19</v>
+        <v>1709.977</v>
       </c>
       <c r="D7" t="n">
         <v>1.15564e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-1930.18</v>
+        <v>1678.77</v>
       </c>
       <c r="D8" t="n">
         <v>1.1381e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-1853.1</v>
+        <v>1643.45</v>
       </c>
       <c r="D9" t="n">
         <v>1.12286e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-1774.15</v>
+        <v>1617.987</v>
       </c>
       <c r="D10" t="n">
         <v>1.10946e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-1716.54</v>
+        <v>1585.458</v>
       </c>
       <c r="D11" t="n">
         <v>1.09743e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-1652.17</v>
+        <v>1565.023</v>
       </c>
       <c r="D12" t="n">
         <v>1.08665e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-1601.62</v>
+        <v>1544.104</v>
       </c>
       <c r="D13" t="n">
         <v>1.07698e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-1543.9</v>
+        <v>1533.734</v>
       </c>
       <c r="D14" t="n">
         <v>1.0681e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-1500.92</v>
+        <v>1509.959</v>
       </c>
       <c r="D15" t="n">
         <v>1.06005e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-1464.27</v>
+        <v>1491.532</v>
       </c>
       <c r="D16" t="n">
         <v>1.05279e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-1423.18</v>
+        <v>1481.609</v>
       </c>
       <c r="D17" t="n">
         <v>1.04601e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-1397.94</v>
+        <v>1459.053</v>
       </c>
       <c r="D18" t="n">
         <v>1.03995e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-1361.5</v>
+        <v>1451.259</v>
       </c>
       <c r="D19" t="n">
         <v>1.03445e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-1344.47</v>
+        <v>1428.427</v>
       </c>
       <c r="D20" t="n">
         <v>1.0294e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-1314.67</v>
+        <v>1422.202</v>
       </c>
       <c r="D21" t="n">
         <v>1.02476e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-1277.58</v>
+        <v>1421.031</v>
       </c>
       <c r="D22" t="n">
         <v>1.02064e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-2184.7</v>
+        <v>2633.046</v>
       </c>
       <c r="D2" t="n">
         <v>1.06066e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-1375.22</v>
+        <v>2117.304</v>
       </c>
       <c r="D3" t="n">
         <v>1.06208e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-1096.69</v>
+        <v>2005.532</v>
       </c>
       <c r="D4" t="n">
         <v>1.04516e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-962.8199999999997</v>
+        <v>1958.687</v>
       </c>
       <c r="D5" t="n">
         <v>1.03513e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-885.1399999999999</v>
+        <v>1926.158</v>
       </c>
       <c r="D6" t="n">
         <v>1.03004e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-822.1300000000001</v>
+        <v>1904.402</v>
       </c>
       <c r="D7" t="n">
         <v>1.02787e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-781.3099999999999</v>
+        <v>1874.635</v>
       </c>
       <c r="D8" t="n">
         <v>1.02807e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-764.1599999999999</v>
+        <v>1830.542</v>
       </c>
       <c r="D9" t="n">
         <v>1.02836e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-732.7199999999998</v>
+        <v>1809.123</v>
       </c>
       <c r="D10" t="n">
         <v>1.02979e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-706.23</v>
+        <v>1784.224</v>
       </c>
       <c r="D11" t="n">
         <v>1.03194e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-1637.08</v>
+        <v>1998.283</v>
       </c>
       <c r="D2" t="n">
         <v>9.57842e-08</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-1580.03</v>
+        <v>1933.762</v>
       </c>
       <c r="D3" t="n">
         <v>9.448459999999999e-08</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-1564.46</v>
+        <v>1906.504</v>
       </c>
       <c r="D4" t="n">
         <v>9.401880000000001e-08</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-1549.19</v>
+        <v>1879.386</v>
       </c>
       <c r="D5" t="n">
         <v>9.375e-08</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-1538.46</v>
+        <v>1846.948</v>
       </c>
       <c r="D6" t="n">
         <v>9.35872e-08</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-1524.24</v>
+        <v>1820.943</v>
       </c>
       <c r="D7" t="n">
         <v>9.35006e-08</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-1516.51</v>
+        <v>1788.521</v>
       </c>
       <c r="D8" t="n">
         <v>9.34184e-08</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-1499.8</v>
+        <v>1766.023</v>
       </c>
       <c r="D9" t="n">
         <v>9.3349e-08</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-1482.93</v>
+        <v>1745.827</v>
       </c>
       <c r="D10" t="n">
         <v>9.32978e-08</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-1461.2</v>
+        <v>1732.728</v>
       </c>
       <c r="D11" t="n">
         <v>9.32597e-08</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-1458.27</v>
+        <v>1705.893</v>
       </c>
       <c r="D12" t="n">
         <v>9.31941e-08</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-1433.41</v>
+        <v>1698.88</v>
       </c>
       <c r="D13" t="n">
         <v>9.315040000000001e-08</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-1431.19</v>
+        <v>1672.98</v>
       </c>
       <c r="D14" t="n">
         <v>9.3097e-08</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-1424.93</v>
+        <v>1651.699</v>
       </c>
       <c r="D15" t="n">
         <v>9.30356e-08</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-1409.17</v>
+        <v>1640.956</v>
       </c>
       <c r="D16" t="n">
         <v>9.29782e-08</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-1397.98</v>
+        <v>1628.318</v>
       </c>
       <c r="D17" t="n">
         <v>9.29285e-08</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-1401.26</v>
+        <v>1598.847</v>
       </c>
       <c r="D18" t="n">
         <v>9.29393e-08</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-1391.67</v>
+        <v>1583.89</v>
       </c>
       <c r="D19" t="n">
         <v>9.289809999999999e-08</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-1376.68</v>
+        <v>1574.268</v>
       </c>
       <c r="D20" t="n">
         <v>9.28614e-08</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-1368.71</v>
+        <v>1560.491</v>
       </c>
       <c r="D21" t="n">
         <v>9.2822e-08</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-1363.06</v>
+        <v>1544.898</v>
       </c>
       <c r="D22" t="n">
         <v>9.27903e-08</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-2016.05</v>
+        <v>2510.091</v>
       </c>
       <c r="D2" t="n">
         <v>1.08446e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-1103.42</v>
+        <v>2098.634</v>
       </c>
       <c r="D3" t="n">
         <v>1.06218e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-826.1200000000003</v>
+        <v>1996.765</v>
       </c>
       <c r="D4" t="n">
         <v>1.04858e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-699.6199999999999</v>
+        <v>1939.945</v>
       </c>
       <c r="D5" t="n">
         <v>1.04557e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-620.5699999999997</v>
+        <v>1902.441</v>
       </c>
       <c r="D6" t="n">
         <v>1.04766e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-563.77</v>
+        <v>1878.83</v>
       </c>
       <c r="D7" t="n">
         <v>1.05223e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-532.4699999999998</v>
+        <v>1840.52</v>
       </c>
       <c r="D8" t="n">
         <v>1.05818e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-516.5599999999999</v>
+        <v>1795.989</v>
       </c>
       <c r="D9" t="n">
         <v>1.0646e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-491.98</v>
+        <v>1770.163</v>
       </c>
       <c r="D10" t="n">
         <v>1.07121e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-468.5299999999997</v>
+        <v>1745.434</v>
       </c>
       <c r="D11" t="n">
         <v>1.07777e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-950.79</v>
+        <v>2112.176</v>
       </c>
       <c r="D2" t="n">
         <v>1.12216e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-620.2600000000002</v>
+        <v>1985.796</v>
       </c>
       <c r="D3" t="n">
         <v>1.08974e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-566.3900000000003</v>
+        <v>1948.864</v>
       </c>
       <c r="D4" t="n">
         <v>1.08961e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-558.3699999999999</v>
+        <v>1910.186</v>
       </c>
       <c r="D5" t="n">
         <v>1.09131e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-528.4299999999998</v>
+        <v>1896.16</v>
       </c>
       <c r="D6" t="n">
         <v>1.09354e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-528.8499999999999</v>
+        <v>1856.954</v>
       </c>
       <c r="D7" t="n">
         <v>1.09563e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-517.3899999999999</v>
+        <v>1835.395</v>
       </c>
       <c r="D8" t="n">
         <v>1.09764e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-507.4299999999998</v>
+        <v>1809.848</v>
       </c>
       <c r="D9" t="n">
         <v>1.09962e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-495.8699999999999</v>
+        <v>1791.046</v>
       </c>
       <c r="D10" t="n">
         <v>1.10124e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-489.21</v>
+        <v>1769.216</v>
       </c>
       <c r="D11" t="n">
         <v>1.10288e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-489.3200000000002</v>
+        <v>1740.558</v>
       </c>
       <c r="D12" t="n">
         <v>1.10439e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-467.8599999999997</v>
+        <v>1734.149</v>
       </c>
       <c r="D13" t="n">
         <v>1.10574e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-468.1500000000001</v>
+        <v>1709.272</v>
       </c>
       <c r="D14" t="n">
         <v>1.1071e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-468.6100000000001</v>
+        <v>1684.773</v>
       </c>
       <c r="D15" t="n">
         <v>1.10818e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-468.04</v>
+        <v>1658.788</v>
       </c>
       <c r="D16" t="n">
         <v>1.1093e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-454.04</v>
+        <v>1648.323</v>
       </c>
       <c r="D17" t="n">
         <v>1.11052e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-454.0500000000002</v>
+        <v>1625.911</v>
       </c>
       <c r="D18" t="n">
         <v>1.11142e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-436.71</v>
+        <v>1620.467</v>
       </c>
       <c r="D19" t="n">
         <v>1.11242e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-437.52</v>
+        <v>1596.118</v>
       </c>
       <c r="D20" t="n">
         <v>1.11353e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-436.5900000000001</v>
+        <v>1572.444</v>
       </c>
       <c r="D21" t="n">
         <v>1.11442e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-427.9099999999999</v>
+        <v>1560.63</v>
       </c>
       <c r="D22" t="n">
         <v>1.11541e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1292.42</v>
+        <v>2017.191</v>
       </c>
       <c r="D2" t="n">
         <v>1.16473e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-681.1700000000001</v>
+        <v>1667.076</v>
       </c>
       <c r="D3" t="n">
         <v>1.14144e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-550.4900000000002</v>
+        <v>1580.666</v>
       </c>
       <c r="D4" t="n">
         <v>1.13888e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-508.9000000000001</v>
+        <v>1531.566</v>
       </c>
       <c r="D5" t="n">
         <v>1.14279e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-482.0499999999997</v>
+        <v>1503.591</v>
       </c>
       <c r="D6" t="n">
         <v>1.14852e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-469.2599999999998</v>
+        <v>1476.514</v>
       </c>
       <c r="D7" t="n">
         <v>1.15459e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-459.7599999999998</v>
+        <v>1447.647</v>
       </c>
       <c r="D8" t="n">
         <v>1.16084e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-450.6699999999998</v>
+        <v>1425.852</v>
       </c>
       <c r="D9" t="n">
         <v>1.16684e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-451.1799999999998</v>
+        <v>1398.577</v>
       </c>
       <c r="D10" t="n">
         <v>1.17275e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-457.0500000000002</v>
+        <v>1366.599</v>
       </c>
       <c r="D11" t="n">
         <v>1.17853e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>2259.073</v>
       </c>
+      <c r="C2" t="n">
+        <v>2737.204568016487</v>
+      </c>
       <c r="D2" t="n">
         <v>1.28197e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>2158.171</v>
       </c>
+      <c r="C3" t="n">
+        <v>2673.615371588079</v>
+      </c>
       <c r="D3" t="n">
         <v>1.28059e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>2080.076</v>
       </c>
+      <c r="C4" t="n">
+        <v>2595.99910736146</v>
+      </c>
       <c r="D4" t="n">
         <v>1.28295e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>2034.017</v>
       </c>
+      <c r="C5" t="n">
+        <v>2547.548074709418</v>
+      </c>
       <c r="D5" t="n">
         <v>1.28391e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1980.094</v>
       </c>
+      <c r="C6" t="n">
+        <v>2498.931155751699</v>
+      </c>
       <c r="D6" t="n">
         <v>1.28426e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1944.416</v>
       </c>
+      <c r="C7" t="n">
+        <v>2460.527627342516</v>
+      </c>
       <c r="D7" t="n">
         <v>1.28414e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1912.142</v>
       </c>
+      <c r="C8" t="n">
+        <v>2429.129771980478</v>
+      </c>
       <c r="D8" t="n">
         <v>1.28377e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1873.944</v>
       </c>
+      <c r="C9" t="n">
+        <v>2395.727308482092</v>
+      </c>
       <c r="D9" t="n">
         <v>1.28335e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1856.957</v>
       </c>
+      <c r="C10" t="n">
+        <v>2377.178508903994</v>
+      </c>
       <c r="D10" t="n">
         <v>1.28267e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1832.666</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2355.036861733116</v>
       </c>
       <c r="D11" t="n">
         <v>1.28177e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>2095.015</v>
       </c>
+      <c r="C2" t="n">
+        <v>2653.830178243172</v>
+      </c>
       <c r="D2" t="n">
         <v>1.14588e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1942.56</v>
       </c>
+      <c r="C3" t="n">
+        <v>2468.339744291992</v>
+      </c>
       <c r="D3" t="n">
         <v>1.15266e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1912.647</v>
       </c>
+      <c r="C4" t="n">
+        <v>2433.510478143692</v>
+      </c>
       <c r="D4" t="n">
         <v>1.15732e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1878.785</v>
       </c>
+      <c r="C5" t="n">
+        <v>2400.576141941989</v>
+      </c>
       <c r="D5" t="n">
         <v>1.16052e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1850.33</v>
       </c>
+      <c r="C6" t="n">
+        <v>2373.502163538838</v>
+      </c>
       <c r="D6" t="n">
         <v>1.16273e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1827.594</v>
       </c>
+      <c r="C7" t="n">
+        <v>2352.211198509247</v>
+      </c>
       <c r="D7" t="n">
         <v>1.16474e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1809.308</v>
       </c>
+      <c r="C8" t="n">
+        <v>2332.285033345474</v>
+      </c>
       <c r="D8" t="n">
         <v>1.16627e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1786.477</v>
       </c>
+      <c r="C9" t="n">
+        <v>2311.393842149942</v>
+      </c>
       <c r="D9" t="n">
         <v>1.16757e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1773.525</v>
       </c>
+      <c r="C10" t="n">
+        <v>2299.6437378789</v>
+      </c>
       <c r="D10" t="n">
         <v>1.16893e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1759.778</v>
       </c>
+      <c r="C11" t="n">
+        <v>2282.017956872544</v>
+      </c>
       <c r="D11" t="n">
         <v>1.16993e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1726.409</v>
       </c>
+      <c r="C12" t="n">
+        <v>2254.773089584517</v>
+      </c>
       <c r="D12" t="n">
         <v>1.171e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1717.154</v>
       </c>
+      <c r="C13" t="n">
+        <v>2241.97129360705</v>
+      </c>
       <c r="D13" t="n">
         <v>1.17173e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1695.56</v>
       </c>
+      <c r="C14" t="n">
+        <v>2220.635126055425</v>
+      </c>
       <c r="D14" t="n">
         <v>1.17268e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1678.577</v>
       </c>
+      <c r="C15" t="n">
+        <v>2205.31762078929</v>
+      </c>
       <c r="D15" t="n">
         <v>1.17331e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1662.797</v>
       </c>
+      <c r="C16" t="n">
+        <v>2188.256044263023</v>
+      </c>
       <c r="D16" t="n">
         <v>1.17404e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1651.177</v>
       </c>
+      <c r="C17" t="n">
+        <v>2173.662716564894</v>
+      </c>
       <c r="D17" t="n">
         <v>1.17489e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1645.527</v>
       </c>
+      <c r="C18" t="n">
+        <v>2167.750450429463</v>
+      </c>
       <c r="D18" t="n">
         <v>1.17559e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1624.622</v>
       </c>
+      <c r="C19" t="n">
+        <v>2146.869857994082</v>
+      </c>
       <c r="D19" t="n">
         <v>1.17626e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1611.732</v>
       </c>
+      <c r="C20" t="n">
+        <v>2131.045968340379</v>
+      </c>
       <c r="D20" t="n">
         <v>1.17692e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1587.974</v>
       </c>
+      <c r="C21" t="n">
+        <v>2109.050045968724</v>
+      </c>
       <c r="D21" t="n">
         <v>1.17784e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1571.216</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2092.650304818193</v>
       </c>
       <c r="D22" t="n">
         <v>1.17848e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>2016.385</v>
       </c>
+      <c r="C2" t="n">
+        <v>2529.108098358644</v>
+      </c>
       <c r="D2" t="n">
         <v>1.28058e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>2000.103</v>
       </c>
+      <c r="C3" t="n">
+        <v>2509.495350729504</v>
+      </c>
       <c r="D3" t="n">
         <v>1.27829e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1970.804</v>
       </c>
+      <c r="C4" t="n">
+        <v>2484.183362577231</v>
+      </c>
       <c r="D4" t="n">
         <v>1.27668e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1940.552</v>
       </c>
+      <c r="C5" t="n">
+        <v>2458.748350015393</v>
+      </c>
       <c r="D5" t="n">
         <v>1.27571e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1928.491</v>
       </c>
+      <c r="C6" t="n">
+        <v>2446.685572855496</v>
+      </c>
       <c r="D6" t="n">
         <v>1.27539e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1888.034</v>
       </c>
+      <c r="C7" t="n">
+        <v>2410.416230257163</v>
+      </c>
       <c r="D7" t="n">
         <v>1.27534e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1866.716</v>
       </c>
+      <c r="C8" t="n">
+        <v>2388.374131060866</v>
+      </c>
       <c r="D8" t="n">
         <v>1.27533e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1841.636</v>
       </c>
+      <c r="C9" t="n">
+        <v>2365.806134527517</v>
+      </c>
       <c r="D9" t="n">
         <v>1.27576e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1819.354</v>
       </c>
+      <c r="C10" t="n">
+        <v>2345.158709162702</v>
+      </c>
       <c r="D10" t="n">
         <v>1.27601e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1799.848</v>
       </c>
+      <c r="C11" t="n">
+        <v>2321.225245743022</v>
+      </c>
       <c r="D11" t="n">
         <v>1.27635e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1776.233</v>
       </c>
+      <c r="C12" t="n">
+        <v>2301.424313041855</v>
+      </c>
       <c r="D12" t="n">
         <v>1.27662e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1750.01</v>
       </c>
+      <c r="C13" t="n">
+        <v>2276.968651658749</v>
+      </c>
       <c r="D13" t="n">
         <v>1.27724e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1743.236</v>
       </c>
+      <c r="C14" t="n">
+        <v>2267.761264769534</v>
+      </c>
       <c r="D14" t="n">
         <v>1.27747e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1717.85</v>
       </c>
+      <c r="C15" t="n">
+        <v>2244.386298297491</v>
+      </c>
       <c r="D15" t="n">
         <v>1.27769e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1702.134</v>
       </c>
+      <c r="C16" t="n">
+        <v>2227.984849847014</v>
+      </c>
       <c r="D16" t="n">
         <v>1.27797e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1685.086</v>
       </c>
+      <c r="C17" t="n">
+        <v>2210.55276866756</v>
+      </c>
       <c r="D17" t="n">
         <v>1.27819e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1664.727</v>
       </c>
+      <c r="C18" t="n">
+        <v>2189.417003654582</v>
+      </c>
       <c r="D18" t="n">
         <v>1.27815e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1643.39</v>
       </c>
+      <c r="C19" t="n">
+        <v>2167.522760731434</v>
+      </c>
       <c r="D19" t="n">
         <v>1.27844e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1634.587</v>
       </c>
+      <c r="C20" t="n">
+        <v>2157.365698893936</v>
+      </c>
       <c r="D20" t="n">
         <v>1.27864e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1622.423</v>
       </c>
+      <c r="C21" t="n">
+        <v>2145.237698154854</v>
+      </c>
       <c r="D21" t="n">
         <v>1.27859e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1611.734</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2135.360716424424</v>
       </c>
       <c r="D22" t="n">
         <v>1.27857e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2497.835</v>
       </c>
+      <c r="C2" t="n">
+        <v>3101.457016487561</v>
+      </c>
       <c r="D2" t="n">
         <v>1.24795e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>2127.574</v>
       </c>
+      <c r="C3" t="n">
+        <v>2626.677057480019</v>
+      </c>
       <c r="D3" t="n">
         <v>1.27591e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>2029.177</v>
       </c>
+      <c r="C4" t="n">
+        <v>2519.66992804949</v>
+      </c>
       <c r="D4" t="n">
         <v>1.27491e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1985.279</v>
       </c>
+      <c r="C5" t="n">
+        <v>2477.050271209985</v>
+      </c>
       <c r="D5" t="n">
         <v>1.27115e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1948.283</v>
       </c>
+      <c r="C6" t="n">
+        <v>2440.467423411923</v>
+      </c>
       <c r="D6" t="n">
         <v>1.26829e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1931.672</v>
       </c>
+      <c r="C7" t="n">
+        <v>2424.14597022872</v>
+      </c>
       <c r="D7" t="n">
         <v>1.26654e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1893.567</v>
       </c>
+      <c r="C8" t="n">
+        <v>2389.946580817895</v>
+      </c>
       <c r="D8" t="n">
         <v>1.26435e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1851.347</v>
       </c>
+      <c r="C9" t="n">
+        <v>2352.253082092855</v>
+      </c>
       <c r="D9" t="n">
         <v>1.26406e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1839.816</v>
       </c>
+      <c r="C10" t="n">
+        <v>2338.231980096235</v>
+      </c>
       <c r="D10" t="n">
         <v>1.26383e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1806.465</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2306.375795148223</v>
       </c>
       <c r="D11" t="n">
         <v>1.2639e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1899.203</v>
       </c>
+      <c r="C2" t="n">
+        <v>2437.063589207194</v>
+      </c>
       <c r="D2" t="n">
         <v>1.30997e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1850.708</v>
       </c>
+      <c r="C3" t="n">
+        <v>2395.318199220897</v>
+      </c>
       <c r="D3" t="n">
         <v>1.26476e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1829.823</v>
       </c>
+      <c r="C4" t="n">
+        <v>2372.93897456787</v>
+      </c>
       <c r="D4" t="n">
         <v>1.22903e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1766.049</v>
       </c>
+      <c r="C5" t="n">
+        <v>2315.056761216935</v>
+      </c>
       <c r="D5" t="n">
         <v>1.20005e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1732.083</v>
       </c>
+      <c r="C6" t="n">
+        <v>2280.727595592389</v>
+      </c>
       <c r="D6" t="n">
         <v>1.17614e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1709.977</v>
       </c>
+      <c r="C7" t="n">
+        <v>2258.922952348992</v>
+      </c>
       <c r="D7" t="n">
         <v>1.15564e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1678.77</v>
       </c>
+      <c r="C8" t="n">
+        <v>2226.805883863057</v>
+      </c>
       <c r="D8" t="n">
         <v>1.1381e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1643.45</v>
       </c>
+      <c r="C9" t="n">
+        <v>2192.020909975792</v>
+      </c>
       <c r="D9" t="n">
         <v>1.12286e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1617.987</v>
       </c>
+      <c r="C10" t="n">
+        <v>2166.517337949469</v>
+      </c>
       <c r="D10" t="n">
         <v>1.10946e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1585.458</v>
       </c>
+      <c r="C11" t="n">
+        <v>2135.751111984242</v>
+      </c>
       <c r="D11" t="n">
         <v>1.09743e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1565.023</v>
       </c>
+      <c r="C12" t="n">
+        <v>2114.970652935471</v>
+      </c>
       <c r="D12" t="n">
         <v>1.08665e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1544.104</v>
       </c>
+      <c r="C13" t="n">
+        <v>2094.107567264193</v>
+      </c>
       <c r="D13" t="n">
         <v>1.07698e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1533.734</v>
       </c>
+      <c r="C14" t="n">
+        <v>2082.268927094585</v>
+      </c>
       <c r="D14" t="n">
         <v>1.0681e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1509.959</v>
       </c>
+      <c r="C15" t="n">
+        <v>2058.74355658138</v>
+      </c>
       <c r="D15" t="n">
         <v>1.06005e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1491.532</v>
       </c>
+      <c r="C16" t="n">
+        <v>2037.547303207411</v>
+      </c>
       <c r="D16" t="n">
         <v>1.05279e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1481.609</v>
       </c>
+      <c r="C17" t="n">
+        <v>2029.148504717127</v>
+      </c>
       <c r="D17" t="n">
         <v>1.04601e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1459.053</v>
       </c>
+      <c r="C18" t="n">
+        <v>2003.617269168306</v>
+      </c>
       <c r="D18" t="n">
         <v>1.03995e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1451.259</v>
       </c>
+      <c r="C19" t="n">
+        <v>1994.325227977113</v>
+      </c>
       <c r="D19" t="n">
         <v>1.03445e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1428.427</v>
       </c>
+      <c r="C20" t="n">
+        <v>1971.297109025651</v>
+      </c>
       <c r="D20" t="n">
         <v>1.0294e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1422.202</v>
       </c>
+      <c r="C21" t="n">
+        <v>1963.708510993314</v>
+      </c>
       <c r="D21" t="n">
         <v>1.02476e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1421.031</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1961.57784968433</v>
       </c>
       <c r="D22" t="n">
         <v>1.02064e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2633.046</v>
       </c>
+      <c r="C2" t="n">
+        <v>3349.077160161025</v>
+      </c>
       <c r="D2" t="n">
         <v>1.06066e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>2117.304</v>
       </c>
+      <c r="C3" t="n">
+        <v>2675.870534502791</v>
+      </c>
       <c r="D3" t="n">
         <v>1.06208e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>2005.532</v>
       </c>
+      <c r="C4" t="n">
+        <v>2539.621795077327</v>
+      </c>
       <c r="D4" t="n">
         <v>1.04516e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1958.687</v>
       </c>
+      <c r="C5" t="n">
+        <v>2490.939530569168</v>
+      </c>
       <c r="D5" t="n">
         <v>1.03513e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1926.158</v>
       </c>
+      <c r="C6" t="n">
+        <v>2460.599200454154</v>
+      </c>
       <c r="D6" t="n">
         <v>1.03004e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1904.402</v>
       </c>
+      <c r="C7" t="n">
+        <v>2437.064580740244</v>
+      </c>
       <c r="D7" t="n">
         <v>1.02787e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1874.635</v>
       </c>
+      <c r="C8" t="n">
+        <v>2409.878441143315</v>
+      </c>
       <c r="D8" t="n">
         <v>1.02807e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1830.542</v>
       </c>
+      <c r="C9" t="n">
+        <v>2370.094703201135</v>
+      </c>
       <c r="D9" t="n">
         <v>1.02836e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1809.123</v>
       </c>
+      <c r="C10" t="n">
+        <v>2348.140824974512</v>
+      </c>
       <c r="D10" t="n">
         <v>1.02979e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1784.224</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2321.899666524001</v>
       </c>
       <c r="D11" t="n">
         <v>1.03194e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1998.283</v>
       </c>
+      <c r="C2" t="n">
+        <v>2609.749532206438</v>
+      </c>
       <c r="D2" t="n">
         <v>9.57842e-08</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1933.762</v>
       </c>
+      <c r="C3" t="n">
+        <v>2535.750867092748</v>
+      </c>
       <c r="D3" t="n">
         <v>9.448459999999999e-08</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1906.504</v>
       </c>
+      <c r="C4" t="n">
+        <v>2505.172487100484</v>
+      </c>
       <c r="D4" t="n">
         <v>9.401880000000001e-08</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1879.386</v>
       </c>
+      <c r="C5" t="n">
+        <v>2477.524192916896</v>
+      </c>
       <c r="D5" t="n">
         <v>9.375e-08</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1846.948</v>
       </c>
+      <c r="C6" t="n">
+        <v>2443.140598917219</v>
+      </c>
       <c r="D6" t="n">
         <v>9.35872e-08</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1820.943</v>
       </c>
+      <c r="C7" t="n">
+        <v>2417.766276408986</v>
+      </c>
       <c r="D7" t="n">
         <v>9.35006e-08</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1788.521</v>
       </c>
+      <c r="C8" t="n">
+        <v>2386.647806149538</v>
+      </c>
       <c r="D8" t="n">
         <v>9.34184e-08</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1766.023</v>
       </c>
+      <c r="C9" t="n">
+        <v>2361.761640671337</v>
+      </c>
       <c r="D9" t="n">
         <v>9.3349e-08</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1745.827</v>
       </c>
+      <c r="C10" t="n">
+        <v>2338.904227814165</v>
+      </c>
       <c r="D10" t="n">
         <v>9.32978e-08</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1732.728</v>
       </c>
+      <c r="C11" t="n">
+        <v>2326.964628918777</v>
+      </c>
       <c r="D11" t="n">
         <v>9.32597e-08</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1705.893</v>
       </c>
+      <c r="C12" t="n">
+        <v>2298.586679628752</v>
+      </c>
       <c r="D12" t="n">
         <v>9.31941e-08</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1698.88</v>
       </c>
+      <c r="C13" t="n">
+        <v>2286.94746927609</v>
+      </c>
       <c r="D13" t="n">
         <v>9.315040000000001e-08</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1672.98</v>
       </c>
+      <c r="C14" t="n">
+        <v>2264.5078578872</v>
+      </c>
       <c r="D14" t="n">
         <v>9.3097e-08</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1651.699</v>
       </c>
+      <c r="C15" t="n">
+        <v>2241.74618998098</v>
+      </c>
       <c r="D15" t="n">
         <v>9.30356e-08</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1640.956</v>
       </c>
+      <c r="C16" t="n">
+        <v>2233.371025059165</v>
+      </c>
       <c r="D16" t="n">
         <v>9.29782e-08</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1628.318</v>
       </c>
+      <c r="C17" t="n">
+        <v>2215.944754939125</v>
+      </c>
       <c r="D17" t="n">
         <v>9.29285e-08</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1598.847</v>
       </c>
+      <c r="C18" t="n">
+        <v>2186.010053814247</v>
+      </c>
       <c r="D18" t="n">
         <v>9.29393e-08</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1583.89</v>
       </c>
+      <c r="C19" t="n">
+        <v>2170.288928138759</v>
+      </c>
       <c r="D19" t="n">
         <v>9.289809999999999e-08</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1574.268</v>
       </c>
+      <c r="C20" t="n">
+        <v>2161.993093956314</v>
+      </c>
       <c r="D20" t="n">
         <v>9.28614e-08</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1560.491</v>
       </c>
+      <c r="C21" t="n">
+        <v>2146.35367951369</v>
+      </c>
       <c r="D21" t="n">
         <v>9.2822e-08</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1544.898</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2129.900848163467</v>
       </c>
       <c r="D22" t="n">
         <v>9.27903e-08</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>2510.091</v>
       </c>
+      <c r="C2" t="n">
+        <v>3179.935435741775</v>
+      </c>
       <c r="D2" t="n">
         <v>1.08446e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>2098.634</v>
       </c>
+      <c r="C3" t="n">
+        <v>2647.917342657336</v>
+      </c>
       <c r="D3" t="n">
         <v>1.06218e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1996.765</v>
       </c>
+      <c r="C4" t="n">
+        <v>2525.975243306968</v>
+      </c>
       <c r="D4" t="n">
         <v>1.04858e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1939.945</v>
       </c>
+      <c r="C5" t="n">
+        <v>2470.761785737807</v>
+      </c>
       <c r="D5" t="n">
         <v>1.04557e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1902.441</v>
       </c>
+      <c r="C6" t="n">
+        <v>2433.085214393198</v>
+      </c>
       <c r="D6" t="n">
         <v>1.04766e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1878.83</v>
       </c>
+      <c r="C7" t="n">
+        <v>2405.713821949396</v>
+      </c>
       <c r="D7" t="n">
         <v>1.05223e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1840.52</v>
       </c>
+      <c r="C8" t="n">
+        <v>2370.561692558135</v>
+      </c>
       <c r="D8" t="n">
         <v>1.05818e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1795.989</v>
       </c>
+      <c r="C9" t="n">
+        <v>2329.52965194358</v>
+      </c>
       <c r="D9" t="n">
         <v>1.0646e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1770.163</v>
       </c>
+      <c r="C10" t="n">
+        <v>2305.340557903121</v>
+      </c>
       <c r="D10" t="n">
         <v>1.07121e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1745.434</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2276.675572452849</v>
       </c>
       <c r="D11" t="n">
         <v>1.07777e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>2112.176</v>
       </c>
+      <c r="C2" t="n">
+        <v>2676.833218541219</v>
+      </c>
       <c r="D2" t="n">
         <v>1.12216e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1985.796</v>
       </c>
+      <c r="C3" t="n">
+        <v>2505.154279492478</v>
+      </c>
       <c r="D3" t="n">
         <v>1.08974e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1948.864</v>
       </c>
+      <c r="C4" t="n">
+        <v>2465.058996613096</v>
+      </c>
       <c r="D4" t="n">
         <v>1.08961e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1910.186</v>
       </c>
+      <c r="C5" t="n">
+        <v>2426.991163628215</v>
+      </c>
       <c r="D5" t="n">
         <v>1.09131e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1896.16</v>
       </c>
+      <c r="C6" t="n">
+        <v>2412.543164739458</v>
+      </c>
       <c r="D6" t="n">
         <v>1.09354e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1856.954</v>
       </c>
+      <c r="C7" t="n">
+        <v>2377.014580914495</v>
+      </c>
       <c r="D7" t="n">
         <v>1.09563e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1835.395</v>
       </c>
+      <c r="C8" t="n">
+        <v>2354.003238828874</v>
+      </c>
       <c r="D8" t="n">
         <v>1.09764e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1809.848</v>
       </c>
+      <c r="C9" t="n">
+        <v>2330.767290842011</v>
+      </c>
       <c r="D9" t="n">
         <v>1.09962e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1791.046</v>
       </c>
+      <c r="C10" t="n">
+        <v>2309.966423309326</v>
+      </c>
       <c r="D10" t="n">
         <v>1.10124e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1769.216</v>
       </c>
+      <c r="C11" t="n">
+        <v>2286.98592403186</v>
+      </c>
       <c r="D11" t="n">
         <v>1.10288e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1740.558</v>
       </c>
+      <c r="C12" t="n">
+        <v>2262.255793341577</v>
+      </c>
       <c r="D12" t="n">
         <v>1.10439e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1734.149</v>
       </c>
+      <c r="C13" t="n">
+        <v>2252.593786169768</v>
+      </c>
       <c r="D13" t="n">
         <v>1.10574e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1709.272</v>
       </c>
+      <c r="C14" t="n">
+        <v>2227.965710072302</v>
+      </c>
       <c r="D14" t="n">
         <v>1.1071e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1684.773</v>
       </c>
+      <c r="C15" t="n">
+        <v>2203.621226033896</v>
+      </c>
       <c r="D15" t="n">
         <v>1.10818e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1658.788</v>
       </c>
+      <c r="C16" t="n">
+        <v>2180.191682556604</v>
+      </c>
       <c r="D16" t="n">
         <v>1.1093e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1648.323</v>
       </c>
+      <c r="C17" t="n">
+        <v>2168.464510905446</v>
+      </c>
       <c r="D17" t="n">
         <v>1.11052e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1625.911</v>
       </c>
+      <c r="C18" t="n">
+        <v>2144.902947232851</v>
+      </c>
       <c r="D18" t="n">
         <v>1.11142e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1620.467</v>
       </c>
+      <c r="C19" t="n">
+        <v>2137.063308750487</v>
+      </c>
       <c r="D19" t="n">
         <v>1.11242e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1596.118</v>
       </c>
+      <c r="C20" t="n">
+        <v>2113.07548591261</v>
+      </c>
       <c r="D20" t="n">
         <v>1.11353e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1572.444</v>
       </c>
+      <c r="C21" t="n">
+        <v>2088.868635983094</v>
+      </c>
       <c r="D21" t="n">
         <v>1.11442e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1560.63</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2076.792040826372</v>
       </c>
       <c r="D22" t="n">
         <v>1.11541e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>2017.191</v>
       </c>
+      <c r="C2" t="n">
+        <v>2720.279869822423</v>
+      </c>
       <c r="D2" t="n">
         <v>1.16473e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1667.076</v>
       </c>
+      <c r="C3" t="n">
+        <v>2241.085947405102</v>
+      </c>
       <c r="D3" t="n">
         <v>1.14144e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1580.666</v>
       </c>
+      <c r="C4" t="n">
+        <v>2133.303863530242</v>
+      </c>
       <c r="D4" t="n">
         <v>1.13888e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1531.566</v>
       </c>
+      <c r="C5" t="n">
+        <v>2081.772786703304</v>
+      </c>
       <c r="D5" t="n">
         <v>1.14279e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1503.591</v>
       </c>
+      <c r="C6" t="n">
+        <v>2056.82922271536</v>
+      </c>
       <c r="D6" t="n">
         <v>1.14852e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1476.514</v>
       </c>
+      <c r="C7" t="n">
+        <v>2030.289428252323</v>
+      </c>
       <c r="D7" t="n">
         <v>1.15459e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1447.647</v>
       </c>
+      <c r="C8" t="n">
+        <v>1999.942728815724</v>
+      </c>
       <c r="D8" t="n">
         <v>1.16084e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1425.852</v>
       </c>
+      <c r="C9" t="n">
+        <v>1979.873648187591</v>
+      </c>
       <c r="D9" t="n">
         <v>1.16684e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1398.577</v>
       </c>
+      <c r="C10" t="n">
+        <v>1955.691108775599</v>
+      </c>
       <c r="D10" t="n">
         <v>1.17275e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1366.599</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1919.712531078129</v>
       </c>
       <c r="D11" t="n">
         <v>1.17853e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -565,7 +565,7 @@
         <v>2259.073</v>
       </c>
       <c r="C2" t="n">
-        <v>2737.204568016487</v>
+        <v>1232.393282543155</v>
       </c>
       <c r="D2" t="n">
         <v>1.28197e-07</v>
@@ -598,16 +598,13 @@
         <v>-38132.8339456133</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.953906100490987e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3175.008692786096</v>
+        <v>352.5868019794945</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000023038e-08</v>
+        <v>1.956912679493394e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.814679482164695</v>
+        <v>0.9232540065170466</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>2158.171</v>
       </c>
       <c r="C3" t="n">
-        <v>2673.615371588079</v>
+        <v>1107.092657756392</v>
       </c>
       <c r="D3" t="n">
         <v>1.28059e-07</v>
@@ -651,16 +648,13 @@
         <v>-38156.19630627904</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.877106411401045e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3055.107758096767</v>
+        <v>363.524337554699</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>7.3278748026759e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8150082898075091</v>
+        <v>0.9913551570929755</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>2080.076</v>
       </c>
       <c r="C4" t="n">
-        <v>2595.99910736146</v>
+        <v>1060.558518500194</v>
       </c>
       <c r="D4" t="n">
         <v>1.28295e-07</v>
@@ -704,16 +698,13 @@
         <v>-38871.99816183687</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.386027534591969e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2963.698906734357</v>
+        <v>383.9920488451905</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000028e-08</v>
+        <v>7.190772231865826e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8152581892365701</v>
+        <v>0.9965979601836417</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>2034.017</v>
       </c>
       <c r="C5" t="n">
-        <v>2547.548074709418</v>
+        <v>1027.740300731219</v>
       </c>
       <c r="D5" t="n">
         <v>1.28391e-07</v>
@@ -757,16 +748,13 @@
         <v>-41102.28092246929</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.439713344369826e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2897.704904144261</v>
+        <v>443.9922907681711</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000372e-08</v>
+        <v>1.386588060516868e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8154826676393956</v>
+        <v>0.955054900459624</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>1980.094</v>
       </c>
       <c r="C6" t="n">
-        <v>2498.931155751699</v>
+        <v>999.9609419713607</v>
       </c>
       <c r="D6" t="n">
         <v>1.28426e-07</v>
@@ -810,16 +798,13 @@
         <v>-40036.46154239417</v>
       </c>
       <c r="Y6" t="n">
-        <v>78.53704790793282</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2969.482668111022</v>
+        <v>434.3639316608859</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.738751977367518e-08</v>
+        <v>7.867012260425984e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7789491904179999</v>
+        <v>0.9957056859435612</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>1944.416</v>
       </c>
       <c r="C7" t="n">
-        <v>2460.527627342516</v>
+        <v>978.9506565742718</v>
       </c>
       <c r="D7" t="n">
         <v>1.28414e-07</v>
@@ -863,16 +848,13 @@
         <v>-40428.37521305256</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.690695553711296e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2798.066878200266</v>
+        <v>444.8324304286526</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000041e-08</v>
+        <v>7.805111906083538e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8158937760381044</v>
+        <v>0.998617011725861</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1912.142</v>
       </c>
       <c r="C8" t="n">
-        <v>2429.129771980478</v>
+        <v>959.2365082549002</v>
       </c>
       <c r="D8" t="n">
         <v>1.28377e-07</v>
@@ -916,16 +898,13 @@
         <v>-40838.12123561982</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.931127353574814e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2757.72998409456</v>
+        <v>519.3742588042153</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>2.489692590638685e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8160969064026584</v>
+        <v>0.9286637468842003</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>1873.944</v>
       </c>
       <c r="C9" t="n">
-        <v>2395.727308482092</v>
+        <v>943.0271154830625</v>
       </c>
       <c r="D9" t="n">
         <v>1.28335e-07</v>
@@ -969,16 +948,13 @@
         <v>-39410.07518989902</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.473006236715822e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2722.957052516254</v>
+        <v>458.8089913595801</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>7.942998973273502e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8162903173407705</v>
+        <v>0.9985428634716336</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>1856.957</v>
       </c>
       <c r="C10" t="n">
-        <v>2377.178508903994</v>
+        <v>929.2929185222765</v>
       </c>
       <c r="D10" t="n">
         <v>1.28267e-07</v>
@@ -1022,16 +998,13 @@
         <v>-41322.73790030564</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.026810933974505e-07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2691.072347880301</v>
+        <v>467.4124477302229</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000084e-08</v>
+        <v>9.294221051305155e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8164823137323599</v>
+        <v>0.9952278742251215</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>1832.666</v>
       </c>
       <c r="C11" t="n">
-        <v>2355.036861733116</v>
+        <v>916.6689014825788</v>
       </c>
       <c r="D11" t="n">
         <v>1.28177e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-41430.59824245364</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.990645963012199e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2662.185686610608</v>
+        <v>461.99849071719</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.00000000008241e-08</v>
+        <v>8.479664772840902e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8166769811266618</v>
+        <v>0.9997148791616904</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>2095.015</v>
       </c>
       <c r="C2" t="n">
-        <v>2653.830178243172</v>
+        <v>1092.553979222853</v>
       </c>
       <c r="D2" t="n">
         <v>1.14588e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-42442.00844638641</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.446174346851953e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2957.310878308546</v>
+        <v>363.7638006652883</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000863e-08</v>
+        <v>7.660223700819083e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8157917288676616</v>
+        <v>0.9900420765569802</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1942.56</v>
       </c>
       <c r="C3" t="n">
-        <v>2468.339744291992</v>
+        <v>1014.219302913969</v>
       </c>
       <c r="D3" t="n">
         <v>1.15266e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-41747.8505701392</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.926645648633865e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2818.136109904397</v>
+        <v>409.6230561202353</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000002828e-08</v>
+        <v>7.911250952577943e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8160709004996413</v>
+        <v>0.9991892404007958</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1912.647</v>
       </c>
       <c r="C4" t="n">
-        <v>2433.510478143692</v>
+        <v>990.9353231264174</v>
       </c>
       <c r="D4" t="n">
         <v>1.15732e-07</v>
@@ -1380,16 +1344,13 @@
         <v>-44233.50237363524</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.611273692567308e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2770.499883988268</v>
+        <v>497.1118973661569</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001066e-08</v>
+        <v>2.278867385997983e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8161112397314851</v>
+        <v>0.933607542346568</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1878.785</v>
       </c>
       <c r="C5" t="n">
-        <v>2400.576141941989</v>
+        <v>974.6630856167343</v>
       </c>
       <c r="D5" t="n">
         <v>1.16052e-07</v>
@@ -1433,16 +1394,13 @@
         <v>-43419.10243874054</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.799116131230236e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2738.470783795171</v>
+        <v>452.9822415224775</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000125e-08</v>
+        <v>1.118678747583567e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8161415299526497</v>
+        <v>0.9756811219389371</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1411,7 @@
         <v>1850.33</v>
       </c>
       <c r="C6" t="n">
-        <v>2373.502163538838</v>
+        <v>960.8282750241763</v>
       </c>
       <c r="D6" t="n">
         <v>1.16273e-07</v>
@@ -1486,16 +1444,13 @@
         <v>-42499.25624233932</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.607870339666786e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2709.938762978423</v>
+        <v>455.195981177735</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000667272e-08</v>
+        <v>1.083471612825145e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8162417044935256</v>
+        <v>0.981171764474664</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1827.594</v>
       </c>
       <c r="C7" t="n">
-        <v>2352.211198509247</v>
+        <v>948.0058983600094</v>
       </c>
       <c r="D7" t="n">
         <v>1.16474e-07</v>
@@ -1539,16 +1494,13 @@
         <v>-42562.09660949936</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.368947295474501e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2682.490353294699</v>
+        <v>424.5184428632296</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>1.075920801520497e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8163743724006977</v>
+        <v>0.989677288033961</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1809.308</v>
       </c>
       <c r="C8" t="n">
-        <v>2332.285033345474</v>
+        <v>936.6167334517993</v>
       </c>
       <c r="D8" t="n">
         <v>1.16627e-07</v>
@@ -1592,16 +1544,13 @@
         <v>-42825.36712938253</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.365977579057178e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2656.665108107153</v>
+        <v>533.7268765577327</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.0000000000008e-08</v>
+        <v>2.939065452239495e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8165368433119899</v>
+        <v>0.9150293484748963</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1786.477</v>
       </c>
       <c r="C9" t="n">
-        <v>2311.393842149942</v>
+        <v>925.2058032534441</v>
       </c>
       <c r="D9" t="n">
         <v>1.16757e-07</v>
@@ -1645,16 +1594,13 @@
         <v>-42825.61654719553</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.427297575336334e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2631.534078467009</v>
+        <v>483.14702287337</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.508176562464623e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8167168904194366</v>
+        <v>0.9602135599563014</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1611,7 @@
         <v>1773.525</v>
       </c>
       <c r="C10" t="n">
-        <v>2299.6437378789</v>
+        <v>915.5670660430397</v>
       </c>
       <c r="D10" t="n">
         <v>1.16893e-07</v>
@@ -1698,16 +1644,13 @@
         <v>-43856.38023846823</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.690208246476083e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2608.156234797522</v>
+        <v>461.5303820158841</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.001862976507322e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8169165456261026</v>
+        <v>0.9888352224891277</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1759.778</v>
       </c>
       <c r="C11" t="n">
-        <v>2282.017956872544</v>
+        <v>905.7166746038662</v>
       </c>
       <c r="D11" t="n">
         <v>1.16993e-07</v>
@@ -1751,16 +1694,13 @@
         <v>-43927.05484160499</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.183236991163669e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2585.520217216732</v>
+        <v>459.3727799413625</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>8.521299251364101e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8171273304527732</v>
+        <v>0.9999443419359549</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1711,7 @@
         <v>1726.409</v>
       </c>
       <c r="C12" t="n">
-        <v>2254.773089584517</v>
+        <v>895.9054305020557</v>
       </c>
       <c r="D12" t="n">
         <v>1.171e-07</v>
@@ -1804,16 +1744,13 @@
         <v>-41567.38222781925</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.321865884620514e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2563.558732946935</v>
+        <v>461.4025619482946</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.00000000000115e-08</v>
+        <v>8.658056129394673e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8173456463765618</v>
+        <v>0.9994776413856772</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1761,7 @@
         <v>1717.154</v>
       </c>
       <c r="C13" t="n">
-        <v>2241.97129360705</v>
+        <v>886.9126623761074</v>
       </c>
       <c r="D13" t="n">
         <v>1.17173e-07</v>
@@ -1857,16 +1794,13 @@
         <v>-42825.60024840761</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.492375011082116e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2542.278840355799</v>
+        <v>465.4458232921396</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000045e-08</v>
+        <v>9.702290674999699e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8175839800948166</v>
+        <v>0.9913829505656294</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1811,7 @@
         <v>1695.56</v>
       </c>
       <c r="C14" t="n">
-        <v>2220.635126055425</v>
+        <v>878.3195790138514</v>
       </c>
       <c r="D14" t="n">
         <v>1.17268e-07</v>
@@ -1910,16 +1844,13 @@
         <v>-41759.59065945874</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.961145902892358e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2521.254784654522</v>
+        <v>445.2898388835629</v>
       </c>
       <c r="AA14" t="n">
-        <v>1e-08</v>
+        <v>8.144151209392884e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8178274353645306</v>
+        <v>0.9995143771197079</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1678.577</v>
       </c>
       <c r="C15" t="n">
-        <v>2205.31762078929</v>
+        <v>870.0090420491854</v>
       </c>
       <c r="D15" t="n">
         <v>1.17331e-07</v>
@@ -1963,16 +1894,13 @@
         <v>-41655.71686141488</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.374557051954847e-07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2500.248698783896</v>
+        <v>454.3964771846345</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000013e-08</v>
+        <v>1.141152143439862e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8180875736245282</v>
+        <v>0.9876661537040088</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1911,7 @@
         <v>1662.797</v>
       </c>
       <c r="C16" t="n">
-        <v>2188.256044263023</v>
+        <v>861.1541502883598</v>
       </c>
       <c r="D16" t="n">
         <v>1.17404e-07</v>
@@ -2016,16 +1944,13 @@
         <v>-41731.68655746619</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.00188860235249e-07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2479.724872045197</v>
+        <v>491.8421759039037</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000011e-08</v>
+        <v>1.534697401977956e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.818339884569883</v>
+        <v>0.9651961852415273</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1961,7 @@
         <v>1651.177</v>
       </c>
       <c r="C17" t="n">
-        <v>2173.662716564894</v>
+        <v>852.9603515904247</v>
       </c>
       <c r="D17" t="n">
         <v>1.17489e-07</v>
@@ -2069,16 +1994,13 @@
         <v>-41939.70817145566</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.547185666435741e-07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2459.630766855817</v>
+        <v>551.7803846485306</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000038e-08</v>
+        <v>3.97201634501209e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8185987080568147</v>
+        <v>0.9048817477395126</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2011,7 @@
         <v>1645.527</v>
       </c>
       <c r="C18" t="n">
-        <v>2167.750450429463</v>
+        <v>844.2462676694129</v>
       </c>
       <c r="D18" t="n">
         <v>1.17559e-07</v>
@@ -2122,16 +2044,13 @@
         <v>-44235.07464291344</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.065801067077589e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2439.037013680881</v>
+        <v>484.6054762523087</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000028196e-08</v>
+        <v>1.267556005851139e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8188696057591242</v>
+        <v>0.9784689442965101</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2061,7 @@
         <v>1624.622</v>
       </c>
       <c r="C19" t="n">
-        <v>2146.869857994082</v>
+        <v>835.9953573952306</v>
       </c>
       <c r="D19" t="n">
         <v>1.17626e-07</v>
@@ -2175,16 +2094,13 @@
         <v>-42958.58507308229</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.697536725218422e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2418.007745563672</v>
+        <v>485.3783498347032</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>1.161654306189516e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8191409326258356</v>
+        <v>0.986709024606343</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1611.732</v>
       </c>
       <c r="C20" t="n">
-        <v>2131.045968340379</v>
+        <v>828.0029170481298</v>
       </c>
       <c r="D20" t="n">
         <v>1.17692e-07</v>
@@ -2228,16 +2144,13 @@
         <v>-43110.92731383773</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.498804900438821e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2397.833093734187</v>
+        <v>481.7972454021082</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000001034516e-08</v>
+        <v>1.135010021183098e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8194210955129446</v>
+        <v>0.9888472694613175</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1587.974</v>
       </c>
       <c r="C21" t="n">
-        <v>2109.050045968724</v>
+        <v>820.1197987838347</v>
       </c>
       <c r="D21" t="n">
         <v>1.17784e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-41981.28002095004</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.108808720553675e-11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2376.986127538287</v>
+        <v>476.1438519286119</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>9.996063454527409e-10</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8197060794426098</v>
+        <v>0.9991864865607923</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1571.216</v>
       </c>
       <c r="C22" t="n">
-        <v>2092.650304818193</v>
+        <v>812.1830372934749</v>
       </c>
       <c r="D22" t="n">
         <v>1.17848e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-41898.68804860903</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.663823310436081e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2355.811891586343</v>
+        <v>484.5118893305717</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.027524595096914e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8200016120837688</v>
+        <v>0.9972139835726811</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>2016.385</v>
       </c>
       <c r="C2" t="n">
-        <v>2529.108098358644</v>
+        <v>1028.015726977752</v>
       </c>
       <c r="D2" t="n">
         <v>1.28058e-07</v>
@@ -2533,16 +2440,13 @@
         <v>-39134.88641109465</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.346201584347315e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2888.025421322149</v>
+        <v>405.2352847216167</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000033e-08</v>
+        <v>7.245043645074371e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8154757819674585</v>
+        <v>0.9929725434757872</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2457,7 @@
         <v>2000.103</v>
       </c>
       <c r="C3" t="n">
-        <v>2509.495350729504</v>
+        <v>1006.539915523826</v>
       </c>
       <c r="D3" t="n">
         <v>1.27829e-07</v>
@@ -2586,16 +2490,13 @@
         <v>-41876.94588019341</v>
       </c>
       <c r="Y3" t="n">
-        <v>83.75473117886415</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3022.27719712357</v>
+        <v>427.8653274766922</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.691142992723424e-08</v>
+        <v>7.226764534343846e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.780967023409491</v>
+        <v>0.9992159796646712</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>1970.804</v>
       </c>
       <c r="C4" t="n">
-        <v>2484.183362577231</v>
+        <v>991.7256567394596</v>
       </c>
       <c r="D4" t="n">
         <v>1.27668e-07</v>
@@ -2639,16 +2540,13 @@
         <v>-40550.86197859904</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.778305349677007e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2832.530158403174</v>
+        <v>448.4552874822233</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000075494e-08</v>
+        <v>1.089267619613249e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8155189922185858</v>
+        <v>0.9820601321688939</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2557,7 @@
         <v>1940.552</v>
       </c>
       <c r="C5" t="n">
-        <v>2458.748350015393</v>
+        <v>975.8285969031182</v>
       </c>
       <c r="D5" t="n">
         <v>1.27571e-07</v>
@@ -2692,16 +2590,13 @@
         <v>-39380.50890870148</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.042367087715085e-13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2803.854535460625</v>
+        <v>460.6395912043117</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000039e-08</v>
+        <v>1.035652359053067e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8156234761308356</v>
+        <v>0.9823447017682546</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1928.491</v>
       </c>
       <c r="C6" t="n">
-        <v>2446.685572855496</v>
+        <v>962.4199437201474</v>
       </c>
       <c r="D6" t="n">
         <v>1.27539e-07</v>
@@ -2745,16 +2640,13 @@
         <v>-43042.06978230023</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.226765655563096e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2773.885529941073</v>
+        <v>467.3855167669679</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.00000000000012e-08</v>
+        <v>1.003026857023365e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8157785700358812</v>
+        <v>0.983192320895939</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2657,7 @@
         <v>1888.034</v>
       </c>
       <c r="C7" t="n">
-        <v>2410.416230257163</v>
+        <v>947.3931688674717</v>
       </c>
       <c r="D7" t="n">
         <v>1.27534e-07</v>
@@ -2798,16 +2690,13 @@
         <v>-39778.55145872511</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.370555213838477e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2743.312331257359</v>
+        <v>483.4342099098311</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000028039e-08</v>
+        <v>1.107280638368643e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.815958463414011</v>
+        <v>0.9762294548597289</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2707,7 @@
         <v>1866.716</v>
       </c>
       <c r="C8" t="n">
-        <v>2388.374131060866</v>
+        <v>935.1406592381393</v>
       </c>
       <c r="D8" t="n">
         <v>1.27533e-07</v>
@@ -2851,16 +2740,13 @@
         <v>-39845.88477792585</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.639426865264397e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2713.193649824203</v>
+        <v>461.8647499168436</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000346e-08</v>
+        <v>8.133303688705961e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8161565733378053</v>
+        <v>0.999933338391822</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2757,7 @@
         <v>1841.636</v>
       </c>
       <c r="C9" t="n">
-        <v>2365.806134527517</v>
+        <v>921.9297114113385</v>
       </c>
       <c r="D9" t="n">
         <v>1.27576e-07</v>
@@ -2904,16 +2790,13 @@
         <v>-40088.36449265295</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.89106698798573e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2683.841014606723</v>
+        <v>481.7292551832429</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>1.340537394473055e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.816367191251169</v>
+        <v>0.9727445492306664</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2807,7 @@
         <v>1819.354</v>
       </c>
       <c r="C10" t="n">
-        <v>2345.158709162702</v>
+        <v>909.6682234663098</v>
       </c>
       <c r="D10" t="n">
         <v>1.27601e-07</v>
@@ -2957,16 +2840,13 @@
         <v>-40265.93407313389</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.487039066630172e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2655.668726110781</v>
+        <v>475.0765110980614</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>9.005809773474005e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8165838324755447</v>
+        <v>0.9960273960128276</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2857,7 @@
         <v>1799.848</v>
       </c>
       <c r="C11" t="n">
-        <v>2321.225245743022</v>
+        <v>898.2220250183034</v>
       </c>
       <c r="D11" t="n">
         <v>1.27635e-07</v>
@@ -3010,16 +2890,13 @@
         <v>-40641.36749474185</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.251661115633033e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2627.814668587311</v>
+        <v>479.8174348997703</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000097e-08</v>
+        <v>8.780508057188111e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8168057218030972</v>
+        <v>0.9994753859695642</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2907,7 @@
         <v>1776.233</v>
       </c>
       <c r="C12" t="n">
-        <v>2301.424313041855</v>
+        <v>886.9621757724316</v>
       </c>
       <c r="D12" t="n">
         <v>1.27662e-07</v>
@@ -3063,16 +2940,13 @@
         <v>-40608.09838101802</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15906019768179e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2601.024340728439</v>
+        <v>482.9870631177748</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000002822e-08</v>
+        <v>9.363977520411154e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8170357128606585</v>
+        <v>0.9995826790340979</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2957,7 @@
         <v>1750.01</v>
       </c>
       <c r="C13" t="n">
-        <v>2276.968651658749</v>
+        <v>877.4539161221406</v>
       </c>
       <c r="D13" t="n">
         <v>1.27724e-07</v>
@@ -3116,16 +2990,13 @@
         <v>-39215.834981334</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.011035109359172e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2576.156561204085</v>
+        <v>477.6793511801759</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000004689e-08</v>
+        <v>9.286103534984344e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.817267568166834</v>
+        <v>0.9881326653360414</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3007,7 @@
         <v>1743.236</v>
       </c>
       <c r="C14" t="n">
-        <v>2267.761264769534</v>
+        <v>866.7371494552206</v>
       </c>
       <c r="D14" t="n">
         <v>1.27747e-07</v>
@@ -3169,16 +3040,13 @@
         <v>-42415.60652058148</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.568197931079739e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2551.28120425517</v>
+        <v>484.3546777151684</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000004463e-08</v>
+        <v>8.980103984549855e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.817498530694392</v>
+        <v>0.9990320951160101</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3057,7 @@
         <v>1717.85</v>
       </c>
       <c r="C15" t="n">
-        <v>2244.386298297491</v>
+        <v>857.9896608633496</v>
       </c>
       <c r="D15" t="n">
         <v>1.27769e-07</v>
@@ -3222,16 +3090,13 @@
         <v>-40865.63523803785</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.668882385665964e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2527.73415986494</v>
+        <v>484.0898953172359</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000034587e-08</v>
+        <v>9.836499948852912e-10</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8177484728990478</v>
+        <v>0.995998913494373</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3107,7 @@
         <v>1702.134</v>
       </c>
       <c r="C16" t="n">
-        <v>2227.984849847014</v>
+        <v>849.4875936604658</v>
       </c>
       <c r="D16" t="n">
         <v>1.27797e-07</v>
@@ -3275,16 +3140,13 @@
         <v>-41060.15352908917</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.975493885944445e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2505.63080053129</v>
+        <v>485.5181494875853</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000083e-08</v>
+        <v>9.95146548893015e-10</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8179983119206899</v>
+        <v>0.9960382595284929</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3157,7 @@
         <v>1685.086</v>
       </c>
       <c r="C17" t="n">
-        <v>2210.55276866756</v>
+        <v>841.2103806103615</v>
       </c>
       <c r="D17" t="n">
         <v>1.27819e-07</v>
@@ -3328,16 +3190,13 @@
         <v>-41297.60757870334</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.180398849691809e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2484.345251598205</v>
+        <v>485.4243705373514</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000036812e-08</v>
+        <v>9.401158641905098e-10</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8182425081455851</v>
+        <v>0.9969288838630489</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3207,7 @@
         <v>1664.727</v>
       </c>
       <c r="C18" t="n">
-        <v>2189.417003654582</v>
+        <v>833.1455325366233</v>
       </c>
       <c r="D18" t="n">
         <v>1.27815e-07</v>
@@ -3381,16 +3240,13 @@
         <v>-39955.25431451828</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.411626433414081e-07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2463.688273415643</v>
+        <v>485.828176155633</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000518e-08</v>
+        <v>9.278469400126421e-10</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8185019954625765</v>
+        <v>0.9985889057810575</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3257,7 @@
         <v>1643.39</v>
       </c>
       <c r="C19" t="n">
-        <v>2167.522760731434</v>
+        <v>825.5629840606257</v>
       </c>
       <c r="D19" t="n">
         <v>1.27844e-07</v>
@@ -3434,16 +3290,13 @@
         <v>-38582.23345171555</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.623225235348359e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2444.242029882198</v>
+        <v>483.3209698762574</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000129e-08</v>
+        <v>9.711954572780221e-10</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8187606006791117</v>
+        <v>0.9974345422957398</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3307,7 @@
         <v>1634.587</v>
       </c>
       <c r="C20" t="n">
-        <v>2157.365698893936</v>
+        <v>818.3329329356237</v>
       </c>
       <c r="D20" t="n">
         <v>1.27864e-07</v>
@@ -3487,16 +3340,13 @@
         <v>-40108.84850815025</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.286020065073641e-07</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2425.190493971836</v>
+        <v>501.7959001881746</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>9.884678590434233e-10</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8190213597313608</v>
+        <v>0.9976685747983659</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3357,7 @@
         <v>1622.423</v>
       </c>
       <c r="C21" t="n">
-        <v>2145.237698154854</v>
+        <v>810.5604162310724</v>
       </c>
       <c r="D21" t="n">
         <v>1.27859e-07</v>
@@ -3540,16 +3390,13 @@
         <v>-40293.17597285898</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.2205882081286e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2406.66336318262</v>
+        <v>513.0674343974455</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000289402e-08</v>
+        <v>1.596313540309569e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8192920096820018</v>
+        <v>0.967522520930196</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3407,7 @@
         <v>1611.734</v>
       </c>
       <c r="C22" t="n">
-        <v>2135.360716424424</v>
+        <v>803.6369556469378</v>
       </c>
       <c r="D22" t="n">
         <v>1.27857e-07</v>
@@ -3593,16 +3440,13 @@
         <v>-41759.07643624504</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.315705945364943e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2388.666390912387</v>
+        <v>501.1005857612511</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000049884e-08</v>
+        <v>1.584743483540919e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8195598352457896</v>
+        <v>0.9745168084901914</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3603,7 @@
         <v>2497.835</v>
       </c>
       <c r="C2" t="n">
-        <v>3101.457016487561</v>
+        <v>1582.943115823263</v>
       </c>
       <c r="D2" t="n">
         <v>1.24795e-07</v>
@@ -3792,16 +3636,13 @@
         <v>-31695.46634223383</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.633407731575203e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3348.858405847063</v>
+        <v>0.1086038451406633</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000001433e-08</v>
+        <v>1.573955277868615e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8176324688964132</v>
+        <v>0.9057769814791193</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3653,7 @@
         <v>2127.574</v>
       </c>
       <c r="C3" t="n">
-        <v>2626.677057480019</v>
+        <v>1165.69767659527</v>
       </c>
       <c r="D3" t="n">
         <v>1.27591e-07</v>
@@ -3845,16 +3686,13 @@
         <v>-34693.27933809021</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.130932399777183e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2971.210459584276</v>
+        <v>250.2990511513612</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>6.229001267231346e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8186304488560482</v>
+        <v>0.9933251192046968</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3703,7 @@
         <v>2029.177</v>
       </c>
       <c r="C4" t="n">
-        <v>2519.66992804949</v>
+        <v>1061.350304093592</v>
       </c>
       <c r="D4" t="n">
         <v>1.27491e-07</v>
@@ -3898,16 +3736,13 @@
         <v>-35722.08121465044</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.34596987664797e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2874.888625268681</v>
+        <v>350.0095192103165</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000494e-08</v>
+        <v>1.116658021112483e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8188392396729105</v>
+        <v>0.9721213666916305</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3753,7 @@
         <v>1985.279</v>
       </c>
       <c r="C5" t="n">
-        <v>2477.050271209985</v>
+        <v>1029.092529813168</v>
       </c>
       <c r="D5" t="n">
         <v>1.27115e-07</v>
@@ -3951,16 +3786,13 @@
         <v>-36866.3705112435</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.068528083846652e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2825.492354650542</v>
+        <v>395.9525081192669</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>1.908450154450703e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.818931678424702</v>
+        <v>0.9340956354880294</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3803,7 @@
         <v>1948.283</v>
       </c>
       <c r="C6" t="n">
-        <v>2440.467423411923</v>
+        <v>1007.964671209499</v>
       </c>
       <c r="D6" t="n">
         <v>1.26829e-07</v>
@@ -4004,16 +3836,13 @@
         <v>-36471.81292042318</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.063072804677998e-13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2786.392827857368</v>
+        <v>383.5290015891609</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>8.286811265607978e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8190300039319343</v>
+        <v>0.9858306517170926</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3853,7 @@
         <v>1931.672</v>
       </c>
       <c r="C7" t="n">
-        <v>2424.14597022872</v>
+        <v>986.825619579698</v>
       </c>
       <c r="D7" t="n">
         <v>1.26654e-07</v>
@@ -4057,16 +3886,13 @@
         <v>-39602.55460301263</v>
       </c>
       <c r="Y7" t="n">
-        <v>71.32371058738921</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2951.124386511959</v>
+        <v>409.6223680536187</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.94122543945176e-08</v>
+        <v>1.240547494474259e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7739560161413798</v>
+        <v>0.9650826386447139</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1893.567</v>
       </c>
       <c r="C8" t="n">
-        <v>2389.946580817895</v>
+        <v>968.4590291792479</v>
       </c>
       <c r="D8" t="n">
         <v>1.26435e-07</v>
@@ -4110,16 +3936,13 @@
         <v>-38731.29715043544</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.671664069029631e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2713.963161309691</v>
+        <v>404.9373049020636</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>1.175127463867515e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8193195411474939</v>
+        <v>0.9735478045495473</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3953,7 @@
         <v>1851.347</v>
       </c>
       <c r="C9" t="n">
-        <v>2352.253082092855</v>
+        <v>952.1437929003279</v>
       </c>
       <c r="D9" t="n">
         <v>1.26406e-07</v>
@@ -4163,16 +3986,13 @@
         <v>-36386.84426795913</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15906027969333e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2679.141089504836</v>
+        <v>435.2906342405523</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000231054e-08</v>
+        <v>1.55022530778144e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8195179577502167</v>
+        <v>0.9582900745594806</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4003,7 @@
         <v>1839.816</v>
       </c>
       <c r="C10" t="n">
-        <v>2338.231980096235</v>
+        <v>934.7429902325325</v>
       </c>
       <c r="D10" t="n">
         <v>1.26383e-07</v>
@@ -4216,16 +4036,13 @@
         <v>-39367.70994830685</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.961402321364459e-07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2644.967983086389</v>
+        <v>416.9280806433306</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000215072e-08</v>
+        <v>8.886695047808962e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.819741044798654</v>
+        <v>0.9935492953315862</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4053,7 @@
         <v>1806.465</v>
       </c>
       <c r="C11" t="n">
-        <v>2306.375795148223</v>
+        <v>920.5814466384115</v>
       </c>
       <c r="D11" t="n">
         <v>1.2639e-07</v>
@@ -4269,16 +4086,13 @@
         <v>-38233.57053699046</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.830874305526209e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2612.878688775992</v>
+        <v>412.314269362279</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>8.548137093070075e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8199776686689161</v>
+        <v>0.9997925884603166</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4249,7 @@
         <v>1899.203</v>
       </c>
       <c r="C2" t="n">
-        <v>2437.063589207194</v>
+        <v>1424.431398373281</v>
       </c>
       <c r="D2" t="n">
         <v>1.30997e-07</v>
@@ -4468,16 +4282,13 @@
         <v>-7394.454779681775</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.250176133771185e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2800.436648582273</v>
+        <v>60.15005764138818</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000040855e-08</v>
+        <v>2.619758048636856e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8193011799911082</v>
+        <v>0.8771489041668847</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4299,7 @@
         <v>1850.708</v>
       </c>
       <c r="C3" t="n">
-        <v>2395.318199220897</v>
+        <v>1468.945359159142</v>
       </c>
       <c r="D3" t="n">
         <v>1.26476e-07</v>
@@ -4521,16 +4332,13 @@
         <v>-8459.62206740124</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49134392677757e-07</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2748.639652876695</v>
+        <v>0.5345765134425984</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000001799e-08</v>
+        <v>2.591646541806648e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8196078125782346</v>
+        <v>0.8737166067354936</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4349,7 @@
         <v>1829.823</v>
       </c>
       <c r="C4" t="n">
-        <v>2372.93897456787</v>
+        <v>1103.437534473122</v>
       </c>
       <c r="D4" t="n">
         <v>1.22903e-07</v>
@@ -4574,16 +4382,13 @@
         <v>-9623.180604717325</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.616761597915119e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2695.722714724801</v>
+        <v>249.7006686356236</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000094228e-08</v>
+        <v>6.581609260185027e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8199153253866724</v>
+        <v>0.990877248403724</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4399,7 @@
         <v>1766.049</v>
       </c>
       <c r="C5" t="n">
-        <v>2315.056761216935</v>
+        <v>1186.730707304513</v>
       </c>
       <c r="D5" t="n">
         <v>1.20005e-07</v>
@@ -4627,16 +4432,13 @@
         <v>-10357.19282243696</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.957277251521179e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2644.119877974922</v>
+        <v>306.9557607132518</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001134e-08</v>
+        <v>4.788982850372065e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8202081499390663</v>
+        <v>0.8634069628551581</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1732.083</v>
       </c>
       <c r="C6" t="n">
-        <v>2280.727595592389</v>
+        <v>1142.196851973715</v>
       </c>
       <c r="D6" t="n">
         <v>1.17614e-07</v>
@@ -4680,16 +4482,13 @@
         <v>-11237.11769570434</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.365394999646195e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2595.641709450079</v>
+        <v>224.2076012760706</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000003405e-08</v>
+        <v>1.273058900135034e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8205028790290346</v>
+        <v>0.9385610560194936</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4499,7 @@
         <v>1709.977</v>
       </c>
       <c r="C7" t="n">
-        <v>2258.922952348992</v>
+        <v>1130.822981051598</v>
       </c>
       <c r="D7" t="n">
         <v>1.15564e-07</v>
@@ -4733,16 +4532,13 @@
         <v>-12235.65279251055</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.907519249614416e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2550.046520342485</v>
+        <v>179.083263381168</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000082604e-08</v>
+        <v>8.213754626324053e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8208088214209822</v>
+        <v>0.979560759126009</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4549,7 @@
         <v>1678.77</v>
       </c>
       <c r="C8" t="n">
-        <v>2226.805883863057</v>
+        <v>1185.334942855327</v>
       </c>
       <c r="D8" t="n">
         <v>1.1381e-07</v>
@@ -4786,16 +4582,13 @@
         <v>-13039.19299753835</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.712281434731494e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2508.296240714393</v>
+        <v>290.2040527109745</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.00000000003338e-08</v>
+        <v>5.7485790842185e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.821104107191778</v>
+        <v>0.8509852099559406</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4599,7 @@
         <v>1643.45</v>
       </c>
       <c r="C9" t="n">
-        <v>2192.020909975792</v>
+        <v>1129.177649567405</v>
       </c>
       <c r="D9" t="n">
         <v>1.12286e-07</v>
@@ -4839,16 +4632,13 @@
         <v>-13681.61296526258</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.77150846792743e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2470.123988374298</v>
+        <v>157.9310447936365</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000182e-08</v>
+        <v>5.76840128902783e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8214009304057527</v>
+        <v>0.9917687586484104</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4649,7 @@
         <v>1617.987</v>
       </c>
       <c r="C10" t="n">
-        <v>2166.517337949469</v>
+        <v>1161.294233284356</v>
       </c>
       <c r="D10" t="n">
         <v>1.10946e-07</v>
@@ -4892,16 +4682,13 @@
         <v>-14416.93606936701</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.267559160568494e-07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2435.292632029961</v>
+        <v>105.4506270546288</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000040989e-08</v>
+        <v>5.257953892016242e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8216952007464622</v>
+        <v>0.9995239233719145</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4699,7 @@
         <v>1585.458</v>
       </c>
       <c r="C11" t="n">
-        <v>2135.751111984242</v>
+        <v>1371.807913928855</v>
       </c>
       <c r="D11" t="n">
         <v>1.09743e-07</v>
@@ -4945,16 +4732,13 @@
         <v>-14959.17237644951</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.970629965494482e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2403.989581371949</v>
+        <v>2.620051135048033</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>2.352370979474825e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8219854515502615</v>
+        <v>0.8832464264502238</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4749,7 @@
         <v>1565.023</v>
       </c>
       <c r="C12" t="n">
-        <v>2114.970652935471</v>
+        <v>1268.182061022431</v>
       </c>
       <c r="D12" t="n">
         <v>1.08665e-07</v>
@@ -4998,16 +4782,13 @@
         <v>-15620.6470556805</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.503251757311421e-13</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2375.224608979984</v>
+        <v>1.762758395040374</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000459538e-08</v>
+        <v>7.086886805349336e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8222867300141146</v>
+        <v>0.9708483563552865</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4799,7 @@
         <v>1544.104</v>
       </c>
       <c r="C13" t="n">
-        <v>2094.107567264193</v>
+        <v>1211.713123987548</v>
       </c>
       <c r="D13" t="n">
         <v>1.07698e-07</v>
@@ -5051,16 +4832,13 @@
         <v>-16202.69067657345</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.880385663385272e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2349.059633724833</v>
+        <v>36.43809632081503</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000332e-08</v>
+        <v>5.907969980276749e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8225974640222026</v>
+        <v>0.9887304002731988</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4849,7 @@
         <v>1533.734</v>
       </c>
       <c r="C14" t="n">
-        <v>2082.268927094585</v>
+        <v>1202.740368300452</v>
       </c>
       <c r="D14" t="n">
         <v>1.0681e-07</v>
@@ -5104,16 +4882,13 @@
         <v>-16933.63222417414</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.33776394399385e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2325.134590092293</v>
+        <v>35.05538601519986</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000271805e-08</v>
+        <v>5.019275491313686e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8228930558337284</v>
+        <v>0.9950186580969111</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4899,7 @@
         <v>1509.959</v>
       </c>
       <c r="C15" t="n">
-        <v>2058.74355658138</v>
+        <v>1350.32110676773</v>
       </c>
       <c r="D15" t="n">
         <v>1.06005e-07</v>
@@ -5157,16 +4932,13 @@
         <v>-17399.93435001546</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.691897970421873e-07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2302.386213503685</v>
+        <v>0.006206200755700456</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000001017256e-08</v>
+        <v>2.890610020908584e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8232082846873828</v>
+        <v>0.8719201613964772</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4949,7 @@
         <v>1491.532</v>
       </c>
       <c r="C16" t="n">
-        <v>2037.547303207411</v>
+        <v>1331.711686874607</v>
       </c>
       <c r="D16" t="n">
         <v>1.05279e-07</v>
@@ -5210,16 +4982,13 @@
         <v>-17780.21772305097</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.596420863316985e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2281.482957277099</v>
+        <v>0.9893544142866205</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000254311e-08</v>
+        <v>2.367538917768684e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8235093953344125</v>
+        <v>0.8814432087221223</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +4999,7 @@
         <v>1481.609</v>
       </c>
       <c r="C17" t="n">
-        <v>2029.148504717127</v>
+        <v>1322.065736475694</v>
       </c>
       <c r="D17" t="n">
         <v>1.04601e-07</v>
@@ -5263,16 +5032,13 @@
         <v>-18432.76049437571</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.04914153174012e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2262.267413097</v>
+        <v>3.400629410075719</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000057361e-08</v>
+        <v>2.32701128071134e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.823833526716292</v>
+        <v>0.8865831215233581</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5049,7 @@
         <v>1459.053</v>
       </c>
       <c r="C18" t="n">
-        <v>2003.617269168306</v>
+        <v>1325.716878630131</v>
       </c>
       <c r="D18" t="n">
         <v>1.03995e-07</v>
@@ -5316,16 +5082,13 @@
         <v>-18590.34975627036</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.332678423767153e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2243.561325798672</v>
+        <v>3.474674081208219</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000059156e-08</v>
+        <v>2.937881841300375e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8241433372471451</v>
+        <v>0.8706070435004833</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5099,7 @@
         <v>1451.259</v>
       </c>
       <c r="C19" t="n">
-        <v>1994.325227977113</v>
+        <v>1316.963663055264</v>
       </c>
       <c r="D19" t="n">
         <v>1.03445e-07</v>
@@ -5369,16 +5132,13 @@
         <v>-19198.0121281137</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.791828506452589e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2225.670396846531</v>
+        <v>4.102014693612383</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000004698e-08</v>
+        <v>2.871658007619563e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.824472087062335</v>
+        <v>0.8740655020577897</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5149,7 @@
         <v>1428.427</v>
       </c>
       <c r="C20" t="n">
-        <v>1971.297109025651</v>
+        <v>1299.252166821238</v>
       </c>
       <c r="D20" t="n">
         <v>1.0294e-07</v>
@@ -5422,16 +5182,13 @@
         <v>-19274.71448398443</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.54871228109796e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2208.721313615383</v>
+        <v>3.483703101026136</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000241999e-08</v>
+        <v>2.314323122361811e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8247862378301662</v>
+        <v>0.8875976547830721</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5199,7 @@
         <v>1422.202</v>
       </c>
       <c r="C21" t="n">
-        <v>1963.708510993314</v>
+        <v>1289.467418745857</v>
       </c>
       <c r="D21" t="n">
         <v>1.02476e-07</v>
@@ -5475,16 +5232,13 @@
         <v>-19784.15357346259</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.308285351258949e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2191.54226953775</v>
+        <v>3.679525828631391</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000523e-08</v>
+        <v>2.260422381699125e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8251300850646156</v>
+        <v>0.8898668814960834</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5249,7 @@
         <v>1421.031</v>
       </c>
       <c r="C22" t="n">
-        <v>1961.57784968433</v>
+        <v>1279.898808669048</v>
       </c>
       <c r="D22" t="n">
         <v>1.02064e-07</v>
@@ -5528,16 +5282,13 @@
         <v>-20508.20360593375</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.981113434266894e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2173.953277816343</v>
+        <v>3.840254715187695</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000004667e-08</v>
+        <v>2.219953646230552e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8254646451709602</v>
+        <v>0.8919012062593159</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5445,7 @@
         <v>2633.046</v>
       </c>
       <c r="C2" t="n">
-        <v>3349.077160161025</v>
+        <v>1241.968161438643</v>
       </c>
       <c r="D2" t="n">
         <v>1.06066e-07</v>
@@ -5727,16 +5478,13 @@
         <v>-17003.7804559832</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.299017170095969e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3561.534783168827</v>
+        <v>353.3854504361224</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000003729e-08</v>
+        <v>1.251821033469689e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8153311125924353</v>
+        <v>0.9502408739754699</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5495,7 @@
         <v>2117.304</v>
       </c>
       <c r="C3" t="n">
-        <v>2675.870534502791</v>
+        <v>1444.766767962289</v>
       </c>
       <c r="D3" t="n">
         <v>1.06208e-07</v>
@@ -5780,16 +5528,13 @@
         <v>-24412.2281274665</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.56791028328439e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3027.806120731897</v>
+        <v>93.10938242055673</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>1.686547503448334e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8164793472096545</v>
+        <v>0.9074292891466224</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5545,7 @@
         <v>2005.532</v>
       </c>
       <c r="C4" t="n">
-        <v>2539.621795077327</v>
+        <v>1518.780640384706</v>
       </c>
       <c r="D4" t="n">
         <v>1.04516e-07</v>
@@ -5833,16 +5578,13 @@
         <v>-29857.0041688394</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.58890149087939e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2904.169312889709</v>
+        <v>1.266184829611237</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001367e-08</v>
+        <v>1.93119523273848e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.816662360779307</v>
+        <v>0.8934159082282722</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5595,7 @@
         <v>1958.687</v>
       </c>
       <c r="C5" t="n">
-        <v>2490.939530569168</v>
+        <v>1167.983802188</v>
       </c>
       <c r="D5" t="n">
         <v>1.03513e-07</v>
@@ -5886,16 +5628,13 @@
         <v>-33763.96624746999</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.047744283612714e-07</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2850.779693181451</v>
+        <v>252.3488871364992</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001214e-08</v>
+        <v>6.441245649761021e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8166529721515329</v>
+        <v>0.9948026938102096</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5645,7 @@
         <v>1926.158</v>
       </c>
       <c r="C6" t="n">
-        <v>2460.599200454154</v>
+        <v>1100.261941858769</v>
       </c>
       <c r="D6" t="n">
         <v>1.03004e-07</v>
@@ -5939,16 +5678,13 @@
         <v>-36400.09492190822</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.766171171012999e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2811.130742374824</v>
+        <v>305.9354800307598</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000024e-08</v>
+        <v>8.712164029062386e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8166752976051159</v>
+        <v>0.9743143504417602</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5695,7 @@
         <v>1904.402</v>
       </c>
       <c r="C7" t="n">
-        <v>2437.064580740244</v>
+        <v>1064.081609514852</v>
       </c>
       <c r="D7" t="n">
         <v>1.02787e-07</v>
@@ -5992,16 +5728,13 @@
         <v>-39140.92978270056</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.709643256509537e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2774.385414273814</v>
+        <v>348.6429605378426</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000001774e-08</v>
+        <v>8.76461900437498e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8167686746850028</v>
+        <v>0.9811825987986152</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5745,7 @@
         <v>1874.635</v>
       </c>
       <c r="C8" t="n">
-        <v>2409.878441143315</v>
+        <v>1034.529815471117</v>
       </c>
       <c r="D8" t="n">
         <v>1.02807e-07</v>
@@ -6045,16 +5778,13 @@
         <v>-40636.05799411037</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.260716213093649e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2737.063204049498</v>
+        <v>375.2409990467532</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000055239e-08</v>
+        <v>9.105764370508922e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8169304140449013</v>
+        <v>0.9837978954467074</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5795,7 @@
         <v>1830.542</v>
       </c>
       <c r="C9" t="n">
-        <v>2370.094703201135</v>
+        <v>1009.09219117245</v>
       </c>
       <c r="D9" t="n">
         <v>1.02836e-07</v>
@@ -6098,16 +5828,13 @@
         <v>-40135.13670245658</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.91574825998866e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2700.104305961372</v>
+        <v>388.0020565127532</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000045479e-08</v>
+        <v>7.876226405085437e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8171093812715161</v>
+        <v>0.9972795733938555</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1809.123</v>
       </c>
       <c r="C10" t="n">
-        <v>2348.140824974512</v>
+        <v>987.3011027641915</v>
       </c>
       <c r="D10" t="n">
         <v>1.02979e-07</v>
@@ -6151,16 +5878,13 @@
         <v>-41779.69062934875</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.430121711400597e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2664.010242578872</v>
+        <v>405.5652356260889</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000043e-08</v>
+        <v>7.667969350777197e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8173120931724253</v>
+        <v>0.9958534679863685</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1784.224</v>
       </c>
       <c r="C11" t="n">
-        <v>2321.899666524001</v>
+        <v>965.0482837578045</v>
       </c>
       <c r="D11" t="n">
         <v>1.03194e-07</v>
@@ -6204,16 +5928,13 @@
         <v>-42674.75409014634</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.211919562091871e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2629.397398106514</v>
+        <v>409.7389254087029</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>8.544668083537483e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8175394345116048</v>
+        <v>0.9935668021426207</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6091,7 @@
         <v>1998.283</v>
       </c>
       <c r="C2" t="n">
-        <v>2609.749532206438</v>
+        <v>1303.344260535521</v>
       </c>
       <c r="D2" t="n">
         <v>9.57842e-08</v>
@@ -6403,16 +6124,13 @@
         <v>-21153.51643436788</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.151231363974261e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2940.378757410544</v>
+        <v>276.510531658782</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000429e-08</v>
+        <v>3.539422898302537e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8170800878527218</v>
+        <v>0.8749324610704677</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6141,7 @@
         <v>1933.762</v>
       </c>
       <c r="C3" t="n">
-        <v>2535.750867092748</v>
+        <v>1417.0050359233</v>
       </c>
       <c r="D3" t="n">
         <v>9.448459999999999e-08</v>
@@ -6456,16 +6174,13 @@
         <v>-21692.06069299027</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.435099714356694e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2877.569849263805</v>
+        <v>85.38020370198683</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000109e-08</v>
+        <v>1.590197500258038e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8171699025327676</v>
+        <v>0.9150004833575127</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6191,7 @@
         <v>1906.504</v>
       </c>
       <c r="C4" t="n">
-        <v>2505.172487100484</v>
+        <v>1420.506282369159</v>
       </c>
       <c r="D4" t="n">
         <v>9.401880000000001e-08</v>
@@ -6509,16 +6224,13 @@
         <v>-21827.75625252727</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8788766745626e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2839.102511532107</v>
+        <v>81.54630358944513</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.636743809730593e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.817286867446649</v>
+        <v>0.9101605324861943</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6241,7 @@
         <v>1879.386</v>
       </c>
       <c r="C5" t="n">
-        <v>2477.524192916896</v>
+        <v>1398.554925087839</v>
       </c>
       <c r="D5" t="n">
         <v>9.375e-08</v>
@@ -6562,16 +6274,13 @@
         <v>-21923.51170903886</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.121789508584776e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2803.344846551031</v>
+        <v>81.12020052598648</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000238e-08</v>
+        <v>1.498406794370335e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8174671550524111</v>
+        <v>0.9192377505341472</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6291,7 @@
         <v>1846.948</v>
       </c>
       <c r="C6" t="n">
-        <v>2443.140598917219</v>
+        <v>1518.562171509999</v>
       </c>
       <c r="D6" t="n">
         <v>9.35872e-08</v>
@@ -6615,16 +6324,13 @@
         <v>-21745.04189984535</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.113421678113385e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2768.84520082553</v>
+        <v>3.644068024541204</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000001092429e-08</v>
+        <v>2.50491467956351e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8176950499965467</v>
+        <v>0.8741496053077807</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6341,7 @@
         <v>1820.943</v>
       </c>
       <c r="C7" t="n">
-        <v>2417.766276408986</v>
+        <v>1503.988800389658</v>
       </c>
       <c r="D7" t="n">
         <v>9.35006e-08</v>
@@ -6668,16 +6374,13 @@
         <v>-21832.57958975694</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.437600200508825e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2735.163410080701</v>
+        <v>0.02516332381841229</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000113e-08</v>
+        <v>2.34134849005619e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8179413635802457</v>
+        <v>0.8818654741299999</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6391,7 @@
         <v>1788.521</v>
       </c>
       <c r="C8" t="n">
-        <v>2386.647806149538</v>
+        <v>1496.708465283601</v>
       </c>
       <c r="D8" t="n">
         <v>9.34184e-08</v>
@@ -6721,16 +6424,13 @@
         <v>-21596.55056860856</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.110718102358396e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2703.336167217894</v>
+        <v>0.05509546434530157</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000038399e-08</v>
+        <v>2.459586914762258e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8182121173767615</v>
+        <v>0.8783506451901836</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1766.023</v>
       </c>
       <c r="C9" t="n">
-        <v>2361.761640671337</v>
+        <v>1489.100225012954</v>
       </c>
       <c r="D9" t="n">
         <v>9.3349e-08</v>
@@ -6774,16 +6474,13 @@
         <v>-21717.16180044214</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.506544322010399e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2673.1586047477</v>
+        <v>3.03654369158345</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000263e-08</v>
+        <v>2.317279679370571e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8184951795438188</v>
+        <v>0.8782343330770188</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1745.827</v>
       </c>
       <c r="C10" t="n">
-        <v>2338.904227814165</v>
+        <v>1480.792755723884</v>
       </c>
       <c r="D10" t="n">
         <v>9.32978e-08</v>
@@ -6827,16 +6524,13 @@
         <v>-21832.00522023965</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.623944926286973e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2644.167051989636</v>
+        <v>0.9251769114139357</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000204752e-08</v>
+        <v>2.484244585640966e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8187806748227648</v>
+        <v>0.8789374334271449</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6541,7 @@
         <v>1732.728</v>
       </c>
       <c r="C11" t="n">
-        <v>2326.964628918777</v>
+        <v>1470.168949444167</v>
       </c>
       <c r="D11" t="n">
         <v>9.32597e-08</v>
@@ -6880,16 +6574,13 @@
         <v>-22181.03649170305</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.444662089361109e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2617.839018677864</v>
+        <v>2.711593901661571</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000681719e-08</v>
+        <v>2.639791441147223e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8190555621016918</v>
+        <v>0.8728223568084511</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6591,7 @@
         <v>1705.893</v>
       </c>
       <c r="C12" t="n">
-        <v>2298.586679628752</v>
+        <v>1462.071621880431</v>
       </c>
       <c r="D12" t="n">
         <v>9.31941e-08</v>
@@ -6933,16 +6624,13 @@
         <v>-21937.96182038993</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.132752311169298e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2592.809537806709</v>
+        <v>4.471523014190056</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000252437e-08</v>
+        <v>2.479080308415738e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8193113550764618</v>
+        <v>0.8771013192902462</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6641,7 @@
         <v>1698.88</v>
       </c>
       <c r="C13" t="n">
-        <v>2286.94746927609</v>
+        <v>1459.244616315052</v>
       </c>
       <c r="D13" t="n">
         <v>9.315040000000001e-08</v>
@@ -6986,16 +6674,13 @@
         <v>-22299.46689124181</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.176235806691076e-11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2569.205079885846</v>
+        <v>5.369201579101255</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000231679e-08</v>
+        <v>2.718579739855687e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.819588945908863</v>
+        <v>0.8712546558605727</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6691,7 @@
         <v>1672.98</v>
       </c>
       <c r="C14" t="n">
-        <v>2264.5078578872</v>
+        <v>1448.039522826034</v>
       </c>
       <c r="D14" t="n">
         <v>9.3097e-08</v>
@@ -7039,16 +6724,13 @@
         <v>-22091.47418929515</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.919843425299996e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2547.103345394961</v>
+        <v>5.310333064294371</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000007411e-08</v>
+        <v>2.721055082118436e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8198538157558599</v>
+        <v>0.8724238636775286</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6741,7 @@
         <v>1651.699</v>
       </c>
       <c r="C15" t="n">
-        <v>2241.74618998098</v>
+        <v>1426.651356091959</v>
       </c>
       <c r="D15" t="n">
         <v>9.30356e-08</v>
@@ -7092,16 +6774,13 @@
         <v>-21924.61462688688</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.732945103672952e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2525.510442954363</v>
+        <v>5.545402119638322</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000012506e-08</v>
+        <v>2.143876364846262e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.820117022014795</v>
+        <v>0.8894883245954581</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6791,7 @@
         <v>1640.956</v>
       </c>
       <c r="C16" t="n">
-        <v>2233.371025059165</v>
+        <v>1424.893834281386</v>
       </c>
       <c r="D16" t="n">
         <v>9.29782e-08</v>
@@ -7145,16 +6824,13 @@
         <v>-22212.93677855975</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.004175479941784e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2504.72971191496</v>
+        <v>6.629008935827025</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000008694e-08</v>
+        <v>2.326166167610367e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8203806527482911</v>
+        <v>0.8808524870626769</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6841,7 @@
         <v>1628.318</v>
       </c>
       <c r="C17" t="n">
-        <v>2215.944754939125</v>
+        <v>1421.129384082954</v>
       </c>
       <c r="D17" t="n">
         <v>9.29285e-08</v>
@@ -7198,16 +6874,13 @@
         <v>-22258.458195896</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.867388137333673e-07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2482.542656206414</v>
+        <v>5.513549678575751</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000010991e-08</v>
+        <v>2.541831486657449e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8207189152318026</v>
+        <v>0.8804810642979977</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6891,7 @@
         <v>1598.847</v>
       </c>
       <c r="C18" t="n">
-        <v>2186.010053814247</v>
+        <v>1416.283495964934</v>
       </c>
       <c r="D18" t="n">
         <v>9.29393e-08</v>
@@ -7251,16 +6924,13 @@
         <v>-21725.98098129785</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.382385891958653e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2461.482341022391</v>
+        <v>1.972399609549993</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.00000000003205e-08</v>
+        <v>2.548811932945695e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8209876267237027</v>
+        <v>0.8800454348044725</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6941,7 @@
         <v>1583.89</v>
       </c>
       <c r="C19" t="n">
-        <v>2170.288928138759</v>
+        <v>1395.590127682757</v>
       </c>
       <c r="D19" t="n">
         <v>9.289809999999999e-08</v>
@@ -7304,16 +6974,13 @@
         <v>-21762.47927966942</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.797996536432553e-07</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2441.084636013304</v>
+        <v>4.812718514412961</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000366e-08</v>
+        <v>2.191285853125157e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8212695826713596</v>
+        <v>0.8886814549819637</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +6991,7 @@
         <v>1574.268</v>
       </c>
       <c r="C20" t="n">
-        <v>2161.993093956314</v>
+        <v>1386.58088898574</v>
       </c>
       <c r="D20" t="n">
         <v>9.28614e-08</v>
@@ -7357,16 +7024,13 @@
         <v>-22071.43666722395</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.81385976352895e-12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2420.631508356611</v>
+        <v>5.159085442466322</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000751e-08</v>
+        <v>2.183126550253294e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8215462268639109</v>
+        <v>0.8873351503146315</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7041,7 @@
         <v>1560.491</v>
       </c>
       <c r="C21" t="n">
-        <v>2146.35367951369</v>
+        <v>1377.254380370869</v>
       </c>
       <c r="D21" t="n">
         <v>9.2822e-08</v>
@@ -7410,16 +7074,13 @@
         <v>-22052.73214628453</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.728538909672386e-12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2400.477899831852</v>
+        <v>4.652377517097236</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000052846e-08</v>
+        <v>2.11286816680549e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8218357846702239</v>
+        <v>0.8917271303251063</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7091,7 @@
         <v>1544.898</v>
       </c>
       <c r="C22" t="n">
-        <v>2129.900848163467</v>
+        <v>1367.386827112086</v>
       </c>
       <c r="D22" t="n">
         <v>9.27903e-08</v>
@@ -7463,16 +7124,13 @@
         <v>-22035.20524721704</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.784561525906281e-14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2380.003056550901</v>
+        <v>4.43788121396965</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000034616e-08</v>
+        <v>2.06615478673233e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8221202952507087</v>
+        <v>0.8937316622141444</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7287,7 @@
         <v>2510.091</v>
       </c>
       <c r="C2" t="n">
-        <v>3179.935435741775</v>
+        <v>1180.846083791991</v>
       </c>
       <c r="D2" t="n">
         <v>1.08446e-07</v>
@@ -7662,16 +7320,13 @@
         <v>-17632.54020588438</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.634118355191929e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3426.277144175976</v>
+        <v>423.6881551984921</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000008346e-08</v>
+        <v>1.887605401608014e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8146441018578838</v>
+        <v>0.9251726441489447</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7337,7 @@
         <v>2098.634</v>
       </c>
       <c r="C3" t="n">
-        <v>2647.917342657336</v>
+        <v>1568.709545685927</v>
       </c>
       <c r="D3" t="n">
         <v>1.06218e-07</v>
@@ -7715,16 +7370,13 @@
         <v>-30470.53300919475</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.545621766313861e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2993.890538410906</v>
+        <v>10.62712475373261</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000003499e-08</v>
+        <v>2.533878339697206e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8159917055448808</v>
+        <v>0.8722653411754574</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7387,7 @@
         <v>1996.765</v>
       </c>
       <c r="C4" t="n">
-        <v>2525.975243306968</v>
+        <v>1112.841901201339</v>
       </c>
       <c r="D4" t="n">
         <v>1.04858e-07</v>
@@ -7768,16 +7420,13 @@
         <v>-38878.02805081943</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.717342870050876e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2881.523445665949</v>
+        <v>531.0052610737118</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>7.387385799205767e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8162090927494554</v>
+        <v>0.8509191549791384</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7437,7 @@
         <v>1939.945</v>
       </c>
       <c r="C5" t="n">
-        <v>2470.761785737807</v>
+        <v>1042.181761134409</v>
       </c>
       <c r="D5" t="n">
         <v>1.04557e-07</v>
@@ -7821,16 +7470,13 @@
         <v>-43691.14923864724</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.82560378692336e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2822.684840454448</v>
+        <v>385.6583887543557</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000004966e-08</v>
+        <v>8.625607465536733e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8162584938880966</v>
+        <v>0.9846163140647017</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7487,7 @@
         <v>1902.441</v>
       </c>
       <c r="C6" t="n">
-        <v>2433.085214393198</v>
+        <v>998.3528691537315</v>
       </c>
       <c r="D6" t="n">
         <v>1.04766e-07</v>
@@ -7874,16 +7520,13 @@
         <v>-47442.44694915169</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.319020738600766e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2776.070691800724</v>
+        <v>447.5072930058419</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.0000000001712e-08</v>
+        <v>1.485344517567215e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8163215401654593</v>
+        <v>0.956845383551734</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7537,7 @@
         <v>1878.83</v>
       </c>
       <c r="C7" t="n">
-        <v>2405.713821949396</v>
+        <v>967.5111762903563</v>
       </c>
       <c r="D7" t="n">
         <v>1.05223e-07</v>
@@ -7927,16 +7570,13 @@
         <v>-50997.17662337609</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.532729892221022e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2732.703664316689</v>
+        <v>446.44836956611</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000002247e-08</v>
+        <v>8.41338962832131e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8164255107216594</v>
+        <v>0.9966735514001177</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7587,7 @@
         <v>1840.52</v>
       </c>
       <c r="C8" t="n">
-        <v>2370.561692558135</v>
+        <v>939.9765841590762</v>
       </c>
       <c r="D8" t="n">
         <v>1.05818e-07</v>
@@ -7980,16 +7620,13 @@
         <v>-52612.93724515766</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.451648262922935e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2690.013723299287</v>
+        <v>535.3864868616357</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000011e-08</v>
+        <v>2.390833997190308e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8165961113650829</v>
+        <v>0.9370689749653716</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7637,7 @@
         <v>1795.989</v>
       </c>
       <c r="C9" t="n">
-        <v>2329.52965194358</v>
+        <v>916.5574792831439</v>
       </c>
       <c r="D9" t="n">
         <v>1.0646e-07</v>
@@ -8033,16 +7670,13 @@
         <v>-50504.57157258208</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.144191463462293e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2649.58340716017</v>
+        <v>472.484802048822</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000024128e-08</v>
+        <v>9.835579974800375e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8167803308257643</v>
+        <v>0.9878569543353058</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7687,7 @@
         <v>1770.163</v>
       </c>
       <c r="C10" t="n">
-        <v>2305.340557903121</v>
+        <v>896.9377753132377</v>
       </c>
       <c r="D10" t="n">
         <v>1.07121e-07</v>
@@ -8086,16 +7720,13 @@
         <v>-52924.02082403241</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.522646389400353e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2612.572034898169</v>
+        <v>486.0559926433783</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000010473e-08</v>
+        <v>9.479400268189395e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.816979169562252</v>
+        <v>0.997355480207373</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7737,7 @@
         <v>1745.434</v>
       </c>
       <c r="C11" t="n">
-        <v>2276.675572452849</v>
+        <v>879.350149496531</v>
       </c>
       <c r="D11" t="n">
         <v>1.07777e-07</v>
@@ -8139,16 +7770,13 @@
         <v>-53765.86962565793</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.739910425933144e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2577.284475807136</v>
+        <v>491.518066850865</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>9.827132052204291e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.817183405243335</v>
+        <v>0.9874181158265507</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7933,7 @@
         <v>2112.176</v>
       </c>
       <c r="C2" t="n">
-        <v>2676.833218541219</v>
+        <v>1204.793735383918</v>
       </c>
       <c r="D2" t="n">
         <v>1.12216e-07</v>
@@ -8338,16 +7966,13 @@
         <v>-32628.33277405092</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.158407408728681e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3000.966359437378</v>
+        <v>240.6281134392071</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000016e-08</v>
+        <v>7.008357642661175e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8164130298239989</v>
+        <v>0.9834095484802852</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7983,7 @@
         <v>1985.796</v>
       </c>
       <c r="C3" t="n">
-        <v>2505.154279492478</v>
+        <v>1036.601935093486</v>
       </c>
       <c r="D3" t="n">
         <v>1.08974e-07</v>
@@ -8391,16 +8016,13 @@
         <v>-46331.83728125821</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.267505402280966e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2858.286452220459</v>
+        <v>397.9239742407081</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000006568e-08</v>
+        <v>1.156440748904684e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8167065647458969</v>
+        <v>0.9644075859522157</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1948.864</v>
       </c>
       <c r="C4" t="n">
-        <v>2465.058996613096</v>
+        <v>1001.846976232257</v>
       </c>
       <c r="D4" t="n">
         <v>1.08961e-07</v>
@@ -8444,16 +8066,13 @@
         <v>-50460.77652652798</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.278638785548944e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2810.125957375854</v>
+        <v>428.2011280381661</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000103e-08</v>
+        <v>9.020687525527894e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8167515396757253</v>
+        <v>0.987563443831746</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8083,7 @@
         <v>1910.186</v>
       </c>
       <c r="C5" t="n">
-        <v>2426.991163628215</v>
+        <v>982.6785680269726</v>
       </c>
       <c r="D5" t="n">
         <v>1.09131e-07</v>
@@ -8497,16 +8116,13 @@
         <v>-48376.39602861545</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.212920454889216e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2775.718603901964</v>
+        <v>437.0122722211401</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>8.165833311962826e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8168150122545582</v>
+        <v>0.9889126432871571</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8133,7 @@
         <v>1896.16</v>
       </c>
       <c r="C6" t="n">
-        <v>2412.543164739458</v>
+        <v>964.6597991057064</v>
       </c>
       <c r="D6" t="n">
         <v>1.09354e-07</v>
@@ -8550,16 +8166,13 @@
         <v>-52222.31034223757</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.772125858531818e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2743.087221394611</v>
+        <v>441.5034060045425</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000412e-08</v>
+        <v>9.594494749324546e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8169349031679062</v>
+        <v>0.9858321991154159</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8183,7 @@
         <v>1856.954</v>
       </c>
       <c r="C7" t="n">
-        <v>2377.014580914495</v>
+        <v>948.1777543876694</v>
       </c>
       <c r="D7" t="n">
         <v>1.09563e-07</v>
@@ -8603,16 +8216,13 @@
         <v>-49409.95767648036</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.662437145494402e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2712.132656919507</v>
+        <v>455.5011286330524</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>9.039552908952046e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8170880359488286</v>
+        <v>0.9971841218078109</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8233,7 @@
         <v>1835.395</v>
       </c>
       <c r="C8" t="n">
-        <v>2354.003238828874</v>
+        <v>934.6126167144232</v>
       </c>
       <c r="D8" t="n">
         <v>1.09764e-07</v>
@@ -8656,16 +8266,13 @@
         <v>-49827.06997530271</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.815134372643754e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2681.705135094257</v>
+        <v>537.3081281357267</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.00000000021995e-08</v>
+        <v>2.560924764693701e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.81727606034416</v>
+        <v>0.9317458241839571</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8283,7 @@
         <v>1809.848</v>
       </c>
       <c r="C9" t="n">
-        <v>2330.767290842011</v>
+        <v>919.5704706629111</v>
       </c>
       <c r="D9" t="n">
         <v>1.09962e-07</v>
@@ -8709,16 +8316,13 @@
         <v>-50164.76515232034</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.189743503652721e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2652.352521733277</v>
+        <v>463.6972661879886</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000058091e-08</v>
+        <v>1.025910545046824e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8174811092270026</v>
+        <v>0.9868420544529959</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8333,7 @@
         <v>1791.046</v>
       </c>
       <c r="C10" t="n">
-        <v>2309.966423309326</v>
+        <v>907.32877755352</v>
       </c>
       <c r="D10" t="n">
         <v>1.10124e-07</v>
@@ -8762,16 +8366,13 @@
         <v>-50547.52303501256</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.874349845264225e-07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2624.277451985394</v>
+        <v>464.0868086312141</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000053324e-08</v>
+        <v>1.015220944963336e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8176967688679421</v>
+        <v>0.9845432984769747</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8383,7 @@
         <v>1769.216</v>
       </c>
       <c r="C11" t="n">
-        <v>2286.98592403186</v>
+        <v>895.4478985686891</v>
       </c>
       <c r="D11" t="n">
         <v>1.10288e-07</v>
@@ -8815,16 +8416,13 @@
         <v>-50785.13580091142</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09508720581169e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2597.402466653782</v>
+        <v>455.1030878057749</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.070350938746804e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8179342730306878</v>
+        <v>0.989450956445705</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8433,7 @@
         <v>1740.558</v>
       </c>
       <c r="C12" t="n">
-        <v>2262.255793341577</v>
+        <v>883.4729556803878</v>
       </c>
       <c r="D12" t="n">
         <v>1.10439e-07</v>
@@ -8868,16 +8466,13 @@
         <v>-49418.88726750809</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.292069902934848e-07</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2571.338485166099</v>
+        <v>487.3553544214296</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000458739e-08</v>
+        <v>1.156751126832658e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8181862236986954</v>
+        <v>0.9839965082545998</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8483,7 @@
         <v>1734.149</v>
       </c>
       <c r="C13" t="n">
-        <v>2252.593786169768</v>
+        <v>872.4294709405208</v>
       </c>
       <c r="D13" t="n">
         <v>1.10574e-07</v>
@@ -8921,16 +8516,13 @@
         <v>-52973.43115342722</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.404457906466545e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2545.880687723539</v>
+        <v>479.4119690293984</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000001074221e-08</v>
+        <v>9.402745419730246e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8184522424406639</v>
+        <v>0.998149941007917</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8533,7 @@
         <v>1709.272</v>
       </c>
       <c r="C14" t="n">
-        <v>2227.965710072302</v>
+        <v>862.180264723808</v>
       </c>
       <c r="D14" t="n">
         <v>1.1071e-07</v>
@@ -8974,16 +8566,13 @@
         <v>-51462.0670299963</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.332997920019119e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2521.208120926528</v>
+        <v>485.6827127793713</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>9.373224767398206e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8187267803925982</v>
+        <v>0.9928408370472072</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8583,7 @@
         <v>1684.773</v>
       </c>
       <c r="C15" t="n">
-        <v>2203.621226033896</v>
+        <v>851.7326852525014</v>
       </c>
       <c r="D15" t="n">
         <v>1.10818e-07</v>
@@ -9027,16 +8616,13 @@
         <v>-50257.67016735821</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.657303427527979e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2496.692704455005</v>
+        <v>480.9712843358856</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000137e-08</v>
+        <v>9.976993961605105e-10</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8190160205410225</v>
+        <v>0.9881119057065312</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8633,7 @@
         <v>1658.788</v>
       </c>
       <c r="C16" t="n">
-        <v>2180.191682556604</v>
+        <v>841.3203860974738</v>
       </c>
       <c r="D16" t="n">
         <v>1.1093e-07</v>
@@ -9080,16 +8666,13 @@
         <v>-48760.84925814068</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.783544532625746e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2472.811559824472</v>
+        <v>482.1927038766152</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000892e-08</v>
+        <v>9.677476874880714e-10</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8193016796615211</v>
+        <v>0.9969304699723815</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8683,7 @@
         <v>1648.323</v>
       </c>
       <c r="C17" t="n">
-        <v>2168.464510905446</v>
+        <v>831.4387982248171</v>
       </c>
       <c r="D17" t="n">
         <v>1.11052e-07</v>
@@ -9133,16 +8716,13 @@
         <v>-50362.63980650193</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.62555120752889e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2449.452069762684</v>
+        <v>481.5770160900411</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000346234e-08</v>
+        <v>9.893749367401097e-10</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8196020131215307</v>
+        <v>0.9993240193754567</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8733,7 @@
         <v>1625.911</v>
       </c>
       <c r="C18" t="n">
-        <v>2144.902947232851</v>
+        <v>822.1503147256767</v>
       </c>
       <c r="D18" t="n">
         <v>1.11142e-07</v>
@@ -9186,16 +8766,13 @@
         <v>-48898.0485121388</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.497575016897093e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2426.012853127347</v>
+        <v>509.0682608006127</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000047255e-08</v>
+        <v>1.423296811274974e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.819906549407887</v>
+        <v>0.9756101835979314</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8783,7 @@
         <v>1620.467</v>
       </c>
       <c r="C19" t="n">
-        <v>2137.063308750487</v>
+        <v>813.8954960241426</v>
       </c>
       <c r="D19" t="n">
         <v>1.11242e-07</v>
@@ -9239,16 +8816,13 @@
         <v>-52205.13770878645</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.316421128727929e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2402.776169862276</v>
+        <v>509.1421610622333</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000004265e-08</v>
+        <v>1.507384283816978e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8202219260390889</v>
+        <v>0.9733023803390328</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8833,7 @@
         <v>1596.118</v>
       </c>
       <c r="C20" t="n">
-        <v>2113.07548591261</v>
+        <v>804.2991291418505</v>
       </c>
       <c r="D20" t="n">
         <v>1.11353e-07</v>
@@ -9292,16 +8866,13 @@
         <v>-50954.37139681785</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.157482282360261e-07</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2379.335549036302</v>
+        <v>496.175943109258</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000001512e-08</v>
+        <v>1.165209345487217e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8205438244321003</v>
+        <v>0.9952776211053085</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8883,7 @@
         <v>1572.444</v>
       </c>
       <c r="C21" t="n">
-        <v>2088.868635983094</v>
+        <v>794.7344754194862</v>
       </c>
       <c r="D21" t="n">
         <v>1.11442e-07</v>
@@ -9345,16 +8916,13 @@
         <v>-49449.55677672399</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.907853953670926e-07</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2355.776928591757</v>
+        <v>502.2666371156239</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000093169e-08</v>
+        <v>1.051940639443014e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8208714781043512</v>
+        <v>0.9972476991946136</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8933,7 @@
         <v>1560.63</v>
       </c>
       <c r="C22" t="n">
-        <v>2076.792040826372</v>
+        <v>786.3659499535489</v>
       </c>
       <c r="D22" t="n">
         <v>1.11541e-07</v>
@@ -9398,16 +8966,13 @@
         <v>-51302.46071411396</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.648069116068909e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2331.960599037601</v>
+        <v>463.6364478237495</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000613e-08</v>
+        <v>9.018425342249132e-10</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8212019332917957</v>
+        <v>0.9999234037528263</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9129,7 @@
         <v>2017.191</v>
       </c>
       <c r="C2" t="n">
-        <v>2720.279869822423</v>
+        <v>1355.71859880994</v>
       </c>
       <c r="D2" t="n">
         <v>1.16473e-07</v>
@@ -9597,16 +9162,13 @@
         <v>-22663.29617342908</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.543391031898314e-07</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2835.730603540367</v>
+        <v>37.40225179653239</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000011267e-08</v>
+        <v>4.462048140714812e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8167432614181571</v>
+        <v>0.9976980889791088</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9179,7 @@
         <v>1667.076</v>
       </c>
       <c r="C3" t="n">
-        <v>2241.085947405102</v>
+        <v>889.9096046401127</v>
       </c>
       <c r="D3" t="n">
         <v>1.14144e-07</v>
@@ -9650,16 +9212,13 @@
         <v>-37185.60590686703</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.120566299024315e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2475.638686923035</v>
+        <v>444.2930926353297</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000058823e-08</v>
+        <v>7.953323176442587e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.817839548612131</v>
+        <v>0.9993988192272801</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9229,7 @@
         <v>1580.666</v>
       </c>
       <c r="C4" t="n">
-        <v>2133.303863530242</v>
+        <v>821.7042473911119</v>
       </c>
       <c r="D4" t="n">
         <v>1.13888e-07</v>
@@ -9703,16 +9262,13 @@
         <v>-42030.69338665235</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.681365641592461e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2384.73543797787</v>
+        <v>484.9510525757274</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>9.061061373466485e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8180575496901341</v>
+        <v>0.9999360950565598</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1531.566</v>
       </c>
       <c r="C5" t="n">
-        <v>2081.772786703304</v>
+        <v>793.5965189692672</v>
       </c>
       <c r="D5" t="n">
         <v>1.14279e-07</v>
@@ -9756,16 +9312,13 @@
         <v>-41999.97855136172</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.271332618036654e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2337.765754142115</v>
+        <v>511.3539226547183</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.405251271532155e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8181737072291551</v>
+        <v>0.9804758912809169</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9329,7 @@
         <v>1503.591</v>
       </c>
       <c r="C6" t="n">
-        <v>2056.82922271536</v>
+        <v>775.2445865663489</v>
       </c>
       <c r="D6" t="n">
         <v>1.14852e-07</v>
@@ -9809,16 +9362,13 @@
         <v>-43750.63328642953</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.542384284277862e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2299.674847311927</v>
+        <v>524.8746933046715</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.271377394099437e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8183282288016709</v>
+        <v>0.994967870713574</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>1476.514</v>
       </c>
       <c r="C7" t="n">
-        <v>2030.289428252323</v>
+        <v>761.0573825240416</v>
       </c>
       <c r="D7" t="n">
         <v>1.15459e-07</v>
@@ -9862,16 +9412,13 @@
         <v>-43879.38074988562</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.994722067746133e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2263.576090227162</v>
+        <v>519.605465422606</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000014804e-08</v>
+        <v>1.368604832462676e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8185535913428899</v>
+        <v>0.9869917439427331</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>1447.647</v>
       </c>
       <c r="C8" t="n">
-        <v>1999.942728815724</v>
+        <v>746.3587080796499</v>
       </c>
       <c r="D8" t="n">
         <v>1.16084e-07</v>
@@ -9915,16 +9462,13 @@
         <v>-43782.55575465207</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.241463530229632e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2227.982508099498</v>
+        <v>511.272523482459</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000019271e-08</v>
+        <v>1.145092568991069e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8188106316763375</v>
+        <v>0.9992493217206134</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>1425.852</v>
       </c>
       <c r="C9" t="n">
-        <v>1979.873648187591</v>
+        <v>734.6592459081119</v>
       </c>
       <c r="D9" t="n">
         <v>1.16684e-07</v>
@@ -9968,16 +9512,13 @@
         <v>-44716.21498348555</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.648657909093709e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2193.76059181959</v>
+        <v>531.5120639047732</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000576e-08</v>
+        <v>1.188289601451299e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8191120987680168</v>
+        <v>0.9973915704701464</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>1398.577</v>
       </c>
       <c r="C10" t="n">
-        <v>1955.691108775599</v>
+        <v>723.9089167768831</v>
       </c>
       <c r="D10" t="n">
         <v>1.17275e-07</v>
@@ -10021,16 +9562,13 @@
         <v>-44328.17691225108</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.862618998077169e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2161.87893388501</v>
+        <v>533.0900543860389</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000451769e-08</v>
+        <v>1.536963333338317e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8194207176122302</v>
+        <v>0.9858787468705041</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9579,7 @@
         <v>1366.599</v>
       </c>
       <c r="C11" t="n">
-        <v>1919.712531078129</v>
+        <v>714.2800471920981</v>
       </c>
       <c r="D11" t="n">
         <v>1.17853e-07</v>
@@ -10074,16 +9612,13 @@
         <v>-41631.84936293787</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.43643614570388e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2132.278289166683</v>
+        <v>535.604307588595</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000017e-08</v>
+        <v>1.27540127824698e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8197143521420047</v>
+        <v>0.9979590670812526</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 40.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.00000000008241e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8166769811266618</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2259.073</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2731.23084733237</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.28197e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-74.108</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1064554128584123</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.723646542944746</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.676437364998014</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.164699549237364</v>
+      </c>
+      <c r="L12" t="n">
+        <v>29.87842624708597</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.9830618655326</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>14.24016815554302</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-38132.8339456133</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-10.33088395259051</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000023038e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.814679482164695</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2158.171</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.95533477669823</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2642.560638735911</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9675347074074444</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.28059e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-74.872</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.07754210820838091</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5794318978754281</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.46129865511279</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.573167636479671</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.17717386508153</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.12328136640721</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.75689193654533</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-38156.19630627904</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-18.60259379170088</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8150082898075091</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2080.076</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.920765287354592</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2553.045574404134</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.934760083314718</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.28295e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-75.40900000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.127993002124909</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.601992350057154</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.590583914195647</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.788867417764002</v>
+      </c>
+      <c r="L14" t="n">
+        <v>32.67782644253197</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.3031339344174</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>15.47695969870335</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-38871.99816183687</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-14.4145543884847</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000028e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8152581892365701</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2034.017</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9003768359853799</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2493.095762819969</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9128103416285773</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.28391e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-75.785</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2746975209751816</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.151410124808615</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.017523787125124</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.688083327609251</v>
+      </c>
+      <c r="L15" t="n">
+        <v>40.04151004180406</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.56350830036413</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.65275615089208</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-41102.28092246929</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-12.74286801461108</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000372e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8154826676393956</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1980.094</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8765073107420611</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2446.016658037408</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8955730199175459</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.28426e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-76.105</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1747247486835757</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8481655765330968</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.667613251273402</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.877180311973918</v>
+      </c>
+      <c r="L16" t="n">
+        <v>36.37031325931914</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.54510966945305</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.56386015521477</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-40036.46154239417</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-11.94623746723596</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.738751977367518e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.7789491904179999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1944.416</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8607141070695813</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2403.193378685488</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8798939060873305</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.28414e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-76.355</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2801884206066353</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9587330388134956</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.692183183613805</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.952344700347482</v>
+      </c>
+      <c r="L17" t="n">
+        <v>37.79967431912971</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.62832489143814</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.97364809196308</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-40428.37521305256</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-10.06624659927684</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000041e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8158937760381044</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1912.142</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.846427716147287</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2368.55977535484</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8672133216671321</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.28377e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-76.58499999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2568233066973304</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9999132273237242</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.901894083248264</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.116360948905601</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39.21264438855209</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.70581550039525</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.3738396417849</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-40838.12123561982</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-9.788821332208499</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8160969064026584</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1873.944</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8295190106738473</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2337.375093576728</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8557955091418487</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.28335e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-76.777</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.063483997821269</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6874721448384377</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.54972212901152</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.556446352945444</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35.03130433638032</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.63775485952988</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.02136339980462</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-39410.07518989902</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-8.685794561879447</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8162903173407705</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1856.957</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8219995546845985</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2311.523017897792</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8463301519003742</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.28267e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-76.94199999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2130723998028579</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.179269023899987</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.899433613260027</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.223206782438076</v>
+      </c>
+      <c r="L20" t="n">
+        <v>40.58253376510598</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.8165993740856</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.97976963939739</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-41322.73790030564</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-9.101683128114928</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000084e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8164823137323599</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1832.666</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8112469141103453</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2286.821675604366</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8372861187614133</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.28177e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-77.098</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.542966985438997</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8374179095309104</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.862952161601065</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.138637684016357</v>
+      </c>
+      <c r="L21" t="n">
+        <v>41.43146965288656</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.85672590772522</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.20976656362333</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-41430.59824245364</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-9.032058063514569</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.00000000008241e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8166769811266618</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.000000000000002e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8200016120837688</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2095.015</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2609.387980657328</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.14588e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-76.476</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4043484521157514</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.215962186150545</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.268641205323905</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.459481751572342</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28.40224004186938</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.59262550879092</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16.79540018822912</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-42442.00844638641</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-35.48125402217011</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000863e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8157917288676616</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1942.56</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9272296379739525</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2425.40398898164</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9294915156199423</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.15266e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-77.35899999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1031259032910742</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5158474768805559</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.708667559043178</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.769346542631169</v>
+      </c>
+      <c r="L24" t="n">
+        <v>26.87303368000161</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.73964791022215</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.55452244310214</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-41747.8505701392</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-11.16559098740117</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000002828e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8160709004996413</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1912.647</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9129514585814422</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2377.85022758425</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9112674102933702</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.15732e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-77.54600000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4003635143987926</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.035660664594701</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.24303048267201</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.877751060886731</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.2135071072412</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.95959426068042</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.8270890532893</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-44233.50237363524</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-8.790701626875943</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000001066e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8161112397314851</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1878.785</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8967883284845216</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2347.169937216722</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8995097527142932</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.16052e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.679</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2790848463037553</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9720057910622409</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.086357294667117</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.56070852187476</v>
+      </c>
+      <c r="L26" t="n">
+        <v>29.69027406821463</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.94337178722895</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.72697952821918</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-43419.10243874054</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-6.936345737706006</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8161415299526497</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1850.33</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8832060868299273</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2324.03202985588</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8906425748425633</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.16273e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.785</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1320005761776266</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5898788448772524</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.722435633099827</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.886422766226668</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28.25570876041729</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.91349190472587</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.54534117618882</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-42499.25624233932</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-7.271643790288408</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000667272e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8162417044935256</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1827.594</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8723536585656906</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2299.851137781693</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8813756922427226</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.16474e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.896</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1011488539538705</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9759825648127232</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.600592509802231</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.592813711548603</v>
+      </c>
+      <c r="L28" t="n">
+        <v>28.75840149040733</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.94667929210912</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.74730401950919</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-42562.09660949936</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-6.419550298626746</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8163743724006977</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1809.308</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8636253201051067</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2279.547409861099</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8735946615676757</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.16627e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.997</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.01113256244457741</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6932445030505685</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.565342913733387</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.05307304989934</v>
+      </c>
+      <c r="L29" t="n">
+        <v>29.12355275679124</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.99139012516692</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>19.02643126283851</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-42825.36712938253</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-7.011279207815505</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.0000000000008e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8165368433119899</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1786.477</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8527275461034887</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2255.903640112858</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8645336212304372</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.16757e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.092</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.08001167371406193</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8978201401428407</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.801134971614064</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.498852406745278</v>
+      </c>
+      <c r="L30" t="n">
+        <v>29.26161573876769</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.01787587563746</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.19572426526515</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-42825.61654719553</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-5.609640158611683</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8167168904194366</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1773.525</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.84654525146598</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2240.728684652006</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8587180983670916</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.16893e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.182</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5091193001696683</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9883547374671894</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.080962937004636</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.641231383331418</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.35913274757482</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.10495485611359</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.77413408734121</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-43856.38023846823</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-7.352361783305696</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8169165456261026</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1759.778</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8399834846051221</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2220.018429600299</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8507812736383711</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.16993e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-78.27500000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6287450907855094</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.555440802087011</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.182005324648082</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.696524026390361</v>
+      </c>
+      <c r="L32" t="n">
+        <v>31.67751904678535</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.13236369503805</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.96345561032832</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-43927.05484160499</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-6.418178133712445</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8171273304527732</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1726.409</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8240556750190334</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2199.349739771929</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8428603780177961</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.171e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-78.357</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.03797378536093708</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7404786995810581</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.504904605511882</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.689527057539915</v>
+      </c>
+      <c r="L33" t="n">
+        <v>28.60051469682928</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.00815885216461</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19.13326669055241</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-41567.38222781925</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-5.260199701773672</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.00000000000115e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8173456463765618</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1717.154</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8196380455509865</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2183.816981350035</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8369077337437233</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.17173e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-78.444</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.372339589765871</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.056167599638492</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.664232576800258</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.186092132764961</v>
+      </c>
+      <c r="L34" t="n">
+        <v>30.39833560627109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.11014508342402</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.80970922560326</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-42825.60024840761</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-5.982118681541351</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000045e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8175839800948166</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1695.56</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8093307207824287</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2166.00586620081</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8300819511152857</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.17268e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-78.527</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2241826537055487</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6995981196637117</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.613274581092191</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.60581834824017</v>
+      </c>
+      <c r="L35" t="n">
+        <v>28.97699599713805</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.06609018252058</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.51174235464678</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-41759.59065945874</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-5.548980320301325</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8178274353645306</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1678.577</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8012243349092966</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2148.07459573363</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8232101211689152</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.17331e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.608</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.152903171872562</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5410564601294139</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.468643521979724</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.897861082371155</v>
+      </c>
+      <c r="L36" t="n">
+        <v>29.18412697496073</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.08117010795162</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>19.61272435039211</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-41655.71686141488</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-5.335813366970342</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8180875736245282</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1662.797</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7936921692684779</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2132.772752567636</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8173459709239449</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.17404e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.69</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.07929164518249984</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7496777894488938</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.47934804324184</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.695175027802178</v>
+      </c>
+      <c r="L37" t="n">
+        <v>29.366564473248</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.10851731474619</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.79853835051375</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-41731.68655746619</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-5.681535053765629</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.818339884569883</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1651.177</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.788145669601411</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2116.076505014713</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8109474408177715</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.17489e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.777</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2834877170914586</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6880792967926237</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.677578895432414</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.570421953081238</v>
+      </c>
+      <c r="L38" t="n">
+        <v>29.7000588817853</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.1432633073413</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20.03975141950219</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-41939.70817145566</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-5.435644257572449</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000038e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8185987080568147</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1645.527</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7854487915360987</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2099.647836909023</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8046514556183796</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.17559e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.857</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6951035669063017</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.369238074906568</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.153683317268301</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.495228206445029</v>
+      </c>
+      <c r="L39" t="n">
+        <v>33.48863692569178</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.29865939470274</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.19440972404233</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-44235.07464291344</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-5.688766280204391</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000028196e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8188696057591242</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1624.622</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7754703426944438</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2080.865001169875</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7974532789277607</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.17626e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.937</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6085294471584232</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9320251544391329</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.763740913529393</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.11548786633966</v>
+      </c>
+      <c r="L40" t="n">
+        <v>31.66075856745751</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.24781104439947</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.80224386687447</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-42958.58507308229</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-4.837839971182348</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8191409326258356</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1611.732</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7693176421171209</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2067.000795952157</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7921400770120284</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.17692e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.024</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5506468406664737</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.006631604603938</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.968783456763452</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.219914874500947</v>
+      </c>
+      <c r="L41" t="n">
+        <v>32.12124618548355</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.27759628297817</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.03018535035652</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-43110.92731383773</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-5.856366540084082</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000001034516e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8194210955129446</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1587.974</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.757977389183371</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2047.031331749961</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7844871467654632</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.17784e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.09699999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3863404955666404</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8908644633863094</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.597349487633154</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.466298700158758</v>
+      </c>
+      <c r="L42" t="n">
+        <v>30.59816874889495</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.23330587556472</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20.69301389221734</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-41981.28002095004</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-4.364106859059007</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8197060794426098</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1571.216</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7499784011093</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2029.475608029705</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7777592382097436</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.17848e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.18000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.0255792381051713</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8619366017402794</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.712016492473449</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.872758600193317</v>
+      </c>
+      <c r="L43" t="n">
+        <v>30.71820629786453</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.25079846954695</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.82488345515663</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-41898.68804860903</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-4.081594128720326</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8200016120837688</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.000000000049884e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8195598352457896</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2016.385</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2479.894191432464</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.28058e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.84099999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.194163433587738</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6670985057724697</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.709193311379262</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.819686127346812</v>
+      </c>
+      <c r="L23" t="n">
+        <v>33.80561875811108</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.42018966566322</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.98442371709577</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-39134.88641109465</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-12.78612376913225</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8154757819674585</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2000.103</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9919251531825519</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2453.250779924927</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9892562305280669</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.27829e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.136</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4747294728314576</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.102091159869512</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.901047706145416</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.679641803997807</v>
+      </c>
+      <c r="L24" t="n">
+        <v>43.05627570807684</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.67330523273606</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.20367645339503</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-41876.94588019341</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-12.13161840626572</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.691142992723424e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.780967023409491</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1970.804</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9773946939696536</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2429.198699982328</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9795573973981317</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.27668e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.336</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1392105860737702</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8768134498366723</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.661150343777948</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.863944713813107</v>
+      </c>
+      <c r="L25" t="n">
+        <v>38.79208983319131</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.60482114697501</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.85587226052932</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-40550.86197859904</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-10.62870428195151</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000075494e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8155189922185858</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1940.552</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9623916067616055</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2403.624016816796</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9692445851604612</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.27571e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.52200000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2143551654566022</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.766405458812792</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.488153616138504</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.580953681497222</v>
+      </c>
+      <c r="L26" t="n">
+        <v>35.15027569081094</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.54534473807956</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.5649899633888</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-39380.50890870148</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-9.853932619949546</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000039e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8156234761308356</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1928.491</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9564101101724125</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2380.758319038969</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9600241523465037</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.27539e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.68300000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4885509323865456</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.020740679921186</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.294267129666909</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.910855980219346</v>
+      </c>
+      <c r="L27" t="n">
+        <v>48.97494706455098</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.84878892542856</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.16380919696649</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-43042.06978230023</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-10.24040802136619</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8157785700358812</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1888.034</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9363459855136792</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2354.017136727689</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9492409574813094</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.27534e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-76.839</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.08132073954127679</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6970211513684268</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.574008974242742</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.635225204086892</v>
+      </c>
+      <c r="L28" t="n">
+        <v>36.58997116610398</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.64711581006519</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>17.06899463426671</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-39778.55145872511</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-9.428473208929518</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000028039e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.815958463414011</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1866.716</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9257735997837715</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2330.803761323619</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.939880326094588</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.27533e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-76.98399999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5503181036311141</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7586991216008276</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.505824045544018</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.714998155504976</v>
+      </c>
+      <c r="L29" t="n">
+        <v>37.04345048996161</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.68626034326493</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17.271085563754</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-39845.88477792585</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-10.17951251325439</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000346e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8161565733378053</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1841.636</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9133354989250565</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2305.05534738265</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9294974581359774</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.27576e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.122</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.248076773120728</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8228164088986888</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.530265305268447</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.704399840750741</v>
+      </c>
+      <c r="L30" t="n">
+        <v>37.57168347329423</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.73805912349943</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>17.54595370870052</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-40088.36449265295</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-9.44362916666887</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.816367191251169</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1819.354</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9022850298926047</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2281.757345404817</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9201027016748657</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.27601e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.26000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.283092877129246</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6324421221654721</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.558016361027063</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.579758735041262</v>
+      </c>
+      <c r="L31" t="n">
+        <v>38.33538168701444</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.78336861665026</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>17.79363728008729</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-40265.93407313389</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-9.303428750424246</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8165838324755447</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1799.848</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8926112820716282</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2258.286477174793</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9106382381057704</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.27635e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-77.39400000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1232250051749076</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9452559549712601</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.892889993227141</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.681253005050837</v>
+      </c>
+      <c r="L32" t="n">
+        <v>38.86940340644297</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.84233742792398</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18.12662325465679</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-40641.36749474185</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-8.887005696815095</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000097e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8168057218030972</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1776.233</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8808997289704099</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2235.949161476587</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9016308716724053</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.27662e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-77.511</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3395658066756795</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8852471682783654</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.53324140218562</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.599496307331837</v>
+      </c>
+      <c r="L33" t="n">
+        <v>38.90562008065035</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.86972303195957</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.28552636377845</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-40608.09838101802</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-8.823435501180711</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000002822e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8170357128606585</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1750.01</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8678947720797368</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2214.682336367256</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8930551730870369</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.27724e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-77.63</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.143103732856886</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.033791853624912</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.553374370983815</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.197847100359748</v>
+      </c>
+      <c r="L34" t="n">
+        <v>35.46209488087393</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.79657569852306</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17.86715096361677</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-39215.834981334</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-8.374170187295704</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000004689e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.817267568166834</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1743.236</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8645352945989977</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2195.23711083496</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8852140217994233</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.27747e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-77.74299999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6867834704656951</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.142718263417642</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.112321836629423</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.222110741927112</v>
+      </c>
+      <c r="L35" t="n">
+        <v>46.26837202526865</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.04622717891026</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.38030285596263</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-42415.60652058148</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-8.6885814230086</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000004463e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.817498530694392</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1717.85</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8519454370073176</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2173.732934371751</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8765426129395204</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.27769e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-77.85599999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3070810280766944</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.945461239627484</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.864621360776083</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.882192974311684</v>
+      </c>
+      <c r="L36" t="n">
+        <v>40.84405486143866</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.96987243117405</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>18.89107024091491</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-40865.63523803785</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-7.764426326025841</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000034587e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8177484728990478</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1702.134</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8441512905521515</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2156.128351946541</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.869443688120054</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.27797e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-77.95399999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2764510935659455</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8584474492437424</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.732304512806591</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.703316406116046</v>
+      </c>
+      <c r="L37" t="n">
+        <v>41.29586192612239</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.00801075613096</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.1323179176302</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-41060.15352908917</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-7.948780329537612</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000083e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8179983119206899</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1685.086</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.8356965559652545</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2139.432459428366</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8627111861545042</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.27819e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.054</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4129723848099105</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9930463655975794</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.868847711609742</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.669374340653552</v>
+      </c>
+      <c r="L38" t="n">
+        <v>41.7331518553174</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.04735833237801</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>19.38774059540615</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-41297.60757870334</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-8.317387800409733</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000036812e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8182425081455851</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1664.727</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.8255997738527115</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2121.345128741882</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8554175964727461</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.27815e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.15300000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2799956614230413</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9266123712229771</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.492119513334114</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.626126002821499</v>
+      </c>
+      <c r="L39" t="n">
+        <v>37.38913629774545</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.97995825622959</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>18.95427703845301</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-39955.25431451828</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-7.794141313475393</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000518e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8185019954625765</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1643.39</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.8150179653191231</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2103.104795671351</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8480623096489985</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.27844e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.249</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1329113333557849</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6156678325618595</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.086166729616057</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.973528992268247</v>
+      </c>
+      <c r="L40" t="n">
+        <v>34.42789423791547</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.90422215506818</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>18.48970275058602</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-38582.23345171555</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-6.460712568734152</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000129e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8187606006791117</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1634.587</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.810652231592677</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2089.555920189802</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8425988203080592</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.27864e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-78.337</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.03525333069189232</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9453581139107263</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.464975822075341</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.397735650134339</v>
+      </c>
+      <c r="L41" t="n">
+        <v>38.46258477845766</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.03502287608852</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>19.30693678333607</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-40108.84850815025</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-7.33649383849388</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8190213597313608</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1622.423</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.8046196534887931</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2459.74740527466</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9918759492935597</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.27859e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-78.43600000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5548289363493469</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.781478476044307</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.590893656929183</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.43492517675447</v>
+      </c>
+      <c r="L42" t="n">
+        <v>39.03253939354724</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.06902628940732</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>19.53132246120225</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-40293.17597285898</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-188.6320827278544</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000289402e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8192920096820018</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1611.734</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7993185825127641</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2058.438589014465</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8300509739995994</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.27857e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-78.52200000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6468039654194114</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.197533273761979</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.89195225538363</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.208686475502759</v>
+      </c>
+      <c r="L43" t="n">
+        <v>44.23170969233752</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.18324832877551</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.32469315436298</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-41759.07643624504</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-6.536349413300854</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000049884e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8195598352457896</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.000000000000004e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8199776686689161</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2497.835</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3091.523979059744</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.24795e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-71.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.351712089447939</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5346525096525196</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.358868894601456</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.891891045710701</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.92521170774455</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.77518067147459</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.93566498503863</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-31695.46634223383</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-83.68906570236823</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000001433e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8176324688964132</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2127.574</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8517672304215451</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2619.666071168149</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8473704518911395</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.27591e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-74.598</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2604726081155406</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8682925588597629</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.843003209222122</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.283966450167652</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.72230928969712</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.8311535793419</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.71953521039776</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-34693.27933809021</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-35.83622629720139</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8186304488560482</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2029.177</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8123743161577927</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2491.699252350716</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8059776567246751</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.27491e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-75.431</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3405891629510262</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7570740741950369</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.624819355432402</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.937162563780081</v>
+      </c>
+      <c r="L14" t="n">
+        <v>26.22588634253819</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.09618173693333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.65413773417267</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-35722.08121465044</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-18.21960180088513</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000494e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8188392396729105</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1985.279</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7947998967105514</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2439.699408634877</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7891575239784773</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.27115e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-75.86799999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.09281359806952362</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6248765585282292</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.673313312434118</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.943416987370702</v>
+      </c>
+      <c r="L15" t="n">
+        <v>28.55264525426246</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.27872389887898</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.37515397966675</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-36866.3705112435</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-14.08549137406794</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.818931678424702</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1948.283</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7799886701883831</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2402.257781422677</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7770464656571414</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.26829e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-76.175</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3252507702836441</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6702863792720708</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.334154849460684</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.498736115110913</v>
+      </c>
+      <c r="L16" t="n">
+        <v>27.39637737286728</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.29693210589024</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.45096703617956</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-36471.81292042318</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-11.90375683121238</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8190300039319343</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1931.672</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7733385111506564</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2371.196060234237</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7669990840424964</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.26654e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-76.435</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6031141791312884</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.361318890316561</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.142103666731459</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.676917197283583</v>
+      </c>
+      <c r="L17" t="n">
+        <v>35.25966877663292</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.60718310888254</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.86763424158514</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-39602.55460301263</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-11.87808188723511</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.94122543945176e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.7739560161413798</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1893.567</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7580833001379195</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2338.785670011248</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7565154551130367</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.26435e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-76.666</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2782517778857684</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8560230663468272</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.730144211991121</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.025694554913239</v>
+      </c>
+      <c r="L18" t="n">
+        <v>32.56882469018585</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.58337727919802</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.7498303194033</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-38731.29715043544</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-10.31986273665984</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8193195411474939</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1851.347</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7411806624536849</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2308.799670107878</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7468160317521056</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.26406e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-76.863</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.209247147859762</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4898523840610475</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.350900677888602</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.341463337810215</v>
+      </c>
+      <c r="L19" t="n">
+        <v>27.90564934737897</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.42852888923302</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.02184381881267</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-36386.84426795913</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-9.617180345565203</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000231054e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8195179577502167</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1839.816</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7365642646531898</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2282.346072110789</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7382592169978709</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.26383e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-77.05</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3554047557858076</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.065682989103138</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.115374416730028</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.19396444985413</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34.40010693709632</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.71544148268364</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.42486898241969</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-39367.70994830685</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-10.64863277401219</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000215072e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.819741044798654</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1806.465</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7232123018534051</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2251.932331115641</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.728421434337554</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2639e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-77.214</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2396836215717126</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8212276295098015</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.65852005091707</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.728566689720725</v>
+      </c>
+      <c r="L21" t="n">
+        <v>31.84643536872823</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.6650937504582</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.16122066654443</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-38233.57053699046</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-8.793329743298045</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8199776686689161</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.000000000004667e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8254646451709602</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1899.203</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2402.472779376992</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.30997e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-62.577</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09828268689513774</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7616029056828015</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.078156139971908</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.887470264740475</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3.540827423535551</v>
+      </c>
+      <c r="M23" t="n">
+        <v>73.45804965490171</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.366889073765473</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7394.454779681775</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-24.45558848479277</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000040855e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8193011799911082</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1850.708</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.974465604782638</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2359.444383607993</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9820899549254595</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.26476e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-65.34699999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07077816799164052</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5862023396974281</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.462658255783064</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.416665106777531</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.229822125904165</v>
+      </c>
+      <c r="M24" t="n">
+        <v>75.57068894449941</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>3.886487644215192</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8459.62206740124</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-22.58012983210915</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000001799e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8196078125782346</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1829.823</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9634688866856257</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2318.733958776364</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9651447369895516</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.22903e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.461</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2051452341700901</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8918816129602155</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.531562759830749</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.377326985851015</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.726290479791841</v>
+      </c>
+      <c r="M25" t="n">
+        <v>77.30774954570983</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>4.440150068679038</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9623.180604717325</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-22.63677971584116</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000094228e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8199153253866724</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1766.049</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9298895378745718</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2271.419482458736</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9454506631487244</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.20005e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-69.122</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.02790397103786388</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6694233187989301</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.300299990918514</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.437635894679349</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5.324860777640135</v>
+      </c>
+      <c r="M26" t="n">
+        <v>78.40122813074431</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4.872150334765174</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10357.19282243696</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-19.44487124420402</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001134e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8202081499390663</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1732.083</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.912005193757592</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2232.418843108765</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9292171225713846</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.17614e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-70.48099999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1703525666696599</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6356889912352495</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.448334753129535</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.581733133281594</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5.87607783700206</v>
+      </c>
+      <c r="M27" t="n">
+        <v>79.41318029601423</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>5.35025935181079</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-11237.11769570434</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-18.85931320954887</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000003405e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8205028790290346</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1709.977</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9003655744014728</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2193.008499456727</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9128130475740154</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.15564e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-71.61499999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3468692571341039</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7992433087307012</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.466827841876408</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.381558727541909</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6.297198166494563</v>
+      </c>
+      <c r="M28" t="n">
+        <v>80.33088549594437</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.869289364400495</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-12235.65279251055</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-17.30684354613345</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000082604e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8208088214209822</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1678.77</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8839339449232125</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2158.098886597347</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8982823468896844</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.1381e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.572</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3559432753220502</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9029088367543165</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.842867295771248</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.460246614094649</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6.809432899368176</v>
+      </c>
+      <c r="M29" t="n">
+        <v>81.02085763252262</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6.328661487669448</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-13039.19299753835</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-16.5603167023703</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.00000000003338e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.821104107191778</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1643.45</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8653366701716457</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2124.516358831063</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8843040291936178</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.12286e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-73.383</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4061000737413815</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9607490568131309</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.890969493454323</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.31893544742964</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.544806418161984</v>
+      </c>
+      <c r="M30" t="n">
+        <v>81.5544416450562</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>6.734926037722675</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-13681.61296526258</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-15.00430680658155</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000182e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8214009304057527</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1617.987</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8519294672554751</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2096.00610802685</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8724369849344912</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.10946e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-74.098</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3574589822946755</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.174132230665793</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.042499321019899</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.345018449643465</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8.072520674758248</v>
+      </c>
+      <c r="M31" t="n">
+        <v>82.06296280385537</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.172551828871325</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-14416.93606936701</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-14.77080443740329</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000040989e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8216952007464622</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1585.458</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8348017563156758</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2069.112969791886</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8612430440641444</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.09743e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-74.703</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.159299162903933</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9348794798731803</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.88919938055293</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.177263910844529</v>
+      </c>
+      <c r="L32" t="n">
+        <v>8.455125735459037</v>
+      </c>
+      <c r="M32" t="n">
+        <v>82.44174116019333</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.536529441977306</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-14959.17237644951</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-13.71419932620643</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8219854515502615</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1565.023</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8240419797146488</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2045.990564412652</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8516186247667779</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.08665e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-75.248</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2818989704902979</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9796848400953101</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.024466056910844</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.302292843004511</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.940381589777905</v>
+      </c>
+      <c r="M33" t="n">
+        <v>82.82501076003599</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.94370037160085</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-15620.6470556805</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-13.81215499341772</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000459538e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8222867300141146</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1544.104</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8130273593712731</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2023.329528870726</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8421862450385037</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.07698e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-75.712</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1445195712622094</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9964225549353219</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.90034700930518</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.341532147649316</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.392634698903572</v>
+      </c>
+      <c r="M34" t="n">
+        <v>83.14070009546953</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.313062941192261</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-16202.69067657345</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-12.81800768093171</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000332e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8225974640222026</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1533.734</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8075671742304535</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2006.906740986025</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8353504598318303</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.0681e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-76.13800000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5109715658727142</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.280810961529238</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.338564743009697</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.898628342599343</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9.971522821040548</v>
+      </c>
+      <c r="M35" t="n">
+        <v>83.47313745807372</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8.740451955515589</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-16933.63222417414</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-13.75869071735269</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000271805e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8228930558337284</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1509.959</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7950487651925571</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1986.190960958863</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8267277689922136</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.06005e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-76.535</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3079482834051703</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.02901282246354</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.080629440570107</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.429391222295253</v>
+      </c>
+      <c r="L36" t="n">
+        <v>10.30814208468092</v>
+      </c>
+      <c r="M36" t="n">
+        <v>83.70982217498826</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.072145225865652</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-17399.93435001546</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-12.60237205899114</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000001017256e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8232082846873828</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1491.532</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7853462742002831</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1968.246259098893</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8192585056507062</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.05279e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-76.875</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2232806569564605</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8083771709602533</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.965184303090051</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.085782893982667</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10.60354919654724</v>
+      </c>
+      <c r="M37" t="n">
+        <v>83.90195612293191</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.36025993347933</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-17780.21772305097</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-12.0169102615605</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000254311e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8235093953344125</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1481.609</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7801214509454756</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1953.796952040739</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8132441577745565</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.04601e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-77.181</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3291835035346856</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.239683973528461</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.186628463024579</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.524495949682303</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11.13585691283479</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.14449794891284</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>9.750857716675728</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-18432.76049437571</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-12.37171701257523</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000057361e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.823833526716292</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1459.053</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7682448900933708</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1937.882278648168</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8066198690295667</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.03995e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-77.462</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1400064075823448</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6469150326797338</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.801147583736497</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.855228063291323</v>
+      </c>
+      <c r="L39" t="n">
+        <v>11.26177529320516</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.25873709399208</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>9.946223720501369</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-18590.34975627036</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-11.69699911509042</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000059156e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8241433372471451</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1451.259</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7641410633829033</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1923.143120026599</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8004848739744337</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.03445e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-77.717</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3362170438938402</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.083205160999825</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.069666852391792</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.270577796676044</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11.77426459771022</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.46349994238881</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.31650625074802</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-19198.0121281137</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-11.392384989025</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000004698e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.824472087062335</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1428.427</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7521191784132608</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1910.171068057466</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7950854155162629</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.0294e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-77.94799999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0727942817379712</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6197745946682452</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.782346509260883</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.350902416540029</v>
+      </c>
+      <c r="L41" t="n">
+        <v>11.84755259556691</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.54481336644989</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10.47123543689568</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-19274.71448398443</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-11.32520603654621</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000241999e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8247862378301662</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1422.202</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7488414877187958</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1895.16250084569</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7888382824204747</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.02476e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-78.15300000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1371498733023936</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7819557533516355</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.735665174115177</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.929247007000049</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.27745721386311</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.70810079069841</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10.79626854335203</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-19784.15357346259</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-10.59612056484127</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000523e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8251300850646156</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1421.031</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.748224913292576</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1881.33410591099</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7830823816446557</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.02064e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-78.36199999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6118407143698689</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.283535086177792</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.242561983970486</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.730252570759999</v>
+      </c>
+      <c r="L43" t="n">
+        <v>12.93574989817571</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.90798416109189</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.22244219281164</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-20508.20360593375</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-10.63608271900614</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000004667e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8254646451709602</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8175394345116048</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2633.046</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3337.131521250853</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.06066e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-68.13500000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.03323529411764239</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5329512893983199</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.040393667094533</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.646461735510718</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.115095997461773</v>
+      </c>
+      <c r="M12" t="n">
+        <v>80.04099918911723</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.695109309334024</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-17003.7804559832</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-114.4057408423034</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000003729e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8153311125924353</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2117.304</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8041272351489492</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2669.781762564069</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8000229375326982</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.06208e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-74.447</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.09072677934034948</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7766287201793104</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.539887881209698</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.036479106934163</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11.2068029139813</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.10238482167318</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.680740778241681</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-24412.2281274665</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-42.87701412982778</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8164793472096545</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2005.532</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7616775400049981</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2508.830496320964</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7517925141232019</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04516e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.376</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.006214192682343294</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7199004900552514</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.574285941957029</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.677150142644777</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.73929516339864</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.36411992149205</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.33222001801092</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-29857.0041688394</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-20.42677618114658</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000001367e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.816662360779307</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1958.687</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7438863582330124</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2453.032722627263</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7350722340448229</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.03513e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-77.25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.04535874625506804</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9479411596577552</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.442507000543924</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.760958915287476</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17.45263507456779</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.96138567476852</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.16348612858299</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-33763.96624746999</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-15.24418159126208</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000001214e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8166529721515329</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1926.158</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7315322254149758</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2417.460586721224</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7244127393022525</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.03004e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.761</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2312135216452247</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.029093103977876</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.704303430190909</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.007237105857376</v>
+      </c>
+      <c r="L16" t="n">
+        <v>19.46884776122788</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.29606168709921</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.44732595469001</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-36400.09492190822</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-13.80283284922848</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8166752976051159</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1904.402</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7232695516903237</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2385.935742247541</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7149660500504409</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.02787e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-78.12</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6491779029721033</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.112004246251603</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.254264922955687</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.585852162641555</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.66769371779804</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.58269874209907</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.74649658596935</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-39140.92978270056</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-12.47212407541338</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000001774e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8167686746850028</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1874.635</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.711964394089583</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2354.111895182209</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7054297621149255</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.02807e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-78.396</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4446433033262315</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.03047810737575</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.159218905806052</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.720878315563495</v>
+      </c>
+      <c r="L18" t="n">
+        <v>23.07699888230249</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.74667569071333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.59252534455447</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-40636.05799411037</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-11.66368739690847</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000055239e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8169304140449013</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1830.542</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6952183896521368</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2321.483878571405</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6956524978977291</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.02836e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-78.63200000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0768541015609565</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7127548916280178</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.902331487485214</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.616194317281392</v>
+      </c>
+      <c r="L19" t="n">
+        <v>22.83192782000825</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.76097448571575</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.67035499512051</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-40135.13670245658</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-10.37980604267159</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000045479e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8171093812715161</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1809.123</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6870837045763728</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2291.538330595826</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6866790583479586</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.02979e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.822</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2981907175878466</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9032201191637206</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.89304867273694</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.496090710654481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>24.43064060720236</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.91784436976786</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.57158067210354</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-41779.69062934875</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-10.28635683947459</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8173120931724253</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1784.224</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6776273563014091</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2264.378754705122</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6785404591594782</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.03194e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.998</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5386269788962353</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.093624007962492</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.299923682823214</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.380605833319633</v>
+      </c>
+      <c r="L21" t="n">
+        <v>25.37458953308474</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.01672316109487</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>19.18829377474301</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-42674.75409014634</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-10.71658026505543</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8175394345116048</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.000000000034616e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8221202952507087</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1998.283</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2601.596118931273</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.57842e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.52500000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2752556759131756</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8738438933436339</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.258277039167286</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.978384527812829</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10.38699743355181</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.45804501702681</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.720111820521359</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-21153.51643436788</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-59.32452775237402</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000429e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8170800878527218</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1933.762</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.967711780563614</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2528.668171088214</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9719679979100607</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9.448459999999999e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.194</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.34125152597249</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.006189172385059</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.835071799875098</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.955126100229385</v>
+      </c>
+      <c r="L24" t="n">
+        <v>12.07052166666573</v>
+      </c>
+      <c r="M24" t="n">
+        <v>83.7692368297954</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.159350156905285</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-21692.06069299027</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-51.20981498750893</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000109e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8171699025327676</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1906.504</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9540710700136067</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2497.725800044699</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.960074387361385</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.401880000000001e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.426</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2897065712944905</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.952688158111617</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.769378983903508</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.982383950829181</v>
+      </c>
+      <c r="L25" t="n">
+        <v>12.2283898656731</v>
+      </c>
+      <c r="M25" t="n">
+        <v>83.88109535025947</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.328105944688248</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-21827.75625252727</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-51.85991924900031</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.817286867446649</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1879.386</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9405004196102356</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2450.335891922904</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9418586820960871</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9.375e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.62</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2784728491911144</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9484133574272525</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.865205005101297</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.121437656206457</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12.37299735721171</v>
+      </c>
+      <c r="M26" t="n">
+        <v>83.97626890675576</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.476605675421231</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-21923.51170903886</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-43.75589167110365</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000238e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8174671550524111</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1846.948</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9242674836347003</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2408.396956392696</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9257382184987488</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.35872e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.804</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2887792939535761</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8608184478155398</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.769491461449418</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.792931833817793</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12.15265269469043</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.0100665319235</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.530471455674709</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-21745.04189984535</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-37.39004388099215</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000001092429e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8176950499965467</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1820.943</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9112538113970843</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2374.461149562192</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9126939928468266</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.35006e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-76.967</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1976087673160707</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9967828845401603</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.653806226773447</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.77575285691956</v>
+      </c>
+      <c r="L28" t="n">
+        <v>12.27558872343377</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.09830283809207</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.673997424453326</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21832.57958975694</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-34.46105159774174</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000113e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8179413635802457</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1788.521</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8950288822954506</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2341.87197598091</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9001673852984308</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.34184e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.126</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1463057955242794</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.856438485434916</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.719302940828131</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.638636263935107</v>
+      </c>
+      <c r="L29" t="n">
+        <v>12.11917066239051</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.11414152123977</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.700214685389138</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-21596.55056860856</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-31.23881148430792</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000038399e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8182121173767615</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1766.023</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8837702167310637</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2313.243995017108</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8891633786597825</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.3349e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.28100000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1682067765033459</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6027132807923332</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.567620268735897</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.478623539342166</v>
+      </c>
+      <c r="L30" t="n">
+        <v>12.27617286274879</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.20301444750847</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.849971030126577</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-21717.16180044214</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-29.16464677039153</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000263e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8184951795438188</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1745.827</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8736635401492181</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2287.083206264449</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8791077099253881</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9.32978e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.426</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2638759593495467</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8460017919454449</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.659374231115234</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.804038992718056</v>
+      </c>
+      <c r="L31" t="n">
+        <v>12.42129076838562</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.28788042574816</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.997309940605348</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-21832.00522023965</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-28.0557078394811</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000204752e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8187806748227648</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1732.728</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8671084125721933</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2264.399898860699</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8703887134452315</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.32597e-08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-77.56100000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2703651978947011</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9339526706017143</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.843266510795637</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.99821834362161</v>
+      </c>
+      <c r="L32" t="n">
+        <v>12.89544509940919</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.41238414287929</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10.22153753297494</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-22181.03649170305</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-27.5017219736917</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000681719e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8190555621016918</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1705.893</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8536793837509502</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2240.331215751889</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.861137207058953</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9.31941e-08</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-77.68000000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.272702464986374</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8516656219295848</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.700321886216652</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.823896425598233</v>
+      </c>
+      <c r="L33" t="n">
+        <v>12.68976922571673</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.41609917966559</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.22838134125219</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-21937.96182038993</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-25.5679819946281</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000252437e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8193113550764618</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1698.88</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8501698708341112</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2221.561860263089</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8539226531348374</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.315040000000001e-08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-77.804</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2432533855233023</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9811496632182641</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.885274537030452</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.185695933084879</v>
+      </c>
+      <c r="L34" t="n">
+        <v>13.161686605499</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.53410750147854</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.45060117301336</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-22299.46689124181</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-25.52704876218831</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000231679e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.819588945908863</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1672.98</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.837208743706472</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2202.1507186429</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8464614098315676</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.3097e-08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-77.917</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2088343137697278</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9405279858098018</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.631914700329005</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.718176772366594</v>
+      </c>
+      <c r="L35" t="n">
+        <v>12.95295012753672</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.54168297740989</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.4651936411462</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-22091.47418929515</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-24.78749577952726</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000007411e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8198538157558599</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1651.699</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8265591009881984</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2181.612758632526</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8385670407321811</v>
+      </c>
+      <c r="F36" t="n">
+        <v>9.30356e-08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.027</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1539535727695503</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7461654873667664</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.57912517488274</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.428835808229914</v>
+      </c>
+      <c r="L36" t="n">
+        <v>12.8050435640045</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.55528078569466</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.49148834252562</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-21924.61462688688</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-23.4224664842352</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000012506e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.820117022014795</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1640.956</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8211829855931319</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2166.823748938552</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8328824498049588</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9.29782e-08</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.13200000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2858722662231373</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8422743896107837</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.804580163022474</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.798510379591264</v>
+      </c>
+      <c r="L37" t="n">
+        <v>13.18660702381656</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.65271676541001</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10.68380529942918</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-22212.93677855975</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-24.10993115064389</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000008694e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8203806527482911</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1628.318</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.8148585560703865</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2147.093157636849</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8252984166192819</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9.29285e-08</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.22799999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1952876557735781</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9575754935998457</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.806523278271809</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.893537039049648</v>
+      </c>
+      <c r="L38" t="n">
+        <v>13.29637268490651</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.70259433701786</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.78498211860076</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-22258.458195896</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-23.22408929195558</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000010991e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8207189152318026</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1598.847</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.8001103947739134</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2125.812382969054</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8171185248547842</v>
+      </c>
+      <c r="F39" t="n">
+        <v>9.29393e-08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.321</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1674167759634101</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5515399556758261</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.476307558152973</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.254327644549057</v>
+      </c>
+      <c r="L39" t="n">
+        <v>12.86616697538675</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.64603379665971</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10.67039167623514</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-21725.98098129785</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-20.90932623761319</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.00000000003205e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8209876267237027</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1583.89</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7926254689651067</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2106.606947101653</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8097363506088869</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9.289809999999999e-08</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.41800000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.05240661942094939</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6821530609324619</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.384632971425122</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.17139615298087</v>
+      </c>
+      <c r="L40" t="n">
+        <v>12.97531977791049</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.69457329624034</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.76858341444017</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-21762.47927966942</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-19.69337803885537</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000366e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8212695826713596</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1574.268</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7878103351727459</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2094.431339423107</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8050562976252793</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9.28614e-08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-78.514</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1443545867623132</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.01683993127507</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.654138553702395</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.616527856109052</v>
+      </c>
+      <c r="L41" t="n">
+        <v>13.34168565550203</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.79348366567947</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10.97432181109442</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-22071.43666722395</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-21.58169867170113</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000751e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8215462268639109</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1560.491</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7809159163141557</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2078.02222180029</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7987489705565576</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9.2822e-08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-78.59999999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1900543335885306</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8466804075772832</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.57034902983026</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.646454359194162</v>
+      </c>
+      <c r="L42" t="n">
+        <v>13.41818418369149</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.82866510632823</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>11.04939312167336</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-22052.73214628453</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-21.33359570537925</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000052846e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8218357846702239</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1544.898</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7731127172677745</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2059.365993520303</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7915779004030354</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9.27903e-08</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-78.684</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2886238425663464</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9033020761400803</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.673273219257798</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.596829312972383</v>
+      </c>
+      <c r="L43" t="n">
+        <v>13.48579011402794</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.86466674483461</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.1272765403254</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-22035.20524721704</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-20.17938823860675</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000034616e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8221202952507087</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.817183405243335</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2510.091</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3169.462621307963</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.08446e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-69.045</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3282519128899155</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4745549738219638</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.406175059952042</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.327945555082893</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.570073520712516</v>
+      </c>
+      <c r="M12" t="n">
+        <v>80.73721974616664</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.131609207638706</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-17632.54020588438</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-99.11731560051226</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000008346e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8146441018578838</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2098.634</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8360788513245138</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2620.437008522798</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8267764355086179</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.06218e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-75.702</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2747326961679309</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.053371435186905</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.203422194001293</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.878288145950755</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.82212803326438</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.28228895460036</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.1173670028781</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-30470.53300919475</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-32.94367551427808</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000003499e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8159917055448808</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1996.765</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7954950637247813</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2486.381938975858</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7844806000424723</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04858e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-77.483</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.06691848804571922</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9825703387453746</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.050678709553928</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.443859330279585</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.10825284867704</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.43391916616659</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.04612428919839</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-38878.02805081943</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-16.54039832356375</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8162090927494554</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1939.945</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.77285843421613</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2427.419186576688</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7658772090440206</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.04557e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-78.26000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1585903117301093</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.920541679164488</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.71063238095848</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.117307654668878</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.50599786847739</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.88917099067753</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18.40006900872297</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-43691.14923864724</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-11.73235005199444</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000004966e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8162584938880966</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1902.441</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7579171432430141</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2386.082002829102</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7528348770506788</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04766e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-78.70399999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2557441835726451</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8920178745492362</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.678978948650969</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.186563895992851</v>
+      </c>
+      <c r="L16" t="n">
+        <v>29.49326071477693</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.17527610992676</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>20.26723810843348</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-47442.44694915169</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-10.02109527182461</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.0000000001712e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8163215401654593</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1878.83</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7485107113646479</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2350.951735659923</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7417508948850579</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.05223e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-78.97199999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7751065582185139</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.296322420044849</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.293963779076286</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.784245072124547</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34.07934373742279</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.40124002427947</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22.03223232509919</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-50997.17662337609</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-10.01356729736403</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000002247e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8164255107216594</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1840.52</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7332483164952985</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2313.54875351193</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7299498463740149</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.05818e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-79.18000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8220000234391124</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.266504796533109</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.31384566685294</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.035243654466353</v>
+      </c>
+      <c r="L18" t="n">
+        <v>36.86370558174956</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.51565192774606</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.04824694090664</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-52612.93724515766</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-8.563113488268982</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8165961113650829</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1795.989</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.715507525424377</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2279.034677935123</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7190602793714661</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.0646e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-79.351</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.000533340677953229</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7218626016830588</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.551734041007746</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.755654836899503</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.97973420230609</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.45931338250887</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>22.53651434714319</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-50504.57157258208</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-8.29545215988469</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000024128e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8167803308257643</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1770.163</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7052186554192656</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2245.862421828817</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7085940710359293</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.07121e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-79.485</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2315240271075035</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.046114567747623</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.611517431102326</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.268281906905949</v>
+      </c>
+      <c r="L20" t="n">
+        <v>38.76723528088041</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.60017302396662</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>23.86099942852023</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-52924.02082403241</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-6.803920218406802</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000010473e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.816979169562252</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1745.434</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6953668213622535</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2217.077919413407</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6995122468106191</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.07777e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-79.614</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4176678509650156</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.032178646042464</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.959736747386208</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.672823096138819</v>
+      </c>
+      <c r="L21" t="n">
+        <v>40.60450106713367</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.66655849222002</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>24.54061881906125</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-53765.86962565793</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-6.838992010465518</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.817183405243335</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>1.000000000000613e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8212019332917957</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2112.176</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2661.268115927172</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.12216e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.479</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01459818192057035</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7843182501984999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.473100244793213</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.864628262350316</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.72544786090992</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.55801376568304</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.87283182847432</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-32628.33277405092</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-44.113541149502</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000016e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8164130298239989</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1985.796</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9401659710175668</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2464.625772459143</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9261095331615922</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.08974e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-77.91</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2852022569977062</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.976256923290896</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.69723827600437</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.386750131070586</v>
+      </c>
+      <c r="L24" t="n">
+        <v>29.41541545467047</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.01869226000765</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19.20099021711397</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-46331.83728125821</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-13.6836321683802</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000006568e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8167065647458969</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1948.864</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.922680685700434</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2416.267751691378</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9079384888844855</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.08961e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-78.289</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5956303474934135</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.131043270143834</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.13368993283181</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.284043524765971</v>
+      </c>
+      <c r="L25" t="n">
+        <v>34.72600850162941</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.29918540887293</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21.19854369776972</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-50460.77652652798</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-10.32660639111828</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000103e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8167515396757253</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1910.186</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9043687647241517</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2384.886643696645</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8961467014253701</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.09131e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-78.46299999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2186491142607339</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5557849035218243</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.647142043977808</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.989378216992125</v>
+      </c>
+      <c r="L26" t="n">
+        <v>32.21264936371034</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.22868639762271</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>20.65846716980608</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-48376.39602861545</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-9.12439117228314</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8168150122545582</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1896.16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8977282196180623</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2356.697200173931</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8855542160782512</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.09354e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-78.617</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7004861922642784</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.282758413169379</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.683304026240483</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.417028269304212</v>
+      </c>
+      <c r="L27" t="n">
+        <v>37.82580566467998</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.4464775306823</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>22.42308050132992</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-52222.31034223757</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-8.669674996824142</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000412e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8169349031679062</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1856.954</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8791663194733773</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2331.259182121273</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8759956083226416</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.09563e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-78.754</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.178904364539893</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9668409934956337</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.897286768666898</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.181105565122921</v>
+      </c>
+      <c r="L28" t="n">
+        <v>34.36444895627479</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.34289911308397</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>21.54780776770696</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-49409.95767648036</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-8.300917448193331</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8170880359488286</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1835.395</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8689593102089977</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2304.105579943724</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8657923514560975</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.09764e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.871</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1875788963649715</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7727692712609656</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.705178506442147</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.057269809859197</v>
+      </c>
+      <c r="L29" t="n">
+        <v>35.01134848913876</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.39173444736568</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>21.95182750864125</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-49827.06997530271</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-7.471787911480533</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.00000000021995e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.81727606034416</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1809.848</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8568642007105469</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2279.083609792955</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8563900781560049</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.09962e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.995</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1984586395792218</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6108531505405014</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.617097081587966</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.141242047260463</v>
+      </c>
+      <c r="L30" t="n">
+        <v>36.06041067582967</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.4350536058772</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>22.32307846666766</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-50164.76515232034</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-7.142333804466034</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000058091e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8174811092270026</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1791.046</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8479624803993606</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2257.916155774577</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8484361805792464</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.10124e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-79.107</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1627757475292828</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8158418787450992</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.990506142132369</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.053935758469916</v>
+      </c>
+      <c r="L31" t="n">
+        <v>36.77464044963155</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.47838622652074</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>22.70719761867609</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-50547.52303501256</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-7.964941257007922</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000053324e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8176967688679421</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1769.216</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8376271674330169</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2232.142800629823</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8387515663194111</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.10288e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-79.20999999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3795029295029077</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8920816479133088</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.765145370883507</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.53370399283537</v>
+      </c>
+      <c r="L32" t="n">
+        <v>37.41929287696064</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.5136861120926</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>23.03000086713526</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-50785.13580091142</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-6.112649501903206</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8179342730306878</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1740.558</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8240591693116482</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2211.974502328334</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8311731122054545</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.10439e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-79.315</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1221528593256752</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.712269772537787</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.605058834299211</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.922214100421593</v>
+      </c>
+      <c r="L33" t="n">
+        <v>36.04157715384267</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.47477935649151</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>22.67472210390794</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-49418.88726750809</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-6.6185514635647</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000458739e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8181862236986954</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1734.149</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8210248577770035</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2191.326135884863</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8234142673450309</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.10574e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-79.42</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5121144597659713</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.26419587763395</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.270105709686632</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.833606801051158</v>
+      </c>
+      <c r="L34" t="n">
+        <v>41.45632676217607</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.65379973104764</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>24.40701755156487</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-52973.43115342722</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-6.596943601805378</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000001074221e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8184522424406639</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1709.272</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8092469566930028</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2170.48391645419</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8155825801482631</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.1071e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-79.51300000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1304831456412655</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9995802760611733</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.824102859274035</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.185914003007538</v>
+      </c>
+      <c r="L35" t="n">
+        <v>39.70790059689025</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.61231714323459</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>23.98250180735008</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-51462.0670299963</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-6.137172937093055</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8187267803925982</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1684.773</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7976480179681996</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2149.137459790324</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.807561420410125</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.10818e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.602</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2839603162915313</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9205451098103361</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.443719874368739</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.220654932892219</v>
+      </c>
+      <c r="L36" t="n">
+        <v>37.65759245200111</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.58201238566807</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>23.68157744952672</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-50257.67016735821</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-5.528173270702382</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000137e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8190160205410225</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1658.788</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7853455393868694</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2128.213530054883</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7996990296911234</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.1093e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.70399999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1232232152711174</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9739127982943729</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.202335417744026</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.573768742174883</v>
+      </c>
+      <c r="L37" t="n">
+        <v>46.43259293589293</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.53579354827451</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>23.23687117540677</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-48760.84925814068</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-4.750088286913297</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000892e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8193016796615211</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1648.323</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7803909333313134</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2112.298521366809</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7937187947073476</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.11052e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.797</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2242079725817378</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9187996126687451</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.663033531451613</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.027639813458334</v>
+      </c>
+      <c r="L38" t="n">
+        <v>39.11480892770913</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.6292814653274</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>24.15431327082992</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-50362.63980650193</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-6.144962313583619</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000346234e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8196020131215307</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1625.911</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7697800751452532</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2091.866492348654</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7860412409517252</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.11142e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.88500000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.09628163967238541</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9741841030878656</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.120354554949283</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.414226438917147</v>
+      </c>
+      <c r="L39" t="n">
+        <v>47.88016550422084</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.58538057022264</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>23.7146504221334</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-48898.0485121388</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-5.501042738485921</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000047255e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.819906549407887</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1620.467</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7672026384164957</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2073.762816690547</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7792385909106563</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.11242e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.97799999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3534869785112671</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.175115882483673</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.006792044378245</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.63146428611903</v>
+      </c>
+      <c r="L40" t="n">
+        <v>42.80082741720497</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.7471153452157</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>25.41907698109745</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-52205.13770878645</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-5.957086542279285</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000004265e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8202219260390889</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1596.118</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7556747165008977</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2448.833703224132</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9201754939941371</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.11353e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-80.068</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.520487214004851</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.029235087183098</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.758815055088038</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.760017712314506</v>
+      </c>
+      <c r="L41" t="n">
+        <v>40.80039090402697</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.71733754839852</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>25.08713564989247</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-50954.37139681785</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-188.1701129836938</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000001512e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8205438244321003</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1572.444</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7444663702267236</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2439.707097982818</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9167460743175954</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.11442e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-80.167</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1204059498060851</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.157991760388923</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.389271685238115</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.692478720796502</v>
+      </c>
+      <c r="L42" t="n">
+        <v>50.14117466759721</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.67545158645949</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>24.63460829349832</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-49449.55677672399</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-192.8806656206841</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000093169e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8208714781043512</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1560.63</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7388730863337147</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2016.552669971999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7577412654904344</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.11541e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-80.247</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4074102287826862</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9613513484258321</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.631324314147351</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.089787321185214</v>
+      </c>
+      <c r="L43" t="n">
+        <v>41.76096035670199</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.77433507579211</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>25.73026928048823</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-51302.46071411396</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-5.690242034066046</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000613e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8212019332917957</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8197143521420047</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2017.191</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2664.125250129288</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.16473e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-73.529</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1705113486479065</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.669380866269891</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.495849710787956</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.680957906794052</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.98386916406004</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.81504757162242</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.227727530269064</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-22663.29617342908</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-90.89618294267939</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000011267e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8167432614181571</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1667.076</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8264343832586998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2168.676571976212</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8140295100130774</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.14144e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-78.32599999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3443449724295845</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8887198939682264</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.038171851145195</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.022664429652752</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23.84978111335135</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.73163801047664</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17.51140777795655</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-37185.60590686703</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-20.01380676788881</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000058823e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.817839548612131</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1580.666</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7835975869414449</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2065.466231047069</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7752887109743936</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.13888e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-79.29600000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3080628928242944</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8883974021555604</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.681490067924781</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.842035550518899</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29.72756344206774</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.22155861351979</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>20.60538730188275</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-42030.69338665235</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-9.427438308506908</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8180575496901341</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1531.566</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7592568081059256</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2017.464056084904</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.757270723659482</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.14279e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-79.645</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1521575297163524</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9787137605648326</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.90350576530762</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.80551532983539</v>
+      </c>
+      <c r="L15" t="n">
+        <v>37.0201779492005</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.28285371747484</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.07093812451513</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-41999.97855136172</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-5.50508476036407</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8181737072291551</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1503.591</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7453885130361975</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1986.627250811649</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7456958905048627</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.14852e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-79.82299999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3909932948450671</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.31732583051466</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.577516924395491</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.608130294759603</v>
+      </c>
+      <c r="L16" t="n">
+        <v>41.92343973626763</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.42452716147827</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>22.23171756142272</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-43750.63328642953</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-5.820776258064029</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8183282288016709</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1476.514</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7319653914775548</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1955.72785794075</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7340975646118141</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.15459e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-79.93899999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5376425147784402</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.11915567034871</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.478954541474962</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.63319318604163</v>
+      </c>
+      <c r="L17" t="n">
+        <v>43.02328505880315</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.46758262560354</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22.61020047834003</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-43879.38074988562</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-5.322663274322167</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000014804e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8185535913428899</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1447.647</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7176548973300001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1927.164144976504</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7233759542209889</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.16084e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-80.044</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.421688878271318</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.143131684485049</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.251422612861625</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.720374269805484</v>
+      </c>
+      <c r="L18" t="n">
+        <v>43.74850398809537</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.4984682620041</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>22.88972329230777</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-43782.55575465207</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-5.115168312113383</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000019271e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8188106316763375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1425.852</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7068502685169625</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1899.004609128685</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7128060548341441</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.16684e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-80.127</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6365592676736873</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.231003351028856</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.057367278282964</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.228800864550201</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36.49159985701773</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.57902636059939</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>23.65233389843858</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-44716.21498348555</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-5.586015095617313</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000576e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8191120987680168</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1398.577</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6933289906607754</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1871.932519378768</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7026443367435237</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.17275e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-80.19</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4924842691373197</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.134240198789247</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.07631910575286</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.48830110929413</v>
+      </c>
+      <c r="L20" t="n">
+        <v>36.50822922866388</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.58993977220025</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>23.75956543365822</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-44328.17691225108</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-5.454559361663996</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000451769e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8194207176122302</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1366.599</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6774762528684691</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1845.634535941393</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6927731854393204</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.17853e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-80.256</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2264305433850435</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.117392401829239</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.322577930274851</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.935797991719898</v>
+      </c>
+      <c r="L21" t="n">
+        <v>40.78955656474856</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.47833890099541</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>22.70677090829318</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-41631.84936293787</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-4.228554027017708</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8197143521420047</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
